--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_heathcare_information_and_technology.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_heathcare_information_and_technology.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="cose_ecl_n0000" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -587,23 +589,29 @@
           <t>Heathcare Information and Technology</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.139</v>
+      </c>
+      <c r="E2">
+        <v>0.186</v>
+      </c>
       <c r="G2">
-        <v>0.2</v>
+        <v>0.5356521739130435</v>
       </c>
       <c r="H2">
-        <v>0.2</v>
+        <v>0.5356521739130435</v>
       </c>
       <c r="I2">
-        <v>0.3218934911242604</v>
+        <v>0.2417391304347827</v>
       </c>
       <c r="J2">
-        <v>0.2531209945042404</v>
+        <v>0.1876184295911746</v>
       </c>
       <c r="K2">
-        <v>0.265</v>
+        <v>0.156</v>
       </c>
       <c r="L2">
-        <v>0.3136094674556213</v>
+        <v>0.271304347826087</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,70 +635,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.244</v>
+        <v>0.012</v>
       </c>
       <c r="V2">
-        <v>0.01544303797468354</v>
+        <v>0.002777777777777777</v>
       </c>
       <c r="W2">
-        <v>0.1743421052631579</v>
+        <v>0.09341317365269461</v>
       </c>
       <c r="X2">
-        <v>0.1484350775575713</v>
+        <v>0.3802271131518281</v>
       </c>
       <c r="Y2">
-        <v>0.02590702770558659</v>
+        <v>-0.2868139394991335</v>
       </c>
       <c r="Z2">
-        <v>0.4924242424242424</v>
+        <v>0.3893026404874746</v>
       </c>
       <c r="AA2">
-        <v>0.1246429139604214</v>
+        <v>0.07304035004395762</v>
       </c>
       <c r="AB2">
-        <v>0.1482131996277623</v>
+        <v>0.3786826278412587</v>
       </c>
       <c r="AC2">
-        <v>-0.02357028566734093</v>
+        <v>-0.3056422777973011</v>
       </c>
       <c r="AD2">
-        <v>0.051</v>
+        <v>0.03</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.051</v>
+        <v>0.03</v>
       </c>
       <c r="AG2">
-        <v>-0.193</v>
+        <v>0.018</v>
       </c>
       <c r="AH2">
-        <v>0.003217462620654848</v>
+        <v>0.00689655172413793</v>
       </c>
       <c r="AI2">
-        <v>0.02963393375944218</v>
+        <v>0.02803738317757009</v>
       </c>
       <c r="AJ2">
-        <v>-0.01236624591529442</v>
+        <v>0.004149377593360996</v>
       </c>
       <c r="AK2">
-        <v>-0.1306702775897089</v>
+        <v>0.01701323251417769</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AM2">
-        <v>-0.065</v>
+        <v>-0.062</v>
       </c>
       <c r="AN2">
-        <v>0.1677631578947368</v>
+        <v>0.1948051948051948</v>
+      </c>
+      <c r="AO2">
+        <v>69.5</v>
       </c>
       <c r="AP2">
-        <v>-0.6348684210526316</v>
+        <v>0.1168831168831169</v>
       </c>
       <c r="AQ2">
-        <v>-4.184615384615385</v>
+        <v>-2.241935483870968</v>
       </c>
     </row>
     <row r="3">
@@ -709,23 +720,29 @@
           <t>Heathcare Information and Technology</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.139</v>
+      </c>
+      <c r="E3">
+        <v>0.186</v>
+      </c>
       <c r="G3">
-        <v>0.2</v>
+        <v>0.5356521739130435</v>
       </c>
       <c r="H3">
-        <v>0.2</v>
+        <v>0.5356521739130435</v>
       </c>
       <c r="I3">
-        <v>0.3218934911242604</v>
+        <v>0.2417391304347827</v>
       </c>
       <c r="J3">
-        <v>0.2531209945042404</v>
+        <v>0.1876184295911746</v>
       </c>
       <c r="K3">
-        <v>0.265</v>
+        <v>0.156</v>
       </c>
       <c r="L3">
-        <v>0.3136094674556213</v>
+        <v>0.271304347826087</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,70 +766,8785 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.244</v>
+        <v>0.012</v>
       </c>
       <c r="V3">
-        <v>0.01544303797468354</v>
+        <v>0.002777777777777777</v>
       </c>
       <c r="W3">
-        <v>0.1743421052631579</v>
+        <v>0.09341317365269461</v>
       </c>
       <c r="X3">
-        <v>0.1484350775575713</v>
+        <v>0.3802271131518281</v>
       </c>
       <c r="Y3">
-        <v>0.02590702770558659</v>
+        <v>-0.2868139394991335</v>
       </c>
       <c r="Z3">
-        <v>0.4924242424242424</v>
+        <v>0.3893026404874746</v>
       </c>
       <c r="AA3">
-        <v>0.1246429139604214</v>
+        <v>0.07304035004395762</v>
       </c>
       <c r="AB3">
-        <v>0.1482131996277623</v>
+        <v>0.3786826278412587</v>
       </c>
       <c r="AC3">
-        <v>-0.02357028566734093</v>
+        <v>-0.3056422777973011</v>
       </c>
       <c r="AD3">
-        <v>0.051</v>
+        <v>0.03</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.051</v>
+        <v>0.03</v>
       </c>
       <c r="AG3">
-        <v>-0.193</v>
+        <v>0.018</v>
       </c>
       <c r="AH3">
-        <v>0.003217462620654848</v>
+        <v>0.00689655172413793</v>
       </c>
       <c r="AI3">
-        <v>0.02963393375944218</v>
+        <v>0.02803738317757009</v>
       </c>
       <c r="AJ3">
-        <v>-0.01236624591529442</v>
+        <v>0.004149377593360996</v>
       </c>
       <c r="AK3">
-        <v>-0.1306702775897089</v>
+        <v>0.01701323251417769</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AM3">
-        <v>-0.065</v>
+        <v>-0.062</v>
       </c>
       <c r="AN3">
-        <v>0.1677631578947368</v>
+        <v>0.1948051948051948</v>
+      </c>
+      <c r="AO3">
+        <v>69.5</v>
       </c>
       <c r="AP3">
-        <v>-0.6348684210526316</v>
+        <v>0.1168831168831169</v>
       </c>
       <c r="AQ3">
-        <v>-4.184615384615385</v>
+        <v>-2.241935483870968</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>eChannelling PLC (COSE:ECL.N0000)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>COSE:ECL.N0000</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Heathcare Information and Technology</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.00689655172413793</v>
+      </c>
+      <c r="F2">
+        <v>0.14</v>
+      </c>
+      <c r="G2">
+        <v>4.32</v>
+      </c>
+      <c r="H2">
+        <v>3.87777193837243</v>
+      </c>
+      <c r="I2">
+        <v>4.338</v>
+      </c>
+      <c r="J2">
+        <v>4.47477193837243</v>
+      </c>
+      <c r="K2">
+        <v>0.03</v>
+      </c>
+      <c r="L2">
+        <v>0.609</v>
+      </c>
+      <c r="M2">
+        <v>0.378682627841259</v>
+      </c>
+      <c r="N2">
+        <v>0.368294074755384</v>
+      </c>
+      <c r="O2">
+        <v>0.156276743119266</v>
+      </c>
+      <c r="P2">
+        <v>0.04788</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.380227113151828</v>
+      </c>
+      <c r="T2">
+        <v>0.420454505529517</v>
+      </c>
+      <c r="U2">
+        <v>1.28230432601101</v>
+      </c>
+      <c r="V2">
+        <v>1.43338711142271</v>
+      </c>
+      <c r="W2">
+        <v>3.622905100737613</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>4.32</v>
+      </c>
+      <c r="AB2">
+        <v>0.2662605952628563</v>
+      </c>
+      <c r="AC2">
+        <v>0.2056272935779817</v>
+      </c>
+      <c r="AD2">
+        <v>0.24</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>0.154</v>
+      </c>
+      <c r="AH2">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="AI2">
+        <v>0.03599999999999999</v>
+      </c>
+      <c r="AJ2">
+        <v>0.03</v>
+      </c>
+      <c r="AK2">
+        <v>0.03</v>
+      </c>
+      <c r="AL2">
+        <v>0.002</v>
+      </c>
+      <c r="AM2">
+        <v>0.03</v>
+      </c>
+      <c r="AN2">
+        <v>0.012</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.3784345972220451</v>
+      </c>
+      <c r="C2">
+        <v>4.353167983576907</v>
+      </c>
+      <c r="D2">
+        <v>4.341167983576907</v>
+      </c>
+      <c r="E2">
+        <v>-0.03</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.012</v>
+      </c>
+      <c r="H2">
+        <v>4.32</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.154</v>
+      </c>
+      <c r="K2">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L2">
+        <v>0.139</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.139</v>
+      </c>
+      <c r="O2">
+        <v>0.03336</v>
+      </c>
+      <c r="P2">
+        <v>0.10564</v>
+      </c>
+      <c r="Q2">
+        <v>0.12064</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.3784345972220451</v>
+      </c>
+      <c r="T2">
+        <v>1.275572139718057</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.24</v>
+      </c>
+      <c r="W2">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.3775787941887122</v>
+      </c>
+      <c r="C3">
+        <v>4.320634386410502</v>
+      </c>
+      <c r="D3">
+        <v>4.352134386410502</v>
+      </c>
+      <c r="E3">
+        <v>0.01350000000000001</v>
+      </c>
+      <c r="F3">
+        <v>0.0435</v>
+      </c>
+      <c r="G3">
+        <v>0.012</v>
+      </c>
+      <c r="H3">
+        <v>4.32</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.154</v>
+      </c>
+      <c r="K3">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L3">
+        <v>0.139</v>
+      </c>
+      <c r="M3">
+        <v>0.00198795</v>
+      </c>
+      <c r="N3">
+        <v>0.13701205</v>
+      </c>
+      <c r="O3">
+        <v>0.032882892</v>
+      </c>
+      <c r="P3">
+        <v>0.104129158</v>
+      </c>
+      <c r="Q3">
+        <v>0.119129158</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.3810418931199113</v>
+      </c>
+      <c r="T3">
+        <v>1.28536441068963</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.24</v>
+      </c>
+      <c r="W3">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>69.9212756860082</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.3767229911553793</v>
+      </c>
+      <c r="C4">
+        <v>4.28815633492199</v>
+      </c>
+      <c r="D4">
+        <v>4.36315633492199</v>
+      </c>
+      <c r="E4">
+        <v>0.05700000000000001</v>
+      </c>
+      <c r="F4">
+        <v>0.08700000000000001</v>
+      </c>
+      <c r="G4">
+        <v>0.012</v>
+      </c>
+      <c r="H4">
+        <v>4.32</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0.154</v>
+      </c>
+      <c r="K4">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L4">
+        <v>0.139</v>
+      </c>
+      <c r="M4">
+        <v>0.003975900000000001</v>
+      </c>
+      <c r="N4">
+        <v>0.1350241</v>
+      </c>
+      <c r="O4">
+        <v>0.032405784</v>
+      </c>
+      <c r="P4">
+        <v>0.102618316</v>
+      </c>
+      <c r="Q4">
+        <v>0.117618316</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.3837023991381421</v>
+      </c>
+      <c r="T4">
+        <v>1.295356523925928</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.24</v>
+      </c>
+      <c r="W4">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>34.96063784300409</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.3758671881220464</v>
+      </c>
+      <c r="C5">
+        <v>4.255734252197581</v>
+      </c>
+      <c r="D5">
+        <v>4.374234252197581</v>
+      </c>
+      <c r="E5">
+        <v>0.1005</v>
+      </c>
+      <c r="F5">
+        <v>0.1305</v>
+      </c>
+      <c r="G5">
+        <v>0.012</v>
+      </c>
+      <c r="H5">
+        <v>4.32</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.154</v>
+      </c>
+      <c r="K5">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L5">
+        <v>0.139</v>
+      </c>
+      <c r="M5">
+        <v>0.005963850000000001</v>
+      </c>
+      <c r="N5">
+        <v>0.13303615</v>
+      </c>
+      <c r="O5">
+        <v>0.031928676</v>
+      </c>
+      <c r="P5">
+        <v>0.101107474</v>
+      </c>
+      <c r="Q5">
+        <v>0.116107474</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.3864177609505633</v>
+      </c>
+      <c r="T5">
+        <v>1.305554660115553</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.24</v>
+      </c>
+      <c r="W5">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>23.30709189533607</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.3750113850887135</v>
+      </c>
+      <c r="C6">
+        <v>4.22336856563123</v>
+      </c>
+      <c r="D6">
+        <v>4.38536856563123</v>
+      </c>
+      <c r="E6">
+        <v>0.144</v>
+      </c>
+      <c r="F6">
+        <v>0.174</v>
+      </c>
+      <c r="G6">
+        <v>0.012</v>
+      </c>
+      <c r="H6">
+        <v>4.32</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0.154</v>
+      </c>
+      <c r="K6">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L6">
+        <v>0.139</v>
+      </c>
+      <c r="M6">
+        <v>0.007951800000000002</v>
+      </c>
+      <c r="N6">
+        <v>0.1310482</v>
+      </c>
+      <c r="O6">
+        <v>0.031451568</v>
+      </c>
+      <c r="P6">
+        <v>0.099596632</v>
+      </c>
+      <c r="Q6">
+        <v>0.114596632</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.3891896928007432</v>
+      </c>
+      <c r="T6">
+        <v>1.315965257475795</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.24</v>
+      </c>
+      <c r="W6">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>17.48031892150205</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.3741555820553805</v>
+      </c>
+      <c r="C7">
+        <v>4.19105970697961</v>
+      </c>
+      <c r="D7">
+        <v>4.396559706979611</v>
+      </c>
+      <c r="E7">
+        <v>0.1875</v>
+      </c>
+      <c r="F7">
+        <v>0.2175</v>
+      </c>
+      <c r="G7">
+        <v>0.012</v>
+      </c>
+      <c r="H7">
+        <v>4.32</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0.154</v>
+      </c>
+      <c r="K7">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L7">
+        <v>0.139</v>
+      </c>
+      <c r="M7">
+        <v>0.009939750000000002</v>
+      </c>
+      <c r="N7">
+        <v>0.12906025</v>
+      </c>
+      <c r="O7">
+        <v>0.03097446</v>
+      </c>
+      <c r="P7">
+        <v>0.09808579000000001</v>
+      </c>
+      <c r="Q7">
+        <v>0.11308579</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.3920199811109269</v>
+      </c>
+      <c r="T7">
+        <v>1.326595025306779</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.24</v>
+      </c>
+      <c r="W7">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>13.98425513720164</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.3733727390220476</v>
+      </c>
+      <c r="C8">
+        <v>4.157846905354773</v>
+      </c>
+      <c r="D8">
+        <v>4.406846905354773</v>
+      </c>
+      <c r="E8">
+        <v>0.231</v>
+      </c>
+      <c r="F8">
+        <v>0.261</v>
+      </c>
+      <c r="G8">
+        <v>0.012</v>
+      </c>
+      <c r="H8">
+        <v>4.32</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0.154</v>
+      </c>
+      <c r="K8">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L8">
+        <v>0.139</v>
+      </c>
+      <c r="M8">
+        <v>0.0123453</v>
+      </c>
+      <c r="N8">
+        <v>0.1266547</v>
+      </c>
+      <c r="O8">
+        <v>0.030397128</v>
+      </c>
+      <c r="P8">
+        <v>0.09625757200000001</v>
+      </c>
+      <c r="Q8">
+        <v>0.111257572</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.3949104883213273</v>
+      </c>
+      <c r="T8">
+        <v>1.337450958410762</v>
+      </c>
+      <c r="U8">
+        <v>0.0473</v>
+      </c>
+      <c r="V8">
+        <v>0.24</v>
+      </c>
+      <c r="W8">
+        <v>0.035948</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>11.25934566191182</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.3727312559887147</v>
+      </c>
+      <c r="C9">
+        <v>4.122812472652182</v>
+      </c>
+      <c r="D9">
+        <v>4.415312472652182</v>
+      </c>
+      <c r="E9">
+        <v>0.2745000000000001</v>
+      </c>
+      <c r="F9">
+        <v>0.3045</v>
+      </c>
+      <c r="G9">
+        <v>0.012</v>
+      </c>
+      <c r="H9">
+        <v>4.32</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.154</v>
+      </c>
+      <c r="K9">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L9">
+        <v>0.139</v>
+      </c>
+      <c r="M9">
+        <v>0.01555995</v>
+      </c>
+      <c r="N9">
+        <v>0.12344005</v>
+      </c>
+      <c r="O9">
+        <v>0.029625612</v>
+      </c>
+      <c r="P9">
+        <v>0.093814438</v>
+      </c>
+      <c r="Q9">
+        <v>0.108814438</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.3978631569771126</v>
+      </c>
+      <c r="T9">
+        <v>1.348540352441713</v>
+      </c>
+      <c r="U9">
+        <v>0.0511</v>
+      </c>
+      <c r="V9">
+        <v>0.24</v>
+      </c>
+      <c r="W9">
+        <v>0.038836</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>8.933190659353016</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.3719164929553819</v>
+      </c>
+      <c r="C10">
+        <v>4.090111797991538</v>
+      </c>
+      <c r="D10">
+        <v>4.426111797991538</v>
+      </c>
+      <c r="E10">
+        <v>0.3180000000000001</v>
+      </c>
+      <c r="F10">
+        <v>0.348</v>
+      </c>
+      <c r="G10">
+        <v>0.012</v>
+      </c>
+      <c r="H10">
+        <v>4.32</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0.154</v>
+      </c>
+      <c r="K10">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L10">
+        <v>0.139</v>
+      </c>
+      <c r="M10">
+        <v>0.0177828</v>
+      </c>
+      <c r="N10">
+        <v>0.1212172</v>
+      </c>
+      <c r="O10">
+        <v>0.029092128</v>
+      </c>
+      <c r="P10">
+        <v>0.092125072</v>
+      </c>
+      <c r="Q10">
+        <v>0.107125072</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.4008800140819368</v>
+      </c>
+      <c r="T10">
+        <v>1.359870820255946</v>
+      </c>
+      <c r="U10">
+        <v>0.0511</v>
+      </c>
+      <c r="V10">
+        <v>0.24</v>
+      </c>
+      <c r="W10">
+        <v>0.038836</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>7.816541826933891</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.371231689922049</v>
+      </c>
+      <c r="C11">
+        <v>4.055729505108587</v>
+      </c>
+      <c r="D11">
+        <v>4.435229505108587</v>
+      </c>
+      <c r="E11">
+        <v>0.3615</v>
+      </c>
+      <c r="F11">
+        <v>0.3915</v>
+      </c>
+      <c r="G11">
+        <v>0.012</v>
+      </c>
+      <c r="H11">
+        <v>4.32</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.154</v>
+      </c>
+      <c r="K11">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L11">
+        <v>0.139</v>
+      </c>
+      <c r="M11">
+        <v>0.0207495</v>
+      </c>
+      <c r="N11">
+        <v>0.1182505</v>
+      </c>
+      <c r="O11">
+        <v>0.02838012</v>
+      </c>
+      <c r="P11">
+        <v>0.08987038</v>
+      </c>
+      <c r="Q11">
+        <v>0.10487038</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.4039631757385153</v>
+      </c>
+      <c r="T11">
+        <v>1.37145030934082</v>
+      </c>
+      <c r="U11">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V11">
+        <v>0.24</v>
+      </c>
+      <c r="W11">
+        <v>0.04028</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>6.698956601363887</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.3705833668887161</v>
+      </c>
+      <c r="C12">
+        <v>4.020896188653468</v>
+      </c>
+      <c r="D12">
+        <v>4.443896188653468</v>
+      </c>
+      <c r="E12">
+        <v>0.405</v>
+      </c>
+      <c r="F12">
+        <v>0.4350000000000001</v>
+      </c>
+      <c r="G12">
+        <v>0.012</v>
+      </c>
+      <c r="H12">
+        <v>4.32</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0.154</v>
+      </c>
+      <c r="K12">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L12">
+        <v>0.139</v>
+      </c>
+      <c r="M12">
+        <v>0.023925</v>
+      </c>
+      <c r="N12">
+        <v>0.115075</v>
+      </c>
+      <c r="O12">
+        <v>0.027618</v>
+      </c>
+      <c r="P12">
+        <v>0.08745700000000001</v>
+      </c>
+      <c r="Q12">
+        <v>0.102457</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.4071148520985734</v>
+      </c>
+      <c r="T12">
+        <v>1.383287120405359</v>
+      </c>
+      <c r="U12">
+        <v>0.055</v>
+      </c>
+      <c r="V12">
+        <v>0.24</v>
+      </c>
+      <c r="W12">
+        <v>0.0418</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>5.8098223615465</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.3697982438553831</v>
+      </c>
+      <c r="C13">
+        <v>3.987937045954744</v>
+      </c>
+      <c r="D13">
+        <v>4.454437045954744</v>
+      </c>
+      <c r="E13">
+        <v>0.4485</v>
+      </c>
+      <c r="F13">
+        <v>0.4785</v>
+      </c>
+      <c r="G13">
+        <v>0.012</v>
+      </c>
+      <c r="H13">
+        <v>4.32</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.154</v>
+      </c>
+      <c r="K13">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L13">
+        <v>0.139</v>
+      </c>
+      <c r="M13">
+        <v>0.0263175</v>
+      </c>
+      <c r="N13">
+        <v>0.1126825</v>
+      </c>
+      <c r="O13">
+        <v>0.0270438</v>
+      </c>
+      <c r="P13">
+        <v>0.08563870000000001</v>
+      </c>
+      <c r="Q13">
+        <v>0.1006387</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.4103373526464979</v>
+      </c>
+      <c r="T13">
+        <v>1.395389927224157</v>
+      </c>
+      <c r="U13">
+        <v>0.055</v>
+      </c>
+      <c r="V13">
+        <v>0.24</v>
+      </c>
+      <c r="W13">
+        <v>0.0418</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>5.281656692315</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.3690131208220502</v>
+      </c>
+      <c r="C14">
+        <v>3.955028027671654</v>
+      </c>
+      <c r="D14">
+        <v>4.465028027671655</v>
+      </c>
+      <c r="E14">
+        <v>0.492</v>
+      </c>
+      <c r="F14">
+        <v>0.522</v>
+      </c>
+      <c r="G14">
+        <v>0.012</v>
+      </c>
+      <c r="H14">
+        <v>4.32</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.154</v>
+      </c>
+      <c r="K14">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L14">
+        <v>0.139</v>
+      </c>
+      <c r="M14">
+        <v>0.02871</v>
+      </c>
+      <c r="N14">
+        <v>0.11029</v>
+      </c>
+      <c r="O14">
+        <v>0.0264696</v>
+      </c>
+      <c r="P14">
+        <v>0.08382040000000002</v>
+      </c>
+      <c r="Q14">
+        <v>0.0988204</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.4136330918432389</v>
+      </c>
+      <c r="T14">
+        <v>1.407767797834292</v>
+      </c>
+      <c r="U14">
+        <v>0.055</v>
+      </c>
+      <c r="V14">
+        <v>0.24</v>
+      </c>
+      <c r="W14">
+        <v>0.0418</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>4.841518634622084</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.3686034377887173</v>
+      </c>
+      <c r="C15">
+        <v>3.91707450177319</v>
+      </c>
+      <c r="D15">
+        <v>4.470574501773191</v>
+      </c>
+      <c r="E15">
+        <v>0.5355000000000001</v>
+      </c>
+      <c r="F15">
+        <v>0.5655000000000001</v>
+      </c>
+      <c r="G15">
+        <v>0.012</v>
+      </c>
+      <c r="H15">
+        <v>4.32</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0.154</v>
+      </c>
+      <c r="K15">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L15">
+        <v>0.139</v>
+      </c>
+      <c r="M15">
+        <v>0.03325140000000001</v>
+      </c>
+      <c r="N15">
+        <v>0.1057486</v>
+      </c>
+      <c r="O15">
+        <v>0.025379664</v>
+      </c>
+      <c r="P15">
+        <v>0.080368936</v>
+      </c>
+      <c r="Q15">
+        <v>0.09536893599999999</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.4170045951594452</v>
+      </c>
+      <c r="T15">
+        <v>1.420430217194084</v>
+      </c>
+      <c r="U15">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V15">
+        <v>0.24</v>
+      </c>
+      <c r="W15">
+        <v>0.04468800000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>4.180275116235707</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.3682940747553844</v>
+      </c>
+      <c r="C16">
+        <v>3.877771938372427</v>
+      </c>
+      <c r="D16">
+        <v>4.474771938372427</v>
+      </c>
+      <c r="E16">
+        <v>0.5790000000000001</v>
+      </c>
+      <c r="F16">
+        <v>0.6090000000000001</v>
+      </c>
+      <c r="G16">
+        <v>0.012</v>
+      </c>
+      <c r="H16">
+        <v>4.32</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0.154</v>
+      </c>
+      <c r="K16">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L16">
+        <v>0.139</v>
+      </c>
+      <c r="M16">
+        <v>0.03836700000000001</v>
+      </c>
+      <c r="N16">
+        <v>0.100633</v>
+      </c>
+      <c r="O16">
+        <v>0.02415192</v>
+      </c>
+      <c r="P16">
+        <v>0.07648108000000001</v>
+      </c>
+      <c r="Q16">
+        <v>0.09148107999999999</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.4204545055295167</v>
+      </c>
+      <c r="T16">
+        <v>1.433387111422709</v>
+      </c>
+      <c r="U16">
+        <v>0.063</v>
+      </c>
+      <c r="V16">
+        <v>0.24</v>
+      </c>
+      <c r="W16">
+        <v>0.04788</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>3.622905100737613</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.3683791517220514</v>
+      </c>
+      <c r="C17">
+        <v>3.833116828830289</v>
+      </c>
+      <c r="D17">
+        <v>4.47361682883029</v>
+      </c>
+      <c r="E17">
+        <v>0.6225000000000001</v>
+      </c>
+      <c r="F17">
+        <v>0.6525000000000001</v>
+      </c>
+      <c r="G17">
+        <v>0.012</v>
+      </c>
+      <c r="H17">
+        <v>4.32</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0.154</v>
+      </c>
+      <c r="K17">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L17">
+        <v>0.139</v>
+      </c>
+      <c r="M17">
+        <v>0.04574025</v>
+      </c>
+      <c r="N17">
+        <v>0.09325975</v>
+      </c>
+      <c r="O17">
+        <v>0.02238234</v>
+      </c>
+      <c r="P17">
+        <v>0.07087741</v>
+      </c>
+      <c r="Q17">
+        <v>0.08587740999999999</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.423985590261237</v>
+      </c>
+      <c r="T17">
+        <v>1.446648873750831</v>
+      </c>
+      <c r="U17">
+        <v>0.0701</v>
+      </c>
+      <c r="V17">
+        <v>0.24</v>
+      </c>
+      <c r="W17">
+        <v>0.053276</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>3.038899000333404</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.3702988686887186</v>
+      </c>
+      <c r="C18">
+        <v>3.763710019064559</v>
+      </c>
+      <c r="D18">
+        <v>4.44771001906456</v>
+      </c>
+      <c r="E18">
+        <v>0.666</v>
+      </c>
+      <c r="F18">
+        <v>0.6960000000000001</v>
+      </c>
+      <c r="G18">
+        <v>0.012</v>
+      </c>
+      <c r="H18">
+        <v>4.32</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0.154</v>
+      </c>
+      <c r="K18">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L18">
+        <v>0.139</v>
+      </c>
+      <c r="M18">
+        <v>0.06361440000000002</v>
+      </c>
+      <c r="N18">
+        <v>0.0753856</v>
+      </c>
+      <c r="O18">
+        <v>0.018092544</v>
+      </c>
+      <c r="P18">
+        <v>0.05729305599999999</v>
+      </c>
+      <c r="Q18">
+        <v>0.07229305599999998</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.4276007484389507</v>
+      </c>
+      <c r="T18">
+        <v>1.460226392324861</v>
+      </c>
+      <c r="U18">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V18">
+        <v>0.24</v>
+      </c>
+      <c r="W18">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>2.185039865187756</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.3697903856553857</v>
+      </c>
+      <c r="C19">
+        <v>3.727042800860928</v>
+      </c>
+      <c r="D19">
+        <v>4.454542800860929</v>
+      </c>
+      <c r="E19">
+        <v>0.7095000000000001</v>
+      </c>
+      <c r="F19">
+        <v>0.7395000000000002</v>
+      </c>
+      <c r="G19">
+        <v>0.012</v>
+      </c>
+      <c r="H19">
+        <v>4.32</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0.154</v>
+      </c>
+      <c r="K19">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L19">
+        <v>0.139</v>
+      </c>
+      <c r="M19">
+        <v>0.06759030000000002</v>
+      </c>
+      <c r="N19">
+        <v>0.07140969999999999</v>
+      </c>
+      <c r="O19">
+        <v>0.017138328</v>
+      </c>
+      <c r="P19">
+        <v>0.054271372</v>
+      </c>
+      <c r="Q19">
+        <v>0.06927137199999998</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.4313030188619105</v>
+      </c>
+      <c r="T19">
+        <v>1.474131080021157</v>
+      </c>
+      <c r="U19">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V19">
+        <v>0.24</v>
+      </c>
+      <c r="W19">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>2.056508108412006</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.3721683826220528</v>
+      </c>
+      <c r="C20">
+        <v>3.651767474163719</v>
+      </c>
+      <c r="D20">
+        <v>4.422767474163719</v>
+      </c>
+      <c r="E20">
+        <v>0.753</v>
+      </c>
+      <c r="F20">
+        <v>0.783</v>
+      </c>
+      <c r="G20">
+        <v>0.012</v>
+      </c>
+      <c r="H20">
+        <v>4.32</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0.154</v>
+      </c>
+      <c r="K20">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L20">
+        <v>0.139</v>
+      </c>
+      <c r="M20">
+        <v>0.0880875</v>
+      </c>
+      <c r="N20">
+        <v>0.05091250000000001</v>
+      </c>
+      <c r="O20">
+        <v>0.012219</v>
+      </c>
+      <c r="P20">
+        <v>0.03869350000000001</v>
+      </c>
+      <c r="Q20">
+        <v>0.0536935</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.4350955885634789</v>
+      </c>
+      <c r="T20">
+        <v>1.488374906441752</v>
+      </c>
+      <c r="U20">
+        <v>0.1125</v>
+      </c>
+      <c r="V20">
+        <v>0.24</v>
+      </c>
+      <c r="W20">
+        <v>0.08550000000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>1.577976443876827</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.3874991779176317</v>
+      </c>
+      <c r="C21">
+        <v>3.413817509608983</v>
+      </c>
+      <c r="D21">
+        <v>4.228317509608984</v>
+      </c>
+      <c r="E21">
+        <v>0.7965000000000001</v>
+      </c>
+      <c r="F21">
+        <v>0.8265000000000001</v>
+      </c>
+      <c r="G21">
+        <v>0.012</v>
+      </c>
+      <c r="H21">
+        <v>4.32</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0.154</v>
+      </c>
+      <c r="K21">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L21">
+        <v>0.139</v>
+      </c>
+      <c r="M21">
+        <v>0.1624899</v>
+      </c>
+      <c r="N21">
+        <v>-0.02348990000000001</v>
+      </c>
+      <c r="O21">
+        <v>-0.005637576000000002</v>
+      </c>
+      <c r="P21">
+        <v>-0.01785232400000001</v>
+      </c>
+      <c r="Q21">
+        <v>-0.002852324000000021</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.4417458560924359</v>
+      </c>
+      <c r="T21">
+        <v>1.513351443140288</v>
+      </c>
+      <c r="U21">
+        <v>0.1966</v>
+      </c>
+      <c r="V21">
+        <v>0.2053050681919307</v>
+      </c>
+      <c r="W21">
+        <v>0.1562370235934664</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.8554377841330445</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.3890771779176316</v>
+      </c>
+      <c r="C22">
+        <v>3.35126892337271</v>
+      </c>
+      <c r="D22">
+        <v>4.209268923372711</v>
+      </c>
+      <c r="E22">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="F22">
+        <v>0.8700000000000001</v>
+      </c>
+      <c r="G22">
+        <v>0.012</v>
+      </c>
+      <c r="H22">
+        <v>4.32</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0.154</v>
+      </c>
+      <c r="K22">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L22">
+        <v>0.139</v>
+      </c>
+      <c r="M22">
+        <v>0.171042</v>
+      </c>
+      <c r="N22">
+        <v>-0.03204200000000001</v>
+      </c>
+      <c r="O22">
+        <v>-0.007690080000000004</v>
+      </c>
+      <c r="P22">
+        <v>-0.02435192000000001</v>
+      </c>
+      <c r="Q22">
+        <v>-0.009351920000000027</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.4467826792935912</v>
+      </c>
+      <c r="T22">
+        <v>1.532268336179542</v>
+      </c>
+      <c r="U22">
+        <v>0.1966</v>
+      </c>
+      <c r="V22">
+        <v>0.1950398147823341</v>
+      </c>
+      <c r="W22">
+        <v>0.1582551724137931</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.8126658949263923</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.3953330030118289</v>
+      </c>
+      <c r="C23">
+        <v>3.233911945374558</v>
+      </c>
+      <c r="D23">
+        <v>4.135411945374559</v>
+      </c>
+      <c r="E23">
+        <v>0.8835000000000001</v>
+      </c>
+      <c r="F23">
+        <v>0.9135000000000001</v>
+      </c>
+      <c r="G23">
+        <v>0.012</v>
+      </c>
+      <c r="H23">
+        <v>4.32</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0.154</v>
+      </c>
+      <c r="K23">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L23">
+        <v>0.139</v>
+      </c>
+      <c r="M23">
+        <v>0.1953063</v>
+      </c>
+      <c r="N23">
+        <v>-0.0563063</v>
+      </c>
+      <c r="O23">
+        <v>-0.013513512</v>
+      </c>
+      <c r="P23">
+        <v>-0.04279278800000001</v>
+      </c>
+      <c r="Q23">
+        <v>-0.02779278800000002</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.4532961626950257</v>
+      </c>
+      <c r="T23">
+        <v>1.556731150119412</v>
+      </c>
+      <c r="U23">
+        <v>0.2138</v>
+      </c>
+      <c r="V23">
+        <v>0.1708086221489015</v>
+      </c>
+      <c r="W23">
+        <v>0.1772811165845649</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.7117025922870895</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.3970830030118289</v>
+      </c>
+      <c r="C24">
+        <v>3.170212910411778</v>
+      </c>
+      <c r="D24">
+        <v>4.115212910411779</v>
+      </c>
+      <c r="E24">
+        <v>0.927</v>
+      </c>
+      <c r="F24">
+        <v>0.9570000000000001</v>
+      </c>
+      <c r="G24">
+        <v>0.012</v>
+      </c>
+      <c r="H24">
+        <v>4.32</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0.154</v>
+      </c>
+      <c r="K24">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L24">
+        <v>0.139</v>
+      </c>
+      <c r="M24">
+        <v>0.2046066</v>
+      </c>
+      <c r="N24">
+        <v>-0.06560659999999999</v>
+      </c>
+      <c r="O24">
+        <v>-0.015745584</v>
+      </c>
+      <c r="P24">
+        <v>-0.04986101599999999</v>
+      </c>
+      <c r="Q24">
+        <v>-0.03486101600000001</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.4586102160629106</v>
+      </c>
+      <c r="T24">
+        <v>1.57668924178761</v>
+      </c>
+      <c r="U24">
+        <v>0.2138</v>
+      </c>
+      <c r="V24">
+        <v>0.163044593869406</v>
+      </c>
+      <c r="W24">
+        <v>0.178941065830721</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.6793524744558583</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.3988330030118288</v>
+      </c>
+      <c r="C25">
+        <v>3.106710236954136</v>
+      </c>
+      <c r="D25">
+        <v>4.095210236954136</v>
+      </c>
+      <c r="E25">
+        <v>0.9705000000000001</v>
+      </c>
+      <c r="F25">
+        <v>1.0005</v>
+      </c>
+      <c r="G25">
+        <v>0.012</v>
+      </c>
+      <c r="H25">
+        <v>4.32</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0.154</v>
+      </c>
+      <c r="K25">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L25">
+        <v>0.139</v>
+      </c>
+      <c r="M25">
+        <v>0.2139069</v>
+      </c>
+      <c r="N25">
+        <v>-0.07490690000000003</v>
+      </c>
+      <c r="O25">
+        <v>-0.01797765600000001</v>
+      </c>
+      <c r="P25">
+        <v>-0.05692924400000002</v>
+      </c>
+      <c r="Q25">
+        <v>-0.04192924400000003</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.4640622967910003</v>
+      </c>
+      <c r="T25">
+        <v>1.597165725447189</v>
+      </c>
+      <c r="U25">
+        <v>0.2138</v>
+      </c>
+      <c r="V25">
+        <v>0.1559556984837796</v>
+      </c>
+      <c r="W25">
+        <v>0.1804566716641679</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.6498154103490816</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.4005830030118289</v>
+      </c>
+      <c r="C26">
+        <v>3.043401075509269</v>
+      </c>
+      <c r="D26">
+        <v>4.075401075509269</v>
+      </c>
+      <c r="E26">
+        <v>1.014</v>
+      </c>
+      <c r="F26">
+        <v>1.044</v>
+      </c>
+      <c r="G26">
+        <v>0.012</v>
+      </c>
+      <c r="H26">
+        <v>4.32</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0.154</v>
+      </c>
+      <c r="K26">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L26">
+        <v>0.139</v>
+      </c>
+      <c r="M26">
+        <v>0.2232072</v>
+      </c>
+      <c r="N26">
+        <v>-0.08420719999999998</v>
+      </c>
+      <c r="O26">
+        <v>-0.020209728</v>
+      </c>
+      <c r="P26">
+        <v>-0.06399747199999999</v>
+      </c>
+      <c r="Q26">
+        <v>-0.048997472</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.469657853327724</v>
+      </c>
+      <c r="T26">
+        <v>1.618181063939915</v>
+      </c>
+      <c r="U26">
+        <v>0.2138</v>
+      </c>
+      <c r="V26">
+        <v>0.1494575443802888</v>
+      </c>
+      <c r="W26">
+        <v>0.1818459770114942</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.6227397682512035</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.4023330030118288</v>
+      </c>
+      <c r="C27">
+        <v>2.980282631453148</v>
+      </c>
+      <c r="D27">
+        <v>4.055782631453149</v>
+      </c>
+      <c r="E27">
+        <v>1.0575</v>
+      </c>
+      <c r="F27">
+        <v>1.0875</v>
+      </c>
+      <c r="G27">
+        <v>0.012</v>
+      </c>
+      <c r="H27">
+        <v>4.32</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0.154</v>
+      </c>
+      <c r="K27">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L27">
+        <v>0.139</v>
+      </c>
+      <c r="M27">
+        <v>0.2325075</v>
+      </c>
+      <c r="N27">
+        <v>-0.09350749999999999</v>
+      </c>
+      <c r="O27">
+        <v>-0.0224418</v>
+      </c>
+      <c r="P27">
+        <v>-0.0710657</v>
+      </c>
+      <c r="Q27">
+        <v>-0.05606570000000001</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.4754026247054269</v>
+      </c>
+      <c r="T27">
+        <v>1.639756811459114</v>
+      </c>
+      <c r="U27">
+        <v>0.2138</v>
+      </c>
+      <c r="V27">
+        <v>0.1434792426050773</v>
+      </c>
+      <c r="W27">
+        <v>0.1831241379310345</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.5978301775211552</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.4040830030118289</v>
+      </c>
+      <c r="C28">
+        <v>2.917352163715745</v>
+      </c>
+      <c r="D28">
+        <v>4.036352163715746</v>
+      </c>
+      <c r="E28">
+        <v>1.101</v>
+      </c>
+      <c r="F28">
+        <v>1.131</v>
+      </c>
+      <c r="G28">
+        <v>0.012</v>
+      </c>
+      <c r="H28">
+        <v>4.32</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0.154</v>
+      </c>
+      <c r="K28">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L28">
+        <v>0.139</v>
+      </c>
+      <c r="M28">
+        <v>0.2418078</v>
+      </c>
+      <c r="N28">
+        <v>-0.1028078</v>
+      </c>
+      <c r="O28">
+        <v>-0.02467387200000001</v>
+      </c>
+      <c r="P28">
+        <v>-0.07813392800000002</v>
+      </c>
+      <c r="Q28">
+        <v>-0.06313392800000003</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.4813026601744193</v>
+      </c>
+      <c r="T28">
+        <v>1.661915687289643</v>
+      </c>
+      <c r="U28">
+        <v>0.2138</v>
+      </c>
+      <c r="V28">
+        <v>0.1379608101971896</v>
+      </c>
+      <c r="W28">
+        <v>0.1843039787798408</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.5748367091549569</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.4058330030118288</v>
+      </c>
+      <c r="C29">
+        <v>2.854606983504322</v>
+      </c>
+      <c r="D29">
+        <v>4.017106983504322</v>
+      </c>
+      <c r="E29">
+        <v>1.1445</v>
+      </c>
+      <c r="F29">
+        <v>1.1745</v>
+      </c>
+      <c r="G29">
+        <v>0.012</v>
+      </c>
+      <c r="H29">
+        <v>4.32</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0.154</v>
+      </c>
+      <c r="K29">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L29">
+        <v>0.139</v>
+      </c>
+      <c r="M29">
+        <v>0.2511081000000001</v>
+      </c>
+      <c r="N29">
+        <v>-0.1121081</v>
+      </c>
+      <c r="O29">
+        <v>-0.02690594400000001</v>
+      </c>
+      <c r="P29">
+        <v>-0.08520215600000003</v>
+      </c>
+      <c r="Q29">
+        <v>-0.07020215600000004</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.4873643404507811</v>
+      </c>
+      <c r="T29">
+        <v>1.684681655608679</v>
+      </c>
+      <c r="U29">
+        <v>0.2138</v>
+      </c>
+      <c r="V29">
+        <v>0.1328511505602567</v>
+      </c>
+      <c r="W29">
+        <v>0.1853964240102171</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.5535464606677363</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.4075830030118289</v>
+      </c>
+      <c r="C30">
+        <v>2.792044453063061</v>
+      </c>
+      <c r="D30">
+        <v>3.998044453063061</v>
+      </c>
+      <c r="E30">
+        <v>1.188</v>
+      </c>
+      <c r="F30">
+        <v>1.218</v>
+      </c>
+      <c r="G30">
+        <v>0.012</v>
+      </c>
+      <c r="H30">
+        <v>4.32</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0.154</v>
+      </c>
+      <c r="K30">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L30">
+        <v>0.139</v>
+      </c>
+      <c r="M30">
+        <v>0.2604084</v>
+      </c>
+      <c r="N30">
+        <v>-0.1214084</v>
+      </c>
+      <c r="O30">
+        <v>-0.02913801600000001</v>
+      </c>
+      <c r="P30">
+        <v>-0.09227038400000002</v>
+      </c>
+      <c r="Q30">
+        <v>-0.07727038400000004</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.4935944007348198</v>
+      </c>
+      <c r="T30">
+        <v>1.708080011936577</v>
+      </c>
+      <c r="U30">
+        <v>0.2138</v>
+      </c>
+      <c r="V30">
+        <v>0.1281064666116761</v>
+      </c>
+      <c r="W30">
+        <v>0.1864108374384236</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.5337769442153171</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.4093330030118288</v>
+      </c>
+      <c r="C31">
+        <v>2.72966198446785</v>
+      </c>
+      <c r="D31">
+        <v>3.97916198446785</v>
+      </c>
+      <c r="E31">
+        <v>1.2315</v>
+      </c>
+      <c r="F31">
+        <v>1.2615</v>
+      </c>
+      <c r="G31">
+        <v>0.012</v>
+      </c>
+      <c r="H31">
+        <v>4.32</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0.154</v>
+      </c>
+      <c r="K31">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L31">
+        <v>0.139</v>
+      </c>
+      <c r="M31">
+        <v>0.2697087</v>
+      </c>
+      <c r="N31">
+        <v>-0.1307087</v>
+      </c>
+      <c r="O31">
+        <v>-0.031370088</v>
+      </c>
+      <c r="P31">
+        <v>-0.09933861200000001</v>
+      </c>
+      <c r="Q31">
+        <v>-0.08433861200000002</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.4999999556747468</v>
+      </c>
+      <c r="T31">
+        <v>1.73213747689343</v>
+      </c>
+      <c r="U31">
+        <v>0.2138</v>
+      </c>
+      <c r="V31">
+        <v>0.1236890022457562</v>
+      </c>
+      <c r="W31">
+        <v>0.1873552913198573</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.5153708426906511</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.4198584038381453</v>
+      </c>
+      <c r="C32">
+        <v>2.576251602181268</v>
+      </c>
+      <c r="D32">
+        <v>3.869251602181269</v>
+      </c>
+      <c r="E32">
+        <v>1.275</v>
+      </c>
+      <c r="F32">
+        <v>1.305</v>
+      </c>
+      <c r="G32">
+        <v>0.012</v>
+      </c>
+      <c r="H32">
+        <v>4.32</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0.154</v>
+      </c>
+      <c r="K32">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L32">
+        <v>0.139</v>
+      </c>
+      <c r="M32">
+        <v>0.3116340000000001</v>
+      </c>
+      <c r="N32">
+        <v>-0.1726340000000001</v>
+      </c>
+      <c r="O32">
+        <v>-0.04143216000000002</v>
+      </c>
+      <c r="P32">
+        <v>-0.13120184</v>
+      </c>
+      <c r="Q32">
+        <v>-0.1162018400000001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.5084105276505524</v>
+      </c>
+      <c r="T32">
+        <v>1.763725222603616</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.1070486532278249</v>
+      </c>
+      <c r="W32">
+        <v>0.2132367816091954</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.4460360551159372</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.4218584038381453</v>
+      </c>
+      <c r="C33">
+        <v>2.51254971357414</v>
+      </c>
+      <c r="D33">
+        <v>3.84904971357414</v>
+      </c>
+      <c r="E33">
+        <v>1.3185</v>
+      </c>
+      <c r="F33">
+        <v>1.3485</v>
+      </c>
+      <c r="G33">
+        <v>0.012</v>
+      </c>
+      <c r="H33">
+        <v>4.32</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0.154</v>
+      </c>
+      <c r="K33">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L33">
+        <v>0.139</v>
+      </c>
+      <c r="M33">
+        <v>0.3220218000000001</v>
+      </c>
+      <c r="N33">
+        <v>-0.1830218000000001</v>
+      </c>
+      <c r="O33">
+        <v>-0.04392523200000002</v>
+      </c>
+      <c r="P33">
+        <v>-0.1390965680000001</v>
+      </c>
+      <c r="Q33">
+        <v>-0.1240965680000001</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.5152164773266474</v>
+      </c>
+      <c r="T33">
+        <v>1.789286457713813</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.103595470865637</v>
+      </c>
+      <c r="W33">
+        <v>0.2140614015572859</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.4316477952734876</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.4238584038381453</v>
+      </c>
+      <c r="C34">
+        <v>2.449057682883689</v>
+      </c>
+      <c r="D34">
+        <v>3.829057682883689</v>
+      </c>
+      <c r="E34">
+        <v>1.362</v>
+      </c>
+      <c r="F34">
+        <v>1.392</v>
+      </c>
+      <c r="G34">
+        <v>0.012</v>
+      </c>
+      <c r="H34">
+        <v>4.32</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0.154</v>
+      </c>
+      <c r="K34">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L34">
+        <v>0.139</v>
+      </c>
+      <c r="M34">
+        <v>0.3324096</v>
+      </c>
+      <c r="N34">
+        <v>-0.1934096</v>
+      </c>
+      <c r="O34">
+        <v>-0.046418304</v>
+      </c>
+      <c r="P34">
+        <v>-0.146991296</v>
+      </c>
+      <c r="Q34">
+        <v>-0.131991296</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.5222226019932158</v>
+      </c>
+      <c r="T34">
+        <v>1.815599493856663</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.1003581124010859</v>
+      </c>
+      <c r="W34">
+        <v>0.2148344827586207</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.4181588016711912</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.4258584038381452</v>
+      </c>
+      <c r="C35">
+        <v>2.385772256989747</v>
+      </c>
+      <c r="D35">
+        <v>3.809272256989748</v>
+      </c>
+      <c r="E35">
+        <v>1.4055</v>
+      </c>
+      <c r="F35">
+        <v>1.4355</v>
+      </c>
+      <c r="G35">
+        <v>0.012</v>
+      </c>
+      <c r="H35">
+        <v>4.32</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0.154</v>
+      </c>
+      <c r="K35">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L35">
+        <v>0.139</v>
+      </c>
+      <c r="M35">
+        <v>0.3427974000000001</v>
+      </c>
+      <c r="N35">
+        <v>-0.2037974000000001</v>
+      </c>
+      <c r="O35">
+        <v>-0.04891137600000001</v>
+      </c>
+      <c r="P35">
+        <v>-0.1548860240000001</v>
+      </c>
+      <c r="Q35">
+        <v>-0.1398860240000001</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.5294378647095324</v>
+      </c>
+      <c r="T35">
+        <v>1.842697993764971</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.09731695747984084</v>
+      </c>
+      <c r="W35">
+        <v>0.215560710553814</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.4054873228326702</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.4278584038381453</v>
+      </c>
+      <c r="C36">
+        <v>2.322690249664314</v>
+      </c>
+      <c r="D36">
+        <v>3.789690249664314</v>
+      </c>
+      <c r="E36">
+        <v>1.449</v>
+      </c>
+      <c r="F36">
+        <v>1.479</v>
+      </c>
+      <c r="G36">
+        <v>0.012</v>
+      </c>
+      <c r="H36">
+        <v>4.32</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0.154</v>
+      </c>
+      <c r="K36">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L36">
+        <v>0.139</v>
+      </c>
+      <c r="M36">
+        <v>0.3531852000000001</v>
+      </c>
+      <c r="N36">
+        <v>-0.2141852000000001</v>
+      </c>
+      <c r="O36">
+        <v>-0.05140444800000002</v>
+      </c>
+      <c r="P36">
+        <v>-0.1627807520000001</v>
+      </c>
+      <c r="Q36">
+        <v>-0.1477807520000001</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.536871771750586</v>
+      </c>
+      <c r="T36">
+        <v>1.870617660337168</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.09445469402455139</v>
+      </c>
+      <c r="W36">
+        <v>0.2162442190669371</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.3935612251022975</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.4298584038381454</v>
+      </c>
+      <c r="C37">
+        <v>2.259808539861023</v>
+      </c>
+      <c r="D37">
+        <v>3.770308539861024</v>
+      </c>
+      <c r="E37">
+        <v>1.4925</v>
+      </c>
+      <c r="F37">
+        <v>1.5225</v>
+      </c>
+      <c r="G37">
+        <v>0.012</v>
+      </c>
+      <c r="H37">
+        <v>4.32</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0.154</v>
+      </c>
+      <c r="K37">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L37">
+        <v>0.139</v>
+      </c>
+      <c r="M37">
+        <v>0.3635730000000001</v>
+      </c>
+      <c r="N37">
+        <v>-0.2245730000000001</v>
+      </c>
+      <c r="O37">
+        <v>-0.05389752000000002</v>
+      </c>
+      <c r="P37">
+        <v>-0.17067548</v>
+      </c>
+      <c r="Q37">
+        <v>-0.1556754800000001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.5445344143929027</v>
+      </c>
+      <c r="T37">
+        <v>1.899396393573124</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.09175598848099278</v>
+      </c>
+      <c r="W37">
+        <v>0.2168886699507389</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.3823166186708034</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.4318584038381453</v>
+      </c>
+      <c r="C38">
+        <v>2.19712407005682</v>
+      </c>
+      <c r="D38">
+        <v>3.751124070056819</v>
+      </c>
+      <c r="E38">
+        <v>1.536</v>
+      </c>
+      <c r="F38">
+        <v>1.566</v>
+      </c>
+      <c r="G38">
+        <v>0.012</v>
+      </c>
+      <c r="H38">
+        <v>4.32</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0.154</v>
+      </c>
+      <c r="K38">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L38">
+        <v>0.139</v>
+      </c>
+      <c r="M38">
+        <v>0.3739608</v>
+      </c>
+      <c r="N38">
+        <v>-0.2349608</v>
+      </c>
+      <c r="O38">
+        <v>-0.056390592</v>
+      </c>
+      <c r="P38">
+        <v>-0.178570208</v>
+      </c>
+      <c r="Q38">
+        <v>-0.163570208</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.5524365146177916</v>
+      </c>
+      <c r="T38">
+        <v>1.929074462222704</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.08920721102318746</v>
+      </c>
+      <c r="W38">
+        <v>0.2174973180076629</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.3716967125966144</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.4338584038381453</v>
+      </c>
+      <c r="C39">
+        <v>2.134633844644004</v>
+      </c>
+      <c r="D39">
+        <v>3.732133844644004</v>
+      </c>
+      <c r="E39">
+        <v>1.5795</v>
+      </c>
+      <c r="F39">
+        <v>1.6095</v>
+      </c>
+      <c r="G39">
+        <v>0.012</v>
+      </c>
+      <c r="H39">
+        <v>4.32</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0.154</v>
+      </c>
+      <c r="K39">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L39">
+        <v>0.139</v>
+      </c>
+      <c r="M39">
+        <v>0.3843486</v>
+      </c>
+      <c r="N39">
+        <v>-0.2453486</v>
+      </c>
+      <c r="O39">
+        <v>-0.058883664</v>
+      </c>
+      <c r="P39">
+        <v>-0.186464936</v>
+      </c>
+      <c r="Q39">
+        <v>-0.171464936</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.5605894751672804</v>
+      </c>
+      <c r="T39">
+        <v>1.959694691781795</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.08679620531985807</v>
+      </c>
+      <c r="W39">
+        <v>0.2180730661696179</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.3616508554994086</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.4358584038381453</v>
+      </c>
+      <c r="C40">
+        <v>2.072334928370894</v>
+      </c>
+      <c r="D40">
+        <v>3.713334928370894</v>
+      </c>
+      <c r="E40">
+        <v>1.623</v>
+      </c>
+      <c r="F40">
+        <v>1.653</v>
+      </c>
+      <c r="G40">
+        <v>0.012</v>
+      </c>
+      <c r="H40">
+        <v>4.32</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0.154</v>
+      </c>
+      <c r="K40">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L40">
+        <v>0.139</v>
+      </c>
+      <c r="M40">
+        <v>0.3947364000000001</v>
+      </c>
+      <c r="N40">
+        <v>-0.2557364000000001</v>
+      </c>
+      <c r="O40">
+        <v>-0.06137673600000002</v>
+      </c>
+      <c r="P40">
+        <v>-0.1943596640000001</v>
+      </c>
+      <c r="Q40">
+        <v>-0.1793596640000001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.5690054344441722</v>
+      </c>
+      <c r="T40">
+        <v>1.991302670681501</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.08451209465354599</v>
+      </c>
+      <c r="W40">
+        <v>0.2186185117967332</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.3521337277231084</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.4378584038381453</v>
+      </c>
+      <c r="C41">
+        <v>2.010224444829356</v>
+      </c>
+      <c r="D41">
+        <v>3.694724444829357</v>
+      </c>
+      <c r="E41">
+        <v>1.6665</v>
+      </c>
+      <c r="F41">
+        <v>1.6965</v>
+      </c>
+      <c r="G41">
+        <v>0.012</v>
+      </c>
+      <c r="H41">
+        <v>4.32</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0.154</v>
+      </c>
+      <c r="K41">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L41">
+        <v>0.139</v>
+      </c>
+      <c r="M41">
+        <v>0.4051242000000001</v>
+      </c>
+      <c r="N41">
+        <v>-0.2661242000000001</v>
+      </c>
+      <c r="O41">
+        <v>-0.06386980800000001</v>
+      </c>
+      <c r="P41">
+        <v>-0.2022543920000001</v>
+      </c>
+      <c r="Q41">
+        <v>-0.1872543920000001</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.5776973268121093</v>
+      </c>
+      <c r="T41">
+        <v>2.023946976758247</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.08234511786755765</v>
+      </c>
+      <c r="W41">
+        <v>0.2191359858532272</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.3431046577814901</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.4398584038381453</v>
+      </c>
+      <c r="C42">
+        <v>1.948299574987604</v>
+      </c>
+      <c r="D42">
+        <v>3.676299574987604</v>
+      </c>
+      <c r="E42">
+        <v>1.71</v>
+      </c>
+      <c r="F42">
+        <v>1.74</v>
+      </c>
+      <c r="G42">
+        <v>0.012</v>
+      </c>
+      <c r="H42">
+        <v>4.32</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0.154</v>
+      </c>
+      <c r="K42">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L42">
+        <v>0.139</v>
+      </c>
+      <c r="M42">
+        <v>0.415512</v>
+      </c>
+      <c r="N42">
+        <v>-0.276512</v>
+      </c>
+      <c r="O42">
+        <v>-0.06636288000000001</v>
+      </c>
+      <c r="P42">
+        <v>-0.21014912</v>
+      </c>
+      <c r="Q42">
+        <v>-0.19514912</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.5866789489256445</v>
+      </c>
+      <c r="T42">
+        <v>2.057679426370885</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.0802864899208687</v>
+      </c>
+      <c r="W42">
+        <v>0.2196275862068966</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.334527041336953</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.4418584038381453</v>
+      </c>
+      <c r="C43">
+        <v>1.886557555766668</v>
+      </c>
+      <c r="D43">
+        <v>3.658057555766669</v>
+      </c>
+      <c r="E43">
+        <v>1.7535</v>
+      </c>
+      <c r="F43">
+        <v>1.7835</v>
+      </c>
+      <c r="G43">
+        <v>0.012</v>
+      </c>
+      <c r="H43">
+        <v>4.32</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0.154</v>
+      </c>
+      <c r="K43">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L43">
+        <v>0.139</v>
+      </c>
+      <c r="M43">
+        <v>0.4258998000000001</v>
+      </c>
+      <c r="N43">
+        <v>-0.2868998000000001</v>
+      </c>
+      <c r="O43">
+        <v>-0.06885595200000003</v>
+      </c>
+      <c r="P43">
+        <v>-0.2180438480000001</v>
+      </c>
+      <c r="Q43">
+        <v>-0.2030438480000001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.5959650328057402</v>
+      </c>
+      <c r="T43">
+        <v>2.092555348851747</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.07832828284962799</v>
+      </c>
+      <c r="W43">
+        <v>0.2200952060555088</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.3263678452067833</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.4438584038381453</v>
+      </c>
+      <c r="C44">
+        <v>1.824995678659048</v>
+      </c>
+      <c r="D44">
+        <v>3.639995678659048</v>
+      </c>
+      <c r="E44">
+        <v>1.797</v>
+      </c>
+      <c r="F44">
+        <v>1.827</v>
+      </c>
+      <c r="G44">
+        <v>0.012</v>
+      </c>
+      <c r="H44">
+        <v>4.32</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0.154</v>
+      </c>
+      <c r="K44">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L44">
+        <v>0.139</v>
+      </c>
+      <c r="M44">
+        <v>0.4362876000000001</v>
+      </c>
+      <c r="N44">
+        <v>-0.2972876</v>
+      </c>
+      <c r="O44">
+        <v>-0.07134902400000001</v>
+      </c>
+      <c r="P44">
+        <v>-0.225938576</v>
+      </c>
+      <c r="Q44">
+        <v>-0.210938576</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.6055713264748046</v>
+      </c>
+      <c r="T44">
+        <v>2.128633889349191</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.07646332373416066</v>
+      </c>
+      <c r="W44">
+        <v>0.2205405582922824</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.3185971822256695</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.4458584038381454</v>
+      </c>
+      <c r="C45">
+        <v>1.763611288388081</v>
+      </c>
+      <c r="D45">
+        <v>3.622111288388081</v>
+      </c>
+      <c r="E45">
+        <v>1.8405</v>
+      </c>
+      <c r="F45">
+        <v>1.8705</v>
+      </c>
+      <c r="G45">
+        <v>0.012</v>
+      </c>
+      <c r="H45">
+        <v>4.32</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0.154</v>
+      </c>
+      <c r="K45">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L45">
+        <v>0.139</v>
+      </c>
+      <c r="M45">
+        <v>0.4466754000000001</v>
+      </c>
+      <c r="N45">
+        <v>-0.3076754000000001</v>
+      </c>
+      <c r="O45">
+        <v>-0.07384209600000002</v>
+      </c>
+      <c r="P45">
+        <v>-0.2338333040000001</v>
+      </c>
+      <c r="Q45">
+        <v>-0.2188333040000001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.6155146830796259</v>
+      </c>
+      <c r="T45">
+        <v>2.1659783435483</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.07468510690313367</v>
+      </c>
+      <c r="W45">
+        <v>0.2209651964715317</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.3111879454297236</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.4478584038381454</v>
+      </c>
+      <c r="C46">
+        <v>1.702401781606642</v>
+      </c>
+      <c r="D46">
+        <v>3.604401781606642</v>
+      </c>
+      <c r="E46">
+        <v>1.884</v>
+      </c>
+      <c r="F46">
+        <v>1.914</v>
+      </c>
+      <c r="G46">
+        <v>0.012</v>
+      </c>
+      <c r="H46">
+        <v>4.32</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0.154</v>
+      </c>
+      <c r="K46">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L46">
+        <v>0.139</v>
+      </c>
+      <c r="M46">
+        <v>0.4570632000000001</v>
+      </c>
+      <c r="N46">
+        <v>-0.3180632</v>
+      </c>
+      <c r="O46">
+        <v>-0.07633516800000001</v>
+      </c>
+      <c r="P46">
+        <v>-0.241728032</v>
+      </c>
+      <c r="Q46">
+        <v>-0.2267280320000001</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.6258131595631906</v>
+      </c>
+      <c r="T46">
+        <v>2.204656528254519</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.07298771810988064</v>
+      </c>
+      <c r="W46">
+        <v>0.2213705329153605</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.3041154921245027</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.4498584038381453</v>
+      </c>
+      <c r="C47">
+        <v>1.641364605633829</v>
+      </c>
+      <c r="D47">
+        <v>3.58686460563383</v>
+      </c>
+      <c r="E47">
+        <v>1.9275</v>
+      </c>
+      <c r="F47">
+        <v>1.9575</v>
+      </c>
+      <c r="G47">
+        <v>0.012</v>
+      </c>
+      <c r="H47">
+        <v>4.32</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0.154</v>
+      </c>
+      <c r="K47">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L47">
+        <v>0.139</v>
+      </c>
+      <c r="M47">
+        <v>0.4674510000000001</v>
+      </c>
+      <c r="N47">
+        <v>-0.328451</v>
+      </c>
+      <c r="O47">
+        <v>-0.07882824000000001</v>
+      </c>
+      <c r="P47">
+        <v>-0.2496227600000001</v>
+      </c>
+      <c r="Q47">
+        <v>-0.2346227600000001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.6364861261007031</v>
+      </c>
+      <c r="T47">
+        <v>2.244741192404601</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.07136576881854996</v>
+      </c>
+      <c r="W47">
+        <v>0.2217578544061303</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.2973573700772915</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.4518584038381454</v>
+      </c>
+      <c r="C48">
+        <v>1.580497257228351</v>
+      </c>
+      <c r="D48">
+        <v>3.569497257228352</v>
+      </c>
+      <c r="E48">
+        <v>1.971</v>
+      </c>
+      <c r="F48">
+        <v>2.001</v>
+      </c>
+      <c r="G48">
+        <v>0.012</v>
+      </c>
+      <c r="H48">
+        <v>4.32</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0.154</v>
+      </c>
+      <c r="K48">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L48">
+        <v>0.139</v>
+      </c>
+      <c r="M48">
+        <v>0.4778388000000001</v>
+      </c>
+      <c r="N48">
+        <v>-0.3388388000000001</v>
+      </c>
+      <c r="O48">
+        <v>-0.08132131200000002</v>
+      </c>
+      <c r="P48">
+        <v>-0.2575174880000001</v>
+      </c>
+      <c r="Q48">
+        <v>-0.2425174880000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.6475543876951606</v>
+      </c>
+      <c r="T48">
+        <v>2.286310473745427</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.06981433906162496</v>
+      </c>
+      <c r="W48">
+        <v>0.222128335832084</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.2908930794234373</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.4538584038381454</v>
+      </c>
+      <c r="C49">
+        <v>1.519797281397382</v>
+      </c>
+      <c r="D49">
+        <v>3.552297281397383</v>
+      </c>
+      <c r="E49">
+        <v>2.0145</v>
+      </c>
+      <c r="F49">
+        <v>2.0445</v>
+      </c>
+      <c r="G49">
+        <v>0.012</v>
+      </c>
+      <c r="H49">
+        <v>4.32</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0.154</v>
+      </c>
+      <c r="K49">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L49">
+        <v>0.139</v>
+      </c>
+      <c r="M49">
+        <v>0.4882266000000001</v>
+      </c>
+      <c r="N49">
+        <v>-0.3492266000000001</v>
+      </c>
+      <c r="O49">
+        <v>-0.08381438400000001</v>
+      </c>
+      <c r="P49">
+        <v>-0.265412216</v>
+      </c>
+      <c r="Q49">
+        <v>-0.2504122160000001</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.6590403195384655</v>
+      </c>
+      <c r="T49">
+        <v>2.329448407212322</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.06832892759222868</v>
+      </c>
+      <c r="W49">
+        <v>0.2224830520909758</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.2847038649676196</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.4558584038381452</v>
+      </c>
+      <c r="C50">
+        <v>1.459262270239685</v>
+      </c>
+      <c r="D50">
+        <v>3.535262270239685</v>
+      </c>
+      <c r="E50">
+        <v>2.058</v>
+      </c>
+      <c r="F50">
+        <v>2.088</v>
+      </c>
+      <c r="G50">
+        <v>0.012</v>
+      </c>
+      <c r="H50">
+        <v>4.32</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0.154</v>
+      </c>
+      <c r="K50">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L50">
+        <v>0.139</v>
+      </c>
+      <c r="M50">
+        <v>0.4986144000000001</v>
+      </c>
+      <c r="N50">
+        <v>-0.3596144000000001</v>
+      </c>
+      <c r="O50">
+        <v>-0.086307456</v>
+      </c>
+      <c r="P50">
+        <v>-0.2733069440000001</v>
+      </c>
+      <c r="Q50">
+        <v>-0.2583069440000001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.6709680179911282</v>
+      </c>
+      <c r="T50">
+        <v>2.374245491966405</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.0669054082673906</v>
+      </c>
+      <c r="W50">
+        <v>0.2228229885057471</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.2787725344474608</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.4578584038381453</v>
+      </c>
+      <c r="C51">
+        <v>1.398889861821858</v>
+      </c>
+      <c r="D51">
+        <v>3.518389861821859</v>
+      </c>
+      <c r="E51">
+        <v>2.101500000000001</v>
+      </c>
+      <c r="F51">
+        <v>2.1315</v>
+      </c>
+      <c r="G51">
+        <v>0.012</v>
+      </c>
+      <c r="H51">
+        <v>4.32</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0.154</v>
+      </c>
+      <c r="K51">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L51">
+        <v>0.139</v>
+      </c>
+      <c r="M51">
+        <v>0.5090022000000001</v>
+      </c>
+      <c r="N51">
+        <v>-0.3700022000000001</v>
+      </c>
+      <c r="O51">
+        <v>-0.08880052800000002</v>
+      </c>
+      <c r="P51">
+        <v>-0.281201672</v>
+      </c>
+      <c r="Q51">
+        <v>-0.266201672</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.6833634693242876</v>
+      </c>
+      <c r="T51">
+        <v>2.420799325142217</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.06553999177213772</v>
+      </c>
+      <c r="W51">
+        <v>0.2231490499648135</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.2730832990505738</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.4598584038381453</v>
+      </c>
+      <c r="C52">
+        <v>1.338677739086627</v>
+      </c>
+      <c r="D52">
+        <v>3.501677739086627</v>
+      </c>
+      <c r="E52">
+        <v>2.145</v>
+      </c>
+      <c r="F52">
+        <v>2.175</v>
+      </c>
+      <c r="G52">
+        <v>0.012</v>
+      </c>
+      <c r="H52">
+        <v>4.32</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0.154</v>
+      </c>
+      <c r="K52">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L52">
+        <v>0.139</v>
+      </c>
+      <c r="M52">
+        <v>0.5193900000000001</v>
+      </c>
+      <c r="N52">
+        <v>-0.3803900000000001</v>
+      </c>
+      <c r="O52">
+        <v>-0.09129360000000003</v>
+      </c>
+      <c r="P52">
+        <v>-0.2890964000000001</v>
+      </c>
+      <c r="Q52">
+        <v>-0.2740964000000001</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.6962547387107734</v>
+      </c>
+      <c r="T52">
+        <v>2.469215311645061</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.06422919193669496</v>
+      </c>
+      <c r="W52">
+        <v>0.2234620689655173</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.2676216330695623</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.4618584038381452</v>
+      </c>
+      <c r="C53">
+        <v>1.278623628792077</v>
+      </c>
+      <c r="D53">
+        <v>3.485123628792077</v>
+      </c>
+      <c r="E53">
+        <v>2.1885</v>
+      </c>
+      <c r="F53">
+        <v>2.2185</v>
+      </c>
+      <c r="G53">
+        <v>0.012</v>
+      </c>
+      <c r="H53">
+        <v>4.32</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0.154</v>
+      </c>
+      <c r="K53">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L53">
+        <v>0.139</v>
+      </c>
+      <c r="M53">
+        <v>0.5297778000000001</v>
+      </c>
+      <c r="N53">
+        <v>-0.3907778000000001</v>
+      </c>
+      <c r="O53">
+        <v>-0.09378667200000002</v>
+      </c>
+      <c r="P53">
+        <v>-0.296991128</v>
+      </c>
+      <c r="Q53">
+        <v>-0.281991128</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.7096721823579319</v>
+      </c>
+      <c r="T53">
+        <v>2.519607460862308</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.06296979601636761</v>
+      </c>
+      <c r="W53">
+        <v>0.2237628127112914</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.2623741500681984</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.4638584038381454</v>
+      </c>
+      <c r="C54">
+        <v>1.218725300480848</v>
+      </c>
+      <c r="D54">
+        <v>3.468725300480849</v>
+      </c>
+      <c r="E54">
+        <v>2.232000000000001</v>
+      </c>
+      <c r="F54">
+        <v>2.262</v>
+      </c>
+      <c r="G54">
+        <v>0.012</v>
+      </c>
+      <c r="H54">
+        <v>4.32</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0.154</v>
+      </c>
+      <c r="K54">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L54">
+        <v>0.139</v>
+      </c>
+      <c r="M54">
+        <v>0.5401656000000001</v>
+      </c>
+      <c r="N54">
+        <v>-0.4011656000000001</v>
+      </c>
+      <c r="O54">
+        <v>-0.09627974400000003</v>
+      </c>
+      <c r="P54">
+        <v>-0.3048858560000001</v>
+      </c>
+      <c r="Q54">
+        <v>-0.2898858560000001</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.7236486861570557</v>
+      </c>
+      <c r="T54">
+        <v>2.572099282963606</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.06175883840066823</v>
+      </c>
+      <c r="W54">
+        <v>0.2240519893899204</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.2573284933361176</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.4658584038381454</v>
+      </c>
+      <c r="C55">
+        <v>1.1589805654783</v>
+      </c>
+      <c r="D55">
+        <v>3.452480565478301</v>
+      </c>
+      <c r="E55">
+        <v>2.275500000000001</v>
+      </c>
+      <c r="F55">
+        <v>2.3055</v>
+      </c>
+      <c r="G55">
+        <v>0.012</v>
+      </c>
+      <c r="H55">
+        <v>4.32</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0.154</v>
+      </c>
+      <c r="K55">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L55">
+        <v>0.139</v>
+      </c>
+      <c r="M55">
+        <v>0.5505534000000001</v>
+      </c>
+      <c r="N55">
+        <v>-0.4115534000000001</v>
+      </c>
+      <c r="O55">
+        <v>-0.09877281600000001</v>
+      </c>
+      <c r="P55">
+        <v>-0.3127805840000001</v>
+      </c>
+      <c r="Q55">
+        <v>-0.2977805840000001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.7382199347986951</v>
+      </c>
+      <c r="T55">
+        <v>2.626824799622406</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.06059357729876883</v>
+      </c>
+      <c r="W55">
+        <v>0.224330253741054</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.2524732387448702</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.4678584038381453</v>
+      </c>
+      <c r="C56">
+        <v>1.099387275918679</v>
+      </c>
+      <c r="D56">
+        <v>3.43638727591868</v>
+      </c>
+      <c r="E56">
+        <v>2.319000000000001</v>
+      </c>
+      <c r="F56">
+        <v>2.349000000000001</v>
+      </c>
+      <c r="G56">
+        <v>0.012</v>
+      </c>
+      <c r="H56">
+        <v>4.32</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0.154</v>
+      </c>
+      <c r="K56">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L56">
+        <v>0.139</v>
+      </c>
+      <c r="M56">
+        <v>0.5609412000000001</v>
+      </c>
+      <c r="N56">
+        <v>-0.4219412000000001</v>
+      </c>
+      <c r="O56">
+        <v>-0.101265888</v>
+      </c>
+      <c r="P56">
+        <v>-0.3206753120000001</v>
+      </c>
+      <c r="Q56">
+        <v>-0.3056753120000001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.753424715989971</v>
+      </c>
+      <c r="T56">
+        <v>2.683929686570719</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.0594714740154583</v>
+      </c>
+      <c r="W56">
+        <v>0.2245982120051086</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.2477978083977429</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.4698584038381453</v>
+      </c>
+      <c r="C57">
+        <v>1.039943323798404</v>
+      </c>
+      <c r="D57">
+        <v>3.420443323798405</v>
+      </c>
+      <c r="E57">
+        <v>2.362500000000001</v>
+      </c>
+      <c r="F57">
+        <v>2.392500000000001</v>
+      </c>
+      <c r="G57">
+        <v>0.012</v>
+      </c>
+      <c r="H57">
+        <v>4.32</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0.154</v>
+      </c>
+      <c r="K57">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L57">
+        <v>0.139</v>
+      </c>
+      <c r="M57">
+        <v>0.5713290000000002</v>
+      </c>
+      <c r="N57">
+        <v>-0.4323290000000002</v>
+      </c>
+      <c r="O57">
+        <v>-0.10375896</v>
+      </c>
+      <c r="P57">
+        <v>-0.3285700400000001</v>
+      </c>
+      <c r="Q57">
+        <v>-0.3135700400000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.7693052652341927</v>
+      </c>
+      <c r="T57">
+        <v>2.743572568494513</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.0583901744879045</v>
+      </c>
+      <c r="W57">
+        <v>0.2248564263322884</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.2432923936996021</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.4718584038381454</v>
+      </c>
+      <c r="C58">
+        <v>0.9806466400555944</v>
+      </c>
+      <c r="D58">
+        <v>3.404646640055595</v>
+      </c>
+      <c r="E58">
+        <v>2.406000000000001</v>
+      </c>
+      <c r="F58">
+        <v>2.436</v>
+      </c>
+      <c r="G58">
+        <v>0.012</v>
+      </c>
+      <c r="H58">
+        <v>4.32</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0.154</v>
+      </c>
+      <c r="K58">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L58">
+        <v>0.139</v>
+      </c>
+      <c r="M58">
+        <v>0.5817168000000001</v>
+      </c>
+      <c r="N58">
+        <v>-0.4427168000000001</v>
+      </c>
+      <c r="O58">
+        <v>-0.106252032</v>
+      </c>
+      <c r="P58">
+        <v>-0.3364647680000001</v>
+      </c>
+      <c r="Q58">
+        <v>-0.3214647680000001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.785907657625879</v>
+      </c>
+      <c r="T58">
+        <v>2.805926490505752</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.05734749280062049</v>
+      </c>
+      <c r="W58">
+        <v>0.2251054187192119</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.238947886669252</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.4738584038381454</v>
+      </c>
+      <c r="C59">
+        <v>0.9214951936749736</v>
+      </c>
+      <c r="D59">
+        <v>3.388995193674974</v>
+      </c>
+      <c r="E59">
+        <v>2.449500000000001</v>
+      </c>
+      <c r="F59">
+        <v>2.479500000000001</v>
+      </c>
+      <c r="G59">
+        <v>0.012</v>
+      </c>
+      <c r="H59">
+        <v>4.32</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0.154</v>
+      </c>
+      <c r="K59">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L59">
+        <v>0.139</v>
+      </c>
+      <c r="M59">
+        <v>0.5921046000000002</v>
+      </c>
+      <c r="N59">
+        <v>-0.4531046000000002</v>
+      </c>
+      <c r="O59">
+        <v>-0.108745104</v>
+      </c>
+      <c r="P59">
+        <v>-0.3443594960000002</v>
+      </c>
+      <c r="Q59">
+        <v>-0.3293594960000001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.803282254314853</v>
+      </c>
+      <c r="T59">
+        <v>2.871180594936118</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.05634139643569733</v>
+      </c>
+      <c r="W59">
+        <v>0.2253456745311555</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.2347558184820722</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.4758584038381453</v>
+      </c>
+      <c r="C60">
+        <v>0.862486990817354</v>
+      </c>
+      <c r="D60">
+        <v>3.373486990817354</v>
+      </c>
+      <c r="E60">
+        <v>2.493</v>
+      </c>
+      <c r="F60">
+        <v>2.523</v>
+      </c>
+      <c r="G60">
+        <v>0.012</v>
+      </c>
+      <c r="H60">
+        <v>4.32</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0.154</v>
+      </c>
+      <c r="K60">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L60">
+        <v>0.139</v>
+      </c>
+      <c r="M60">
+        <v>0.6024924</v>
+      </c>
+      <c r="N60">
+        <v>-0.4634924</v>
+      </c>
+      <c r="O60">
+        <v>-0.111238176</v>
+      </c>
+      <c r="P60">
+        <v>-0.352254224</v>
+      </c>
+      <c r="Q60">
+        <v>-0.337254224</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.8214842127509205</v>
+      </c>
+      <c r="T60">
+        <v>2.939542037672692</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.05536999304887497</v>
+      </c>
+      <c r="W60">
+        <v>0.2255776456599287</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.2307083043703124</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.4778584038381453</v>
+      </c>
+      <c r="C61">
+        <v>0.8036200739729114</v>
+      </c>
+      <c r="D61">
+        <v>3.358120073972911</v>
+      </c>
+      <c r="E61">
+        <v>2.5365</v>
+      </c>
+      <c r="F61">
+        <v>2.5665</v>
+      </c>
+      <c r="G61">
+        <v>0.012</v>
+      </c>
+      <c r="H61">
+        <v>4.32</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0.154</v>
+      </c>
+      <c r="K61">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L61">
+        <v>0.139</v>
+      </c>
+      <c r="M61">
+        <v>0.6128802</v>
+      </c>
+      <c r="N61">
+        <v>-0.4738802</v>
+      </c>
+      <c r="O61">
+        <v>-0.113731248</v>
+      </c>
+      <c r="P61">
+        <v>-0.360148952</v>
+      </c>
+      <c r="Q61">
+        <v>-0.345148952</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.8405740715985039</v>
+      </c>
+      <c r="T61">
+        <v>3.011238184933001</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.05443151859041948</v>
+      </c>
+      <c r="W61">
+        <v>0.2258017533606078</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.2267979941267478</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.4798584038381453</v>
+      </c>
+      <c r="C62">
+        <v>0.744892521137503</v>
+      </c>
+      <c r="D62">
+        <v>3.342892521137503</v>
+      </c>
+      <c r="E62">
+        <v>2.580000000000001</v>
+      </c>
+      <c r="F62">
+        <v>2.61</v>
+      </c>
+      <c r="G62">
+        <v>0.012</v>
+      </c>
+      <c r="H62">
+        <v>4.32</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0.154</v>
+      </c>
+      <c r="K62">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L62">
+        <v>0.139</v>
+      </c>
+      <c r="M62">
+        <v>0.6232680000000002</v>
+      </c>
+      <c r="N62">
+        <v>-0.4842680000000001</v>
+      </c>
+      <c r="O62">
+        <v>-0.11622432</v>
+      </c>
+      <c r="P62">
+        <v>-0.3680436800000001</v>
+      </c>
+      <c r="Q62">
+        <v>-0.3530436800000001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.8606184233884666</v>
+      </c>
+      <c r="T62">
+        <v>3.086519139556327</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.05352432661391246</v>
+      </c>
+      <c r="W62">
+        <v>0.2260183908045977</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.2230180275579686</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.4818584038381453</v>
+      </c>
+      <c r="C63">
+        <v>0.6863024450112927</v>
+      </c>
+      <c r="D63">
+        <v>3.327802445011293</v>
+      </c>
+      <c r="E63">
+        <v>2.6235</v>
+      </c>
+      <c r="F63">
+        <v>2.6535</v>
+      </c>
+      <c r="G63">
+        <v>0.012</v>
+      </c>
+      <c r="H63">
+        <v>4.32</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0.154</v>
+      </c>
+      <c r="K63">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L63">
+        <v>0.139</v>
+      </c>
+      <c r="M63">
+        <v>0.6336558000000001</v>
+      </c>
+      <c r="N63">
+        <v>-0.4946558000000001</v>
+      </c>
+      <c r="O63">
+        <v>-0.118717392</v>
+      </c>
+      <c r="P63">
+        <v>-0.3759384080000001</v>
+      </c>
+      <c r="Q63">
+        <v>-0.3609384080000001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.8816906906548376</v>
+      </c>
+      <c r="T63">
+        <v>3.165660655955207</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.05264687863663522</v>
+      </c>
+      <c r="W63">
+        <v>0.2262279253815715</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.2193619943193134</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.4838584038381453</v>
+      </c>
+      <c r="C64">
+        <v>0.6278479922189724</v>
+      </c>
+      <c r="D64">
+        <v>3.312847992218973</v>
+      </c>
+      <c r="E64">
+        <v>2.667000000000001</v>
+      </c>
+      <c r="F64">
+        <v>2.697000000000001</v>
+      </c>
+      <c r="G64">
+        <v>0.012</v>
+      </c>
+      <c r="H64">
+        <v>4.32</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0.154</v>
+      </c>
+      <c r="K64">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L64">
+        <v>0.139</v>
+      </c>
+      <c r="M64">
+        <v>0.6440436000000002</v>
+      </c>
+      <c r="N64">
+        <v>-0.5050436000000001</v>
+      </c>
+      <c r="O64">
+        <v>-0.121210464</v>
+      </c>
+      <c r="P64">
+        <v>-0.3838331360000001</v>
+      </c>
+      <c r="Q64">
+        <v>-0.3688331360000001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.9038720246194387</v>
+      </c>
+      <c r="T64">
+        <v>3.248967515322449</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.05179773543281851</v>
+      </c>
+      <c r="W64">
+        <v>0.2264307007786429</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.2158238976367438</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.4858584038381453</v>
+      </c>
+      <c r="C65">
+        <v>0.5695273425509342</v>
+      </c>
+      <c r="D65">
+        <v>3.298027342550935</v>
+      </c>
+      <c r="E65">
+        <v>2.710500000000001</v>
+      </c>
+      <c r="F65">
+        <v>2.7405</v>
+      </c>
+      <c r="G65">
+        <v>0.012</v>
+      </c>
+      <c r="H65">
+        <v>4.32</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0.154</v>
+      </c>
+      <c r="K65">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L65">
+        <v>0.139</v>
+      </c>
+      <c r="M65">
+        <v>0.6544314000000001</v>
+      </c>
+      <c r="N65">
+        <v>-0.5154314000000001</v>
+      </c>
+      <c r="O65">
+        <v>-0.123703536</v>
+      </c>
+      <c r="P65">
+        <v>-0.3917278640000001</v>
+      </c>
+      <c r="Q65">
+        <v>-0.3767278640000001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.9272523496091531</v>
+      </c>
+      <c r="T65">
+        <v>3.336777448169002</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.05097554915610712</v>
+      </c>
+      <c r="W65">
+        <v>0.2266270388615216</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.2123981214837797</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.4878584038381453</v>
+      </c>
+      <c r="C66">
+        <v>0.5113387082246978</v>
+      </c>
+      <c r="D66">
+        <v>3.283338708224698</v>
+      </c>
+      <c r="E66">
+        <v>2.754</v>
+      </c>
+      <c r="F66">
+        <v>2.784</v>
+      </c>
+      <c r="G66">
+        <v>0.012</v>
+      </c>
+      <c r="H66">
+        <v>4.32</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0.154</v>
+      </c>
+      <c r="K66">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L66">
+        <v>0.139</v>
+      </c>
+      <c r="M66">
+        <v>0.6648192000000001</v>
+      </c>
+      <c r="N66">
+        <v>-0.5258192</v>
+      </c>
+      <c r="O66">
+        <v>-0.126196608</v>
+      </c>
+      <c r="P66">
+        <v>-0.3996225920000001</v>
+      </c>
+      <c r="Q66">
+        <v>-0.384622592</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.9519315815427407</v>
+      </c>
+      <c r="T66">
+        <v>3.429465710618141</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.05017905620054294</v>
+      </c>
+      <c r="W66">
+        <v>0.2268172413793104</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2090794008355956</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.4898584038381453</v>
+      </c>
+      <c r="C67">
+        <v>0.4532803331660085</v>
+      </c>
+      <c r="D67">
+        <v>3.268780333166009</v>
+      </c>
+      <c r="E67">
+        <v>2.797500000000001</v>
+      </c>
+      <c r="F67">
+        <v>2.827500000000001</v>
+      </c>
+      <c r="G67">
+        <v>0.012</v>
+      </c>
+      <c r="H67">
+        <v>4.32</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0.154</v>
+      </c>
+      <c r="K67">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L67">
+        <v>0.139</v>
+      </c>
+      <c r="M67">
+        <v>0.6752070000000002</v>
+      </c>
+      <c r="N67">
+        <v>-0.5362070000000002</v>
+      </c>
+      <c r="O67">
+        <v>-0.1286896800000001</v>
+      </c>
+      <c r="P67">
+        <v>-0.4075173200000002</v>
+      </c>
+      <c r="Q67">
+        <v>-0.3925173200000002</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.9780210553011048</v>
+      </c>
+      <c r="T67">
+        <v>3.527450445207231</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.04940707072053458</v>
+      </c>
+      <c r="W67">
+        <v>0.2270015915119363</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.2058627946688941</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.4918584038381454</v>
+      </c>
+      <c r="C68">
+        <v>0.3953504923089608</v>
+      </c>
+      <c r="D68">
+        <v>3.254350492308961</v>
+      </c>
+      <c r="E68">
+        <v>2.841000000000001</v>
+      </c>
+      <c r="F68">
+        <v>2.871</v>
+      </c>
+      <c r="G68">
+        <v>0.012</v>
+      </c>
+      <c r="H68">
+        <v>4.32</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0.154</v>
+      </c>
+      <c r="K68">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L68">
+        <v>0.139</v>
+      </c>
+      <c r="M68">
+        <v>0.6855948000000002</v>
+      </c>
+      <c r="N68">
+        <v>-0.5465948000000002</v>
+      </c>
+      <c r="O68">
+        <v>-0.131182752</v>
+      </c>
+      <c r="P68">
+        <v>-0.4154120480000001</v>
+      </c>
+      <c r="Q68">
+        <v>-0.4004120480000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>1.005645203986432</v>
+      </c>
+      <c r="T68">
+        <v>3.631198987713326</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.04865847873992042</v>
+      </c>
+      <c r="W68">
+        <v>0.227180355276907</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.2027436614163352</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.4938584038381454</v>
+      </c>
+      <c r="C69">
+        <v>0.3375474909145888</v>
+      </c>
+      <c r="D69">
+        <v>3.240047490914589</v>
+      </c>
+      <c r="E69">
+        <v>2.884500000000001</v>
+      </c>
+      <c r="F69">
+        <v>2.9145</v>
+      </c>
+      <c r="G69">
+        <v>0.012</v>
+      </c>
+      <c r="H69">
+        <v>4.32</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0.154</v>
+      </c>
+      <c r="K69">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L69">
+        <v>0.139</v>
+      </c>
+      <c r="M69">
+        <v>0.6959826000000001</v>
+      </c>
+      <c r="N69">
+        <v>-0.5569826000000001</v>
+      </c>
+      <c r="O69">
+        <v>-0.133675824</v>
+      </c>
+      <c r="P69">
+        <v>-0.4233067760000001</v>
+      </c>
+      <c r="Q69">
+        <v>-0.4083067760000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>1.034943543501172</v>
+      </c>
+      <c r="T69">
+        <v>3.741235320674336</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.04793223278857833</v>
+      </c>
+      <c r="W69">
+        <v>0.2273537828100875</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1997176366190764</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.4958584038381453</v>
+      </c>
+      <c r="C70">
+        <v>0.2798696639073337</v>
+      </c>
+      <c r="D70">
+        <v>3.225869663907334</v>
+      </c>
+      <c r="E70">
+        <v>2.928000000000001</v>
+      </c>
+      <c r="F70">
+        <v>2.958000000000001</v>
+      </c>
+      <c r="G70">
+        <v>0.012</v>
+      </c>
+      <c r="H70">
+        <v>4.32</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0.154</v>
+      </c>
+      <c r="K70">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L70">
+        <v>0.139</v>
+      </c>
+      <c r="M70">
+        <v>0.7063704000000002</v>
+      </c>
+      <c r="N70">
+        <v>-0.5673704000000002</v>
+      </c>
+      <c r="O70">
+        <v>-0.136168896</v>
+      </c>
+      <c r="P70">
+        <v>-0.4312015040000001</v>
+      </c>
+      <c r="Q70">
+        <v>-0.4162015040000001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>1.066073029235584</v>
+      </c>
+      <c r="T70">
+        <v>3.858148924445409</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.0472273470122757</v>
+      </c>
+      <c r="W70">
+        <v>0.2275221095334686</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1967806125511488</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.4978584038381453</v>
+      </c>
+      <c r="C71">
+        <v>0.2223153752288733</v>
+      </c>
+      <c r="D71">
+        <v>3.211815375228874</v>
+      </c>
+      <c r="E71">
+        <v>2.971500000000001</v>
+      </c>
+      <c r="F71">
+        <v>3.001500000000001</v>
+      </c>
+      <c r="G71">
+        <v>0.012</v>
+      </c>
+      <c r="H71">
+        <v>4.32</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0.154</v>
+      </c>
+      <c r="K71">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L71">
+        <v>0.139</v>
+      </c>
+      <c r="M71">
+        <v>0.7167582000000001</v>
+      </c>
+      <c r="N71">
+        <v>-0.5777582000000001</v>
+      </c>
+      <c r="O71">
+        <v>-0.138661968</v>
+      </c>
+      <c r="P71">
+        <v>-0.4390962320000001</v>
+      </c>
+      <c r="Q71">
+        <v>-0.4240962320000001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>1.099210868888344</v>
+      </c>
+      <c r="T71">
+        <v>3.982605341363003</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.04654289270774997</v>
+      </c>
+      <c r="W71">
+        <v>0.2276855572213893</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1939287196156249</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.4998584038381453</v>
+      </c>
+      <c r="C72">
+        <v>0.1648830172087541</v>
+      </c>
+      <c r="D72">
+        <v>3.197883017208755</v>
+      </c>
+      <c r="E72">
+        <v>3.015000000000001</v>
+      </c>
+      <c r="F72">
+        <v>3.045000000000001</v>
+      </c>
+      <c r="G72">
+        <v>0.012</v>
+      </c>
+      <c r="H72">
+        <v>4.32</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0.154</v>
+      </c>
+      <c r="K72">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L72">
+        <v>0.139</v>
+      </c>
+      <c r="M72">
+        <v>0.7271460000000002</v>
+      </c>
+      <c r="N72">
+        <v>-0.5881460000000002</v>
+      </c>
+      <c r="O72">
+        <v>-0.14115504</v>
+      </c>
+      <c r="P72">
+        <v>-0.4469909600000002</v>
+      </c>
+      <c r="Q72">
+        <v>-0.4319909600000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>1.134557897851289</v>
+      </c>
+      <c r="T72">
+        <v>4.11535885274177</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.04587799424049639</v>
+      </c>
+      <c r="W72">
+        <v>0.2278443349753695</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1911583093354017</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.5018584038381454</v>
+      </c>
+      <c r="C73">
+        <v>0.1075710099513429</v>
+      </c>
+      <c r="D73">
+        <v>3.184071009951343</v>
+      </c>
+      <c r="E73">
+        <v>3.0585</v>
+      </c>
+      <c r="F73">
+        <v>3.0885</v>
+      </c>
+      <c r="G73">
+        <v>0.012</v>
+      </c>
+      <c r="H73">
+        <v>4.32</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0.154</v>
+      </c>
+      <c r="K73">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L73">
+        <v>0.139</v>
+      </c>
+      <c r="M73">
+        <v>0.7375338000000001</v>
+      </c>
+      <c r="N73">
+        <v>-0.5985338000000001</v>
+      </c>
+      <c r="O73">
+        <v>-0.143648112</v>
+      </c>
+      <c r="P73">
+        <v>-0.4548856880000001</v>
+      </c>
+      <c r="Q73">
+        <v>-0.4398856880000001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>1.172342652949609</v>
+      </c>
+      <c r="T73">
+        <v>4.257267778698382</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.04523182530753166</v>
+      </c>
+      <c r="W73">
+        <v>0.2279986401165615</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.188465938781382</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.5038584038381453</v>
+      </c>
+      <c r="C74">
+        <v>0.05037780073859555</v>
+      </c>
+      <c r="D74">
+        <v>3.170377800738596</v>
+      </c>
+      <c r="E74">
+        <v>3.102</v>
+      </c>
+      <c r="F74">
+        <v>3.132</v>
+      </c>
+      <c r="G74">
+        <v>0.012</v>
+      </c>
+      <c r="H74">
+        <v>4.32</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0.154</v>
+      </c>
+      <c r="K74">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L74">
+        <v>0.139</v>
+      </c>
+      <c r="M74">
+        <v>0.7479216000000001</v>
+      </c>
+      <c r="N74">
+        <v>-0.6089216000000001</v>
+      </c>
+      <c r="O74">
+        <v>-0.146141184</v>
+      </c>
+      <c r="P74">
+        <v>-0.4627804160000001</v>
+      </c>
+      <c r="Q74">
+        <v>-0.4477804160000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>1.212826319126381</v>
+      </c>
+      <c r="T74">
+        <v>4.409313056509037</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.04460360551159373</v>
+      </c>
+      <c r="W74">
+        <v>0.2281486590038314</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1858483562983072</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.5058584038381453</v>
+      </c>
+      <c r="C75">
+        <v>-0.006698136551839706</v>
+      </c>
+      <c r="D75">
+        <v>3.156801863448161</v>
+      </c>
+      <c r="E75">
+        <v>3.145500000000001</v>
+      </c>
+      <c r="F75">
+        <v>3.1755</v>
+      </c>
+      <c r="G75">
+        <v>0.012</v>
+      </c>
+      <c r="H75">
+        <v>4.32</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0.154</v>
+      </c>
+      <c r="K75">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L75">
+        <v>0.139</v>
+      </c>
+      <c r="M75">
+        <v>0.7583094000000001</v>
+      </c>
+      <c r="N75">
+        <v>-0.6193094000000001</v>
+      </c>
+      <c r="O75">
+        <v>-0.148634256</v>
+      </c>
+      <c r="P75">
+        <v>-0.4706751440000001</v>
+      </c>
+      <c r="Q75">
+        <v>-0.4556751440000001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>1.256308775390321</v>
+      </c>
+      <c r="T75">
+        <v>4.572620947490854</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.04399259721691436</v>
+      </c>
+      <c r="W75">
+        <v>0.2282945677846009</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1833024884038098</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.5078584038381453</v>
+      </c>
+      <c r="C76">
+        <v>-0.06365830201361211</v>
+      </c>
+      <c r="D76">
+        <v>3.143341697986388</v>
+      </c>
+      <c r="E76">
+        <v>3.189000000000001</v>
+      </c>
+      <c r="F76">
+        <v>3.219</v>
+      </c>
+      <c r="G76">
+        <v>0.012</v>
+      </c>
+      <c r="H76">
+        <v>4.32</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0.154</v>
+      </c>
+      <c r="K76">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L76">
+        <v>0.139</v>
+      </c>
+      <c r="M76">
+        <v>0.7686972000000001</v>
+      </c>
+      <c r="N76">
+        <v>-0.6296972000000001</v>
+      </c>
+      <c r="O76">
+        <v>-0.151127328</v>
+      </c>
+      <c r="P76">
+        <v>-0.4785698720000001</v>
+      </c>
+      <c r="Q76">
+        <v>-0.4635698720000001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>1.303136035982256</v>
+      </c>
+      <c r="T76">
+        <v>4.74849098393281</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.04339810265992904</v>
+      </c>
+      <c r="W76">
+        <v>0.228436533084809</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1808254277497043</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.5098584038381453</v>
+      </c>
+      <c r="C77">
+        <v>-0.1205041702642351</v>
+      </c>
+      <c r="D77">
+        <v>3.129995829735765</v>
+      </c>
+      <c r="E77">
+        <v>3.2325</v>
+      </c>
+      <c r="F77">
+        <v>3.2625</v>
+      </c>
+      <c r="G77">
+        <v>0.012</v>
+      </c>
+      <c r="H77">
+        <v>4.32</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0.154</v>
+      </c>
+      <c r="K77">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L77">
+        <v>0.139</v>
+      </c>
+      <c r="M77">
+        <v>0.779085</v>
+      </c>
+      <c r="N77">
+        <v>-0.640085</v>
+      </c>
+      <c r="O77">
+        <v>-0.1536204</v>
+      </c>
+      <c r="P77">
+        <v>-0.4864646</v>
+      </c>
+      <c r="Q77">
+        <v>-0.4714646</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>1.353709477421547</v>
+      </c>
+      <c r="T77">
+        <v>4.938430623290123</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.04281946129112998</v>
+      </c>
+      <c r="W77">
+        <v>0.2285747126436782</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1784144220463749</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.5118584038381454</v>
+      </c>
+      <c r="C78">
+        <v>-0.1772371909836261</v>
+      </c>
+      <c r="D78">
+        <v>3.116762809016374</v>
+      </c>
+      <c r="E78">
+        <v>3.276000000000001</v>
+      </c>
+      <c r="F78">
+        <v>3.306</v>
+      </c>
+      <c r="G78">
+        <v>0.012</v>
+      </c>
+      <c r="H78">
+        <v>4.32</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0.154</v>
+      </c>
+      <c r="K78">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L78">
+        <v>0.139</v>
+      </c>
+      <c r="M78">
+        <v>0.7894728000000002</v>
+      </c>
+      <c r="N78">
+        <v>-0.6504728000000002</v>
+      </c>
+      <c r="O78">
+        <v>-0.156113472</v>
+      </c>
+      <c r="P78">
+        <v>-0.4943593280000002</v>
+      </c>
+      <c r="Q78">
+        <v>-0.4793593280000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>1.408497372314111</v>
+      </c>
+      <c r="T78">
+        <v>5.144198565927212</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.042256047326773</v>
+      </c>
+      <c r="W78">
+        <v>0.2287092558983666</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.1760668638615541</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.5138584038381453</v>
+      </c>
+      <c r="C79">
+        <v>-0.2338587894390365</v>
+      </c>
+      <c r="D79">
+        <v>3.103641210560964</v>
+      </c>
+      <c r="E79">
+        <v>3.319500000000001</v>
+      </c>
+      <c r="F79">
+        <v>3.3495</v>
+      </c>
+      <c r="G79">
+        <v>0.012</v>
+      </c>
+      <c r="H79">
+        <v>4.32</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0.154</v>
+      </c>
+      <c r="K79">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L79">
+        <v>0.139</v>
+      </c>
+      <c r="M79">
+        <v>0.7998606000000001</v>
+      </c>
+      <c r="N79">
+        <v>-0.6608606000000001</v>
+      </c>
+      <c r="O79">
+        <v>-0.158606544</v>
+      </c>
+      <c r="P79">
+        <v>-0.5022540560000002</v>
+      </c>
+      <c r="Q79">
+        <v>-0.4872540560000002</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>1.468049431979942</v>
+      </c>
+      <c r="T79">
+        <v>5.367859373141439</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.04170726749136036</v>
+      </c>
+      <c r="W79">
+        <v>0.2288403045230632</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1737802812140016</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.5158584038381453</v>
+      </c>
+      <c r="C80">
+        <v>-0.2903703669967981</v>
+      </c>
+      <c r="D80">
+        <v>3.090629633003203</v>
+      </c>
+      <c r="E80">
+        <v>3.363000000000001</v>
+      </c>
+      <c r="F80">
+        <v>3.393000000000001</v>
+      </c>
+      <c r="G80">
+        <v>0.012</v>
+      </c>
+      <c r="H80">
+        <v>4.32</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0.154</v>
+      </c>
+      <c r="K80">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L80">
+        <v>0.139</v>
+      </c>
+      <c r="M80">
+        <v>0.8102484000000002</v>
+      </c>
+      <c r="N80">
+        <v>-0.6712484000000002</v>
+      </c>
+      <c r="O80">
+        <v>-0.161099616</v>
+      </c>
+      <c r="P80">
+        <v>-0.5101487840000002</v>
+      </c>
+      <c r="Q80">
+        <v>-0.4951487840000002</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>1.533015315251758</v>
+      </c>
+      <c r="T80">
+        <v>5.611852981011504</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.04117255893377882</v>
+      </c>
+      <c r="W80">
+        <v>0.2289679929266136</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1715523288907451</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.5178584038381453</v>
+      </c>
+      <c r="C81">
+        <v>-0.3467733016212255</v>
+      </c>
+      <c r="D81">
+        <v>3.077726698378775</v>
+      </c>
+      <c r="E81">
+        <v>3.406500000000001</v>
+      </c>
+      <c r="F81">
+        <v>3.436500000000001</v>
+      </c>
+      <c r="G81">
+        <v>0.012</v>
+      </c>
+      <c r="H81">
+        <v>4.32</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0.154</v>
+      </c>
+      <c r="K81">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L81">
+        <v>0.139</v>
+      </c>
+      <c r="M81">
+        <v>0.8206362000000001</v>
+      </c>
+      <c r="N81">
+        <v>-0.6816362000000001</v>
+      </c>
+      <c r="O81">
+        <v>-0.163592688</v>
+      </c>
+      <c r="P81">
+        <v>-0.5180435120000001</v>
+      </c>
+      <c r="Q81">
+        <v>-0.5030435120000001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>1.604168425501842</v>
+      </c>
+      <c r="T81">
+        <v>5.879084075345386</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.04065138730170567</v>
+      </c>
+      <c r="W81">
+        <v>0.2290924487123527</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1693807804237737</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.5198584038381453</v>
+      </c>
+      <c r="C82">
+        <v>-0.403068948361093</v>
+      </c>
+      <c r="D82">
+        <v>3.064931051638907</v>
+      </c>
+      <c r="E82">
+        <v>3.450000000000001</v>
+      </c>
+      <c r="F82">
+        <v>3.48</v>
+      </c>
+      <c r="G82">
+        <v>0.012</v>
+      </c>
+      <c r="H82">
+        <v>4.32</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0.154</v>
+      </c>
+      <c r="K82">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L82">
+        <v>0.139</v>
+      </c>
+      <c r="M82">
+        <v>0.8310240000000001</v>
+      </c>
+      <c r="N82">
+        <v>-0.6920240000000001</v>
+      </c>
+      <c r="O82">
+        <v>-0.16608576</v>
+      </c>
+      <c r="P82">
+        <v>-0.5259382400000001</v>
+      </c>
+      <c r="Q82">
+        <v>-0.5109382400000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>1.682436846776934</v>
+      </c>
+      <c r="T82">
+        <v>6.173038279112655</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.04014324496043435</v>
+      </c>
+      <c r="W82">
+        <v>0.2292137931034483</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1672635206684765</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.5218584038381453</v>
+      </c>
+      <c r="C83">
+        <v>-0.4592586398240162</v>
+      </c>
+      <c r="D83">
+        <v>3.052241360175985</v>
+      </c>
+      <c r="E83">
+        <v>3.493500000000001</v>
+      </c>
+      <c r="F83">
+        <v>3.523500000000001</v>
+      </c>
+      <c r="G83">
+        <v>0.012</v>
+      </c>
+      <c r="H83">
+        <v>4.32</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0.154</v>
+      </c>
+      <c r="K83">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L83">
+        <v>0.139</v>
+      </c>
+      <c r="M83">
+        <v>0.8414118000000003</v>
+      </c>
+      <c r="N83">
+        <v>-0.7024118000000003</v>
+      </c>
+      <c r="O83">
+        <v>-0.1685788320000001</v>
+      </c>
+      <c r="P83">
+        <v>-0.5338329680000002</v>
+      </c>
+      <c r="Q83">
+        <v>-0.5188329680000002</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>1.768944049238878</v>
+      </c>
+      <c r="T83">
+        <v>6.4979350306449</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.03964764934363886</v>
+      </c>
+      <c r="W83">
+        <v>0.229332141336739</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1651985389318286</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.5238584038381453</v>
+      </c>
+      <c r="C84">
+        <v>-0.5153436866390977</v>
+      </c>
+      <c r="D84">
+        <v>3.039656313360903</v>
+      </c>
+      <c r="E84">
+        <v>3.537000000000001</v>
+      </c>
+      <c r="F84">
+        <v>3.567000000000001</v>
+      </c>
+      <c r="G84">
+        <v>0.012</v>
+      </c>
+      <c r="H84">
+        <v>4.32</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0.154</v>
+      </c>
+      <c r="K84">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L84">
+        <v>0.139</v>
+      </c>
+      <c r="M84">
+        <v>0.8517996000000002</v>
+      </c>
+      <c r="N84">
+        <v>-0.7127996000000002</v>
+      </c>
+      <c r="O84">
+        <v>-0.1710719040000001</v>
+      </c>
+      <c r="P84">
+        <v>-0.5417276960000001</v>
+      </c>
+      <c r="Q84">
+        <v>-0.5267276960000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>1.865063163085482</v>
+      </c>
+      <c r="T84">
+        <v>6.858931421236284</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.039164141424814</v>
+      </c>
+      <c r="W84">
+        <v>0.2294476030277544</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1631839226033917</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.5258584038381453</v>
+      </c>
+      <c r="C85">
+        <v>-0.5713253779081851</v>
+      </c>
+      <c r="D85">
+        <v>3.027174622091816</v>
+      </c>
+      <c r="E85">
+        <v>3.580500000000001</v>
+      </c>
+      <c r="F85">
+        <v>3.610500000000001</v>
+      </c>
+      <c r="G85">
+        <v>0.012</v>
+      </c>
+      <c r="H85">
+        <v>4.32</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0.154</v>
+      </c>
+      <c r="K85">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L85">
+        <v>0.139</v>
+      </c>
+      <c r="M85">
+        <v>0.8621874000000003</v>
+      </c>
+      <c r="N85">
+        <v>-0.7231874000000003</v>
+      </c>
+      <c r="O85">
+        <v>-0.1735649760000001</v>
+      </c>
+      <c r="P85">
+        <v>-0.5496224240000002</v>
+      </c>
+      <c r="Q85">
+        <v>-0.5346224240000002</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>1.972490407972864</v>
+      </c>
+      <c r="T85">
+        <v>7.262397975426654</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.03869228429921383</v>
+      </c>
+      <c r="W85">
+        <v>0.2295602825093478</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1612178512467243</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.5278584038381453</v>
+      </c>
+      <c r="C86">
+        <v>-0.6272049816460386</v>
+      </c>
+      <c r="D86">
+        <v>3.014795018353962</v>
+      </c>
+      <c r="E86">
+        <v>3.624000000000001</v>
+      </c>
+      <c r="F86">
+        <v>3.654</v>
+      </c>
+      <c r="G86">
+        <v>0.012</v>
+      </c>
+      <c r="H86">
+        <v>4.32</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0.154</v>
+      </c>
+      <c r="K86">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L86">
+        <v>0.139</v>
+      </c>
+      <c r="M86">
+        <v>0.8725752000000001</v>
+      </c>
+      <c r="N86">
+        <v>-0.7335752000000001</v>
+      </c>
+      <c r="O86">
+        <v>-0.176058048</v>
+      </c>
+      <c r="P86">
+        <v>-0.5575171520000001</v>
+      </c>
+      <c r="Q86">
+        <v>-0.5425171520000001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>2.093346058471167</v>
+      </c>
+      <c r="T86">
+        <v>7.716297848890815</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.03823166186708033</v>
+      </c>
+      <c r="W86">
+        <v>0.2296702791461412</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1592985911128347</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.5298584038381453</v>
+      </c>
+      <c r="C87">
+        <v>-0.6829837452097616</v>
+      </c>
+      <c r="D87">
+        <v>3.002516254790239</v>
+      </c>
+      <c r="E87">
+        <v>3.6675</v>
+      </c>
+      <c r="F87">
+        <v>3.6975</v>
+      </c>
+      <c r="G87">
+        <v>0.012</v>
+      </c>
+      <c r="H87">
+        <v>4.32</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0.154</v>
+      </c>
+      <c r="K87">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L87">
+        <v>0.139</v>
+      </c>
+      <c r="M87">
+        <v>0.8829630000000001</v>
+      </c>
+      <c r="N87">
+        <v>-0.743963</v>
+      </c>
+      <c r="O87">
+        <v>-0.17855112</v>
+      </c>
+      <c r="P87">
+        <v>-0.5654118800000001</v>
+      </c>
+      <c r="Q87">
+        <v>-0.5504118800000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>2.230315795702578</v>
+      </c>
+      <c r="T87">
+        <v>8.230717705483537</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.03778187760982057</v>
+      </c>
+      <c r="W87">
+        <v>0.2297776876267749</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1574244900409191</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.5318584038381454</v>
+      </c>
+      <c r="C88">
+        <v>-0.738662895717765</v>
+      </c>
+      <c r="D88">
+        <v>2.990337104282236</v>
+      </c>
+      <c r="E88">
+        <v>3.711000000000001</v>
+      </c>
+      <c r="F88">
+        <v>3.741000000000001</v>
+      </c>
+      <c r="G88">
+        <v>0.012</v>
+      </c>
+      <c r="H88">
+        <v>4.32</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0.154</v>
+      </c>
+      <c r="K88">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L88">
+        <v>0.139</v>
+      </c>
+      <c r="M88">
+        <v>0.8933508000000002</v>
+      </c>
+      <c r="N88">
+        <v>-0.7543508000000002</v>
+      </c>
+      <c r="O88">
+        <v>-0.181044192</v>
+      </c>
+      <c r="P88">
+        <v>-0.5733066080000002</v>
+      </c>
+      <c r="Q88">
+        <v>-0.5583066080000002</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>2.386852638252762</v>
+      </c>
+      <c r="T88">
+        <v>8.818626113018077</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.03734255345156683</v>
+      </c>
+      <c r="W88">
+        <v>0.2298825982357659</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1555939727148619</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.5338584038381453</v>
+      </c>
+      <c r="C89">
+        <v>-0.7942436404585806</v>
+      </c>
+      <c r="D89">
+        <v>2.97825635954142</v>
+      </c>
+      <c r="E89">
+        <v>3.754500000000001</v>
+      </c>
+      <c r="F89">
+        <v>3.7845</v>
+      </c>
+      <c r="G89">
+        <v>0.012</v>
+      </c>
+      <c r="H89">
+        <v>4.32</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0.154</v>
+      </c>
+      <c r="K89">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L89">
+        <v>0.139</v>
+      </c>
+      <c r="M89">
+        <v>0.9037386000000002</v>
+      </c>
+      <c r="N89">
+        <v>-0.7647386000000002</v>
+      </c>
+      <c r="O89">
+        <v>-0.183537264</v>
+      </c>
+      <c r="P89">
+        <v>-0.5812013360000001</v>
+      </c>
+      <c r="Q89">
+        <v>-0.5662013360000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>2.567472071964513</v>
+      </c>
+      <c r="T89">
+        <v>9.49698196786562</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.03691332869924997</v>
+      </c>
+      <c r="W89">
+        <v>0.2299850971066191</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1538055362468749</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.5358584038381454</v>
+      </c>
+      <c r="C90">
+        <v>-0.8497271672898115</v>
+      </c>
+      <c r="D90">
+        <v>2.966272832710189</v>
+      </c>
+      <c r="E90">
+        <v>3.798</v>
+      </c>
+      <c r="F90">
+        <v>3.828</v>
+      </c>
+      <c r="G90">
+        <v>0.012</v>
+      </c>
+      <c r="H90">
+        <v>4.32</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0.154</v>
+      </c>
+      <c r="K90">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L90">
+        <v>0.139</v>
+      </c>
+      <c r="M90">
+        <v>0.9141264000000001</v>
+      </c>
+      <c r="N90">
+        <v>-0.7751264000000001</v>
+      </c>
+      <c r="O90">
+        <v>-0.186030336</v>
+      </c>
+      <c r="P90">
+        <v>-0.589096064</v>
+      </c>
+      <c r="Q90">
+        <v>-0.574096064</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>2.778194744628223</v>
+      </c>
+      <c r="T90">
+        <v>10.28839713185442</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.03649385905494032</v>
+      </c>
+      <c r="W90">
+        <v>0.2300852664576803</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1520577460622513</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.5378584038381453</v>
+      </c>
+      <c r="C91">
+        <v>-0.9051146450274752</v>
+      </c>
+      <c r="D91">
+        <v>2.954385354972525</v>
+      </c>
+      <c r="E91">
+        <v>3.841500000000001</v>
+      </c>
+      <c r="F91">
+        <v>3.871500000000001</v>
+      </c>
+      <c r="G91">
+        <v>0.012</v>
+      </c>
+      <c r="H91">
+        <v>4.32</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0.154</v>
+      </c>
+      <c r="K91">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L91">
+        <v>0.139</v>
+      </c>
+      <c r="M91">
+        <v>0.9245142000000002</v>
+      </c>
+      <c r="N91">
+        <v>-0.7855142000000002</v>
+      </c>
+      <c r="O91">
+        <v>-0.188523408</v>
+      </c>
+      <c r="P91">
+        <v>-0.5969907920000002</v>
+      </c>
+      <c r="Q91">
+        <v>-0.5819907920000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>3.027230630503516</v>
+      </c>
+      <c r="T91">
+        <v>11.22370596202301</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.03608381569477245</v>
+      </c>
+      <c r="W91">
+        <v>0.2301831848120884</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1503492320615519</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.5398584038381453</v>
+      </c>
+      <c r="C92">
+        <v>-0.9604072238260417</v>
+      </c>
+      <c r="D92">
+        <v>2.942592776173959</v>
+      </c>
+      <c r="E92">
+        <v>3.885000000000001</v>
+      </c>
+      <c r="F92">
+        <v>3.915</v>
+      </c>
+      <c r="G92">
+        <v>0.012</v>
+      </c>
+      <c r="H92">
+        <v>4.32</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0.154</v>
+      </c>
+      <c r="K92">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L92">
+        <v>0.139</v>
+      </c>
+      <c r="M92">
+        <v>0.9349020000000001</v>
+      </c>
+      <c r="N92">
+        <v>-0.7959020000000001</v>
+      </c>
+      <c r="O92">
+        <v>-0.19101648</v>
+      </c>
+      <c r="P92">
+        <v>-0.6048855200000001</v>
+      </c>
+      <c r="Q92">
+        <v>-0.5898855200000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>3.326073693553868</v>
+      </c>
+      <c r="T92">
+        <v>12.34607655822531</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.03568288440927498</v>
+      </c>
+      <c r="W92">
+        <v>0.2302789272030651</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1486786850386458</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.5418584038381453</v>
+      </c>
+      <c r="C93">
+        <v>-1.015606035549385</v>
+      </c>
+      <c r="D93">
+        <v>2.930893964450616</v>
+      </c>
+      <c r="E93">
+        <v>3.928500000000001</v>
+      </c>
+      <c r="F93">
+        <v>3.958500000000001</v>
+      </c>
+      <c r="G93">
+        <v>0.012</v>
+      </c>
+      <c r="H93">
+        <v>4.32</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0.154</v>
+      </c>
+      <c r="K93">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L93">
+        <v>0.139</v>
+      </c>
+      <c r="M93">
+        <v>0.9452898000000003</v>
+      </c>
+      <c r="N93">
+        <v>-0.8062898000000003</v>
+      </c>
+      <c r="O93">
+        <v>-0.1935095520000001</v>
+      </c>
+      <c r="P93">
+        <v>-0.6127802480000002</v>
+      </c>
+      <c r="Q93">
+        <v>-0.5977802480000002</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>3.691326326170965</v>
+      </c>
+      <c r="T93">
+        <v>13.71786284247257</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.03529076480038184</v>
+      </c>
+      <c r="W93">
+        <v>0.2303725653656688</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1470448533349243</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.5438584038381453</v>
+      </c>
+      <c r="C94">
+        <v>-1.070712194132937</v>
+      </c>
+      <c r="D94">
+        <v>2.919287805867063</v>
+      </c>
+      <c r="E94">
+        <v>3.972000000000001</v>
+      </c>
+      <c r="F94">
+        <v>4.002000000000001</v>
+      </c>
+      <c r="G94">
+        <v>0.012</v>
+      </c>
+      <c r="H94">
+        <v>4.32</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0.154</v>
+      </c>
+      <c r="K94">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L94">
+        <v>0.139</v>
+      </c>
+      <c r="M94">
+        <v>0.9556776000000002</v>
+      </c>
+      <c r="N94">
+        <v>-0.8166776000000002</v>
+      </c>
+      <c r="O94">
+        <v>-0.196002624</v>
+      </c>
+      <c r="P94">
+        <v>-0.6206749760000002</v>
+      </c>
+      <c r="Q94">
+        <v>-0.6056749760000002</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>4.147892116942336</v>
+      </c>
+      <c r="T94">
+        <v>15.43259569778164</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.03490716953081248</v>
+      </c>
+      <c r="W94">
+        <v>0.230464167916042</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1454465397117186</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.5458584038381453</v>
+      </c>
+      <c r="C95">
+        <v>-1.125726795937264</v>
+      </c>
+      <c r="D95">
+        <v>2.907773204062737</v>
+      </c>
+      <c r="E95">
+        <v>4.0155</v>
+      </c>
+      <c r="F95">
+        <v>4.045500000000001</v>
+      </c>
+      <c r="G95">
+        <v>0.012</v>
+      </c>
+      <c r="H95">
+        <v>4.32</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0.154</v>
+      </c>
+      <c r="K95">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L95">
+        <v>0.139</v>
+      </c>
+      <c r="M95">
+        <v>0.9660654000000002</v>
+      </c>
+      <c r="N95">
+        <v>-0.8270654000000002</v>
+      </c>
+      <c r="O95">
+        <v>-0.198495696</v>
+      </c>
+      <c r="P95">
+        <v>-0.6285697040000001</v>
+      </c>
+      <c r="Q95">
+        <v>-0.6135697040000001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>4.734905276505527</v>
+      </c>
+      <c r="T95">
+        <v>17.63725222603616</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.03453182362187901</v>
+      </c>
+      <c r="W95">
+        <v>0.2305538005190953</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1438825984244959</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.5478584038381453</v>
+      </c>
+      <c r="C96">
+        <v>-1.18065092009331</v>
+      </c>
+      <c r="D96">
+        <v>2.896349079906691</v>
+      </c>
+      <c r="E96">
+        <v>4.059</v>
+      </c>
+      <c r="F96">
+        <v>4.089</v>
+      </c>
+      <c r="G96">
+        <v>0.012</v>
+      </c>
+      <c r="H96">
+        <v>4.32</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0.154</v>
+      </c>
+      <c r="K96">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L96">
+        <v>0.139</v>
+      </c>
+      <c r="M96">
+        <v>0.9764532000000001</v>
+      </c>
+      <c r="N96">
+        <v>-0.8374532000000001</v>
+      </c>
+      <c r="O96">
+        <v>-0.200988768</v>
+      </c>
+      <c r="P96">
+        <v>-0.6364644320000001</v>
+      </c>
+      <c r="Q96">
+        <v>-0.6214644320000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>5.51758948925645</v>
+      </c>
+      <c r="T96">
+        <v>20.57679426370886</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.03416446379611434</v>
+      </c>
+      <c r="W96">
+        <v>0.2306415260454879</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1423519324838097</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.5498584038381454</v>
+      </c>
+      <c r="C97">
+        <v>-1.235485628839531</v>
+      </c>
+      <c r="D97">
+        <v>2.88501437116047</v>
+      </c>
+      <c r="E97">
+        <v>4.102500000000001</v>
+      </c>
+      <c r="F97">
+        <v>4.132500000000001</v>
+      </c>
+      <c r="G97">
+        <v>0.012</v>
+      </c>
+      <c r="H97">
+        <v>4.32</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0.154</v>
+      </c>
+      <c r="K97">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L97">
+        <v>0.139</v>
+      </c>
+      <c r="M97">
+        <v>0.9868410000000003</v>
+      </c>
+      <c r="N97">
+        <v>-0.8478410000000003</v>
+      </c>
+      <c r="O97">
+        <v>-0.2034818400000001</v>
+      </c>
+      <c r="P97">
+        <v>-0.6443591600000003</v>
+      </c>
+      <c r="Q97">
+        <v>-0.6293591600000003</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>6.613347387107744</v>
+      </c>
+      <c r="T97">
+        <v>24.69215311645065</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.0338048378614184</v>
+      </c>
+      <c r="W97">
+        <v>0.2307274047186933</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1408534910892433</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.5518584038381453</v>
+      </c>
+      <c r="C98">
+        <v>-1.290231967851143</v>
+      </c>
+      <c r="D98">
+        <v>2.873768032148857</v>
+      </c>
+      <c r="E98">
+        <v>4.146</v>
+      </c>
+      <c r="F98">
+        <v>4.176</v>
+      </c>
+      <c r="G98">
+        <v>0.012</v>
+      </c>
+      <c r="H98">
+        <v>4.32</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0.154</v>
+      </c>
+      <c r="K98">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L98">
+        <v>0.139</v>
+      </c>
+      <c r="M98">
+        <v>0.9972288000000001</v>
+      </c>
+      <c r="N98">
+        <v>-0.8582288000000001</v>
+      </c>
+      <c r="O98">
+        <v>-0.205974912</v>
+      </c>
+      <c r="P98">
+        <v>-0.6522538880000002</v>
+      </c>
+      <c r="Q98">
+        <v>-0.6372538880000002</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>8.25698423388466</v>
+      </c>
+      <c r="T98">
+        <v>30.86519139556324</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.0334527041336953</v>
+      </c>
+      <c r="W98">
+        <v>0.2308114942528736</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1393862672237304</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.5538584038381453</v>
+      </c>
+      <c r="C99">
+        <v>-1.344890966561712</v>
+      </c>
+      <c r="D99">
+        <v>2.862609033438288</v>
+      </c>
+      <c r="E99">
+        <v>4.1895</v>
+      </c>
+      <c r="F99">
+        <v>4.2195</v>
+      </c>
+      <c r="G99">
+        <v>0.012</v>
+      </c>
+      <c r="H99">
+        <v>4.32</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0.154</v>
+      </c>
+      <c r="K99">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L99">
+        <v>0.139</v>
+      </c>
+      <c r="M99">
+        <v>1.0076166</v>
+      </c>
+      <c r="N99">
+        <v>-0.8686166</v>
+      </c>
+      <c r="O99">
+        <v>-0.208467984</v>
+      </c>
+      <c r="P99">
+        <v>-0.660148616</v>
+      </c>
+      <c r="Q99">
+        <v>-0.645148616</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>10.99637897851288</v>
+      </c>
+      <c r="T99">
+        <v>41.15358852741766</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.0331078308952036</v>
+      </c>
+      <c r="W99">
+        <v>0.2308938499822254</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1379492953966817</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.5558584038381453</v>
+      </c>
+      <c r="C100">
+        <v>-1.39946363847726</v>
+      </c>
+      <c r="D100">
+        <v>2.85153636152274</v>
+      </c>
+      <c r="E100">
+        <v>4.233000000000001</v>
+      </c>
+      <c r="F100">
+        <v>4.263000000000001</v>
+      </c>
+      <c r="G100">
+        <v>0.012</v>
+      </c>
+      <c r="H100">
+        <v>4.32</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0.154</v>
+      </c>
+      <c r="K100">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L100">
+        <v>0.139</v>
+      </c>
+      <c r="M100">
+        <v>1.0180044</v>
+      </c>
+      <c r="N100">
+        <v>-0.8790044000000001</v>
+      </c>
+      <c r="O100">
+        <v>-0.210961056</v>
+      </c>
+      <c r="P100">
+        <v>-0.6680433440000001</v>
+      </c>
+      <c r="Q100">
+        <v>-0.6530433440000001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>16.47516846776932</v>
+      </c>
+      <c r="T100">
+        <v>61.73038279112649</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.03276999588606886</v>
+      </c>
+      <c r="W100">
+        <v>0.2309745249824068</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1365416495252869</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.5578584038381453</v>
+      </c>
+      <c r="C101">
+        <v>-1.453950981483123</v>
+      </c>
+      <c r="D101">
+        <v>2.840549018516878</v>
+      </c>
+      <c r="E101">
+        <v>4.2765</v>
+      </c>
+      <c r="F101">
+        <v>4.306500000000001</v>
+      </c>
+      <c r="G101">
+        <v>0.012</v>
+      </c>
+      <c r="H101">
+        <v>4.32</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0.154</v>
+      </c>
+      <c r="K101">
+        <v>0.01499999999999999</v>
+      </c>
+      <c r="L101">
+        <v>0.139</v>
+      </c>
+      <c r="M101">
+        <v>1.0283922</v>
+      </c>
+      <c r="N101">
+        <v>-0.8893922000000003</v>
+      </c>
+      <c r="O101">
+        <v>-0.2134541280000001</v>
+      </c>
+      <c r="P101">
+        <v>-0.6759380720000002</v>
+      </c>
+      <c r="Q101">
+        <v>-0.6609380720000002</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>32.91153693553864</v>
+      </c>
+      <c r="T101">
+        <v>123.460765582253</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.03243898582661361</v>
+      </c>
+      <c r="W101">
+        <v>0.2310535701846047</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1351624409442234</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_heathcare_information_and_technology.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_heathcare_information_and_technology.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.284751115863874</v>
+        <v>0.2841019131858007</v>
       </c>
       <c r="C2">
-        <v>5.787144146291965</v>
+        <v>5.744524230354599</v>
       </c>
       <c r="D2">
-        <v>5.583144146291965</v>
+        <v>5.598354230354599</v>
       </c>
       <c r="E2">
-        <v>-0.033</v>
+        <v>0.02483</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.05783000000000001</v>
       </c>
       <c r="G2">
         <v>0.204</v>
@@ -1445,28 +1445,28 @@
         <v>0.057</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.002908849</v>
       </c>
       <c r="N2">
-        <v>0.057</v>
+        <v>0.054091151</v>
       </c>
       <c r="O2">
-        <v>0.01368</v>
+        <v>0.01298187624</v>
       </c>
       <c r="P2">
-        <v>0.04332</v>
+        <v>0.04110927476</v>
       </c>
       <c r="Q2">
-        <v>0.04232</v>
+        <v>0.04010927476</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.284751115863874</v>
+        <v>0.2865854880664653</v>
       </c>
       <c r="T2">
-        <v>1.174055766301309</v>
+        <v>1.183068719658774</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>19.59537947827474</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2841019131858007</v>
+        <v>0.2835013505077274</v>
       </c>
       <c r="C3">
-        <v>5.744524230354599</v>
+        <v>5.700838712925703</v>
       </c>
       <c r="D3">
-        <v>5.598354230354599</v>
+        <v>5.612498712925704</v>
       </c>
       <c r="E3">
-        <v>0.02483</v>
+        <v>0.08266000000000001</v>
       </c>
       <c r="F3">
-        <v>0.05783000000000001</v>
+        <v>0.11566</v>
       </c>
       <c r="G3">
         <v>0.204</v>
@@ -1527,45 +1527,45 @@
         <v>0.057</v>
       </c>
       <c r="M3">
-        <v>0.002908849</v>
+        <v>0.00618781</v>
       </c>
       <c r="N3">
-        <v>0.054091151</v>
+        <v>0.05081219</v>
       </c>
       <c r="O3">
-        <v>0.01298187624</v>
+        <v>0.0121949256</v>
       </c>
       <c r="P3">
-        <v>0.04110927476</v>
+        <v>0.0386172644</v>
       </c>
       <c r="Q3">
-        <v>0.04010927476</v>
+        <v>0.0376172644</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2865854880664653</v>
+        <v>0.2884572964364565</v>
       </c>
       <c r="T3">
-        <v>1.183068719658774</v>
+        <v>1.19226561083986</v>
       </c>
       <c r="U3">
-        <v>0.0503</v>
+        <v>0.0535</v>
       </c>
       <c r="V3">
         <v>0.24</v>
       </c>
       <c r="W3">
-        <v>0.038228</v>
+        <v>0.04066</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y3">
-        <v>19.59537947827474</v>
+        <v>9.211659698665603</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2835013505077274</v>
+        <v>0.2829175078296541</v>
       </c>
       <c r="C4">
-        <v>5.700838712925703</v>
+        <v>5.656828090116492</v>
       </c>
       <c r="D4">
-        <v>5.612498712925704</v>
+        <v>5.626318090116492</v>
       </c>
       <c r="E4">
-        <v>0.08266000000000001</v>
+        <v>0.14049</v>
       </c>
       <c r="F4">
-        <v>0.11566</v>
+        <v>0.17349</v>
       </c>
       <c r="G4">
         <v>0.204</v>
@@ -1609,45 +1609,45 @@
         <v>0.057</v>
       </c>
       <c r="M4">
-        <v>0.00618781</v>
+        <v>0.009593997</v>
       </c>
       <c r="N4">
-        <v>0.05081219</v>
+        <v>0.047406003</v>
       </c>
       <c r="O4">
-        <v>0.0121949256</v>
+        <v>0.01137744072</v>
       </c>
       <c r="P4">
-        <v>0.0386172644</v>
+        <v>0.03602856228</v>
       </c>
       <c r="Q4">
-        <v>0.0376172644</v>
+        <v>0.03502856228</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2884572964364565</v>
+        <v>0.2903676987934579</v>
       </c>
       <c r="T4">
-        <v>1.19226561083986</v>
+        <v>1.201652128643237</v>
       </c>
       <c r="U4">
-        <v>0.0535</v>
+        <v>0.0553</v>
       </c>
       <c r="V4">
         <v>0.24</v>
       </c>
       <c r="W4">
-        <v>0.04066</v>
+        <v>0.042028</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y4">
-        <v>9.211659698665603</v>
+        <v>5.941215116077272</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2829175078296541</v>
+        <v>0.2823823051515808</v>
       </c>
       <c r="C5">
-        <v>5.656828090116492</v>
+        <v>5.611726094045581</v>
       </c>
       <c r="D5">
-        <v>5.626318090116492</v>
+        <v>5.639046094045582</v>
       </c>
       <c r="E5">
-        <v>0.14049</v>
+        <v>0.19832</v>
       </c>
       <c r="F5">
-        <v>0.17349</v>
+        <v>0.23132</v>
       </c>
       <c r="G5">
         <v>0.204</v>
@@ -1691,45 +1691,45 @@
         <v>0.057</v>
       </c>
       <c r="M5">
-        <v>0.009593997</v>
+        <v>0.013370296</v>
       </c>
       <c r="N5">
-        <v>0.047406003</v>
+        <v>0.043629704</v>
       </c>
       <c r="O5">
-        <v>0.01137744072</v>
+        <v>0.01047112896</v>
       </c>
       <c r="P5">
-        <v>0.03602856228</v>
+        <v>0.03315857504</v>
       </c>
       <c r="Q5">
-        <v>0.03502856228</v>
+        <v>0.03215857504</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2903676987934579</v>
+        <v>0.2923179011995634</v>
       </c>
       <c r="T5">
-        <v>1.201652128643237</v>
+        <v>1.211234198900851</v>
       </c>
       <c r="U5">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V5">
         <v>0.24</v>
       </c>
       <c r="W5">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y5">
-        <v>5.941215116077272</v>
+        <v>4.26318160794645</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2823823051515808</v>
+        <v>0.2820295024735075</v>
       </c>
       <c r="C6">
-        <v>5.611726094045581</v>
+        <v>5.562317864158656</v>
       </c>
       <c r="D6">
-        <v>5.639046094045582</v>
+        <v>5.647467864158656</v>
       </c>
       <c r="E6">
-        <v>0.19832</v>
+        <v>0.25615</v>
       </c>
       <c r="F6">
-        <v>0.23132</v>
+        <v>0.28915</v>
       </c>
       <c r="G6">
         <v>0.204</v>
@@ -1773,45 +1773,45 @@
         <v>0.057</v>
       </c>
       <c r="M6">
-        <v>0.013370296</v>
+        <v>0.018534515</v>
       </c>
       <c r="N6">
-        <v>0.043629704</v>
+        <v>0.038465485</v>
       </c>
       <c r="O6">
-        <v>0.01047112896</v>
+        <v>0.009231716399999999</v>
       </c>
       <c r="P6">
-        <v>0.03315857504</v>
+        <v>0.0292337686</v>
       </c>
       <c r="Q6">
-        <v>0.03215857504</v>
+        <v>0.0282337686</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2923179011995634</v>
+        <v>0.294309160498429</v>
       </c>
       <c r="T6">
-        <v>1.211234198900851</v>
+        <v>1.221017996953362</v>
       </c>
       <c r="U6">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="V6">
         <v>0.24</v>
       </c>
       <c r="W6">
-        <v>0.043928</v>
+        <v>0.048716</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y6">
-        <v>4.26318160794645</v>
+        <v>3.075343487542026</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2820295024735075</v>
+        <v>0.2820186997954342</v>
       </c>
       <c r="C7">
-        <v>5.562317864158656</v>
+        <v>5.504746132353845</v>
       </c>
       <c r="D7">
-        <v>5.647467864158656</v>
+        <v>5.647726132353846</v>
       </c>
       <c r="E7">
-        <v>0.25615</v>
+        <v>0.31398</v>
       </c>
       <c r="F7">
-        <v>0.28915</v>
+        <v>0.3469800000000001</v>
       </c>
       <c r="G7">
         <v>0.204</v>
@@ -1855,45 +1855,45 @@
         <v>0.057</v>
       </c>
       <c r="M7">
-        <v>0.018534515</v>
+        <v>0.02630108400000001</v>
       </c>
       <c r="N7">
-        <v>0.038465485</v>
+        <v>0.030698916</v>
       </c>
       <c r="O7">
-        <v>0.009231716399999999</v>
+        <v>0.007367739839999999</v>
       </c>
       <c r="P7">
-        <v>0.0292337686</v>
+        <v>0.02333117616</v>
       </c>
       <c r="Q7">
-        <v>0.0282337686</v>
+        <v>0.02233117616</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.294309160498429</v>
+        <v>0.2963427870164194</v>
       </c>
       <c r="T7">
-        <v>1.221017996953362</v>
+        <v>1.231009960921883</v>
       </c>
       <c r="U7">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V7">
         <v>0.24</v>
       </c>
       <c r="W7">
-        <v>0.048716</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y7">
-        <v>3.075343487542026</v>
+        <v>2.167211054875152</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.2820186997954342</v>
+        <v>0.2823187371173609</v>
       </c>
       <c r="C8">
-        <v>5.504746132353845</v>
+        <v>5.439751674077178</v>
       </c>
       <c r="D8">
-        <v>5.647726132353846</v>
+        <v>5.640561674077179</v>
       </c>
       <c r="E8">
-        <v>0.31398</v>
+        <v>0.37181</v>
       </c>
       <c r="F8">
-        <v>0.34698</v>
+        <v>0.40481</v>
       </c>
       <c r="G8">
         <v>0.204</v>
@@ -1937,45 +1937,45 @@
         <v>0.057</v>
       </c>
       <c r="M8">
-        <v>0.026301084</v>
+        <v>0.0364329</v>
       </c>
       <c r="N8">
-        <v>0.030698916</v>
+        <v>0.0205671</v>
       </c>
       <c r="O8">
-        <v>0.00736773984</v>
+        <v>0.004936104000000001</v>
       </c>
       <c r="P8">
-        <v>0.02333117616</v>
+        <v>0.015630996</v>
       </c>
       <c r="Q8">
-        <v>0.02233117616</v>
+        <v>0.014630996</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2963427870164194</v>
+        <v>0.2984201474380225</v>
       </c>
       <c r="T8">
-        <v>1.231009960921883</v>
+        <v>1.241216805835964</v>
       </c>
       <c r="U8">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V8">
         <v>0.24</v>
       </c>
       <c r="W8">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y8">
-        <v>2.167211054875152</v>
+        <v>1.564519980567015</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2823187371173609</v>
+        <v>0.2866150724280285</v>
       </c>
       <c r="C9">
-        <v>5.439751674077179</v>
+        <v>5.281289499986088</v>
       </c>
       <c r="D9">
-        <v>5.64056167407718</v>
+        <v>5.539929499986089</v>
       </c>
       <c r="E9">
-        <v>0.3718100000000001</v>
+        <v>0.42964</v>
       </c>
       <c r="F9">
-        <v>0.4048100000000001</v>
+        <v>0.4626400000000001</v>
       </c>
       <c r="G9">
         <v>0.204</v>
@@ -2019,45 +2019,45 @@
         <v>0.057</v>
       </c>
       <c r="M9">
-        <v>0.0364329</v>
+        <v>0.06791555200000002</v>
       </c>
       <c r="N9">
-        <v>0.0205671</v>
+        <v>-0.01091555200000002</v>
       </c>
       <c r="O9">
-        <v>0.004936103999999999</v>
+        <v>-0.002619732480000004</v>
       </c>
       <c r="P9">
-        <v>0.015630996</v>
+        <v>-0.008295819520000011</v>
       </c>
       <c r="Q9">
-        <v>0.014630996</v>
+        <v>-0.009295819520000012</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2984201474380225</v>
+        <v>0.3013441593898324</v>
       </c>
       <c r="T9">
-        <v>1.241216805835964</v>
+        <v>1.255583564829097</v>
       </c>
       <c r="U9">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V9">
-        <v>0.24</v>
+        <v>0.2014266187514753</v>
       </c>
       <c r="W9">
-        <v>0.0684</v>
+        <v>0.1172305723672834</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y9">
-        <v>1.564519980567015</v>
+        <v>0.8392775781311471</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2866150724280285</v>
+        <v>0.293520562558319</v>
       </c>
       <c r="C10">
-        <v>5.281289499986088</v>
+        <v>5.06902771568214</v>
       </c>
       <c r="D10">
-        <v>5.539929499986089</v>
+        <v>5.38549771568214</v>
       </c>
       <c r="E10">
-        <v>0.42964</v>
+        <v>0.48747</v>
       </c>
       <c r="F10">
-        <v>0.4626400000000001</v>
+        <v>0.52047</v>
       </c>
       <c r="G10">
         <v>0.204</v>
@@ -2101,45 +2101,45 @@
         <v>0.057</v>
       </c>
       <c r="M10">
-        <v>0.06791555200000002</v>
+        <v>0.104510376</v>
       </c>
       <c r="N10">
-        <v>-0.01091555200000002</v>
+        <v>-0.047510376</v>
       </c>
       <c r="O10">
-        <v>-0.002619732480000004</v>
+        <v>-0.01140249024</v>
       </c>
       <c r="P10">
-        <v>-0.008295819520000011</v>
+        <v>-0.03610788576</v>
       </c>
       <c r="Q10">
-        <v>-0.009295819520000012</v>
+        <v>-0.03710788576</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.3013441593898324</v>
+        <v>0.3052902382076223</v>
       </c>
       <c r="T10">
-        <v>1.255583564829097</v>
+        <v>1.274972118732921</v>
       </c>
       <c r="U10">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V10">
-        <v>0.2014266187514753</v>
+        <v>0.1308960939916626</v>
       </c>
       <c r="W10">
-        <v>0.1172305723672834</v>
+        <v>0.1745160643264742</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y10">
-        <v>0.8392775781311471</v>
+        <v>0.5454003916319276</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.293520562558319</v>
+        <v>0.298988395333225</v>
       </c>
       <c r="C11">
-        <v>5.06902771568214</v>
+        <v>4.894893013485056</v>
       </c>
       <c r="D11">
-        <v>5.38549771568214</v>
+        <v>5.269193013485057</v>
       </c>
       <c r="E11">
-        <v>0.48747</v>
+        <v>0.5453</v>
       </c>
       <c r="F11">
-        <v>0.52047</v>
+        <v>0.5783</v>
       </c>
       <c r="G11">
         <v>0.204</v>
@@ -2183,45 +2183,45 @@
         <v>0.057</v>
       </c>
       <c r="M11">
-        <v>0.104510376</v>
+        <v>0.13636314</v>
       </c>
       <c r="N11">
-        <v>-0.047510376</v>
+        <v>-0.07936314000000003</v>
       </c>
       <c r="O11">
-        <v>-0.01140249024</v>
+        <v>-0.01904715360000001</v>
       </c>
       <c r="P11">
-        <v>-0.03610788576</v>
+        <v>-0.06031598640000002</v>
       </c>
       <c r="Q11">
-        <v>-0.03710788576</v>
+        <v>-0.06131598640000002</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.3052902382076223</v>
+        <v>0.3086377217153803</v>
       </c>
       <c r="T11">
-        <v>1.274972118732921</v>
+        <v>1.291419551090261</v>
       </c>
       <c r="U11">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>0.1308960939916626</v>
+        <v>0.1003203651661292</v>
       </c>
       <c r="W11">
-        <v>0.1745160643264742</v>
+        <v>0.2121444578938267</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y11">
-        <v>0.5454003916319276</v>
+        <v>0.4180015215255383</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.298988395333225</v>
+        <v>0.3008883953332249</v>
       </c>
       <c r="C12">
-        <v>4.894893013485056</v>
+        <v>4.797815964584448</v>
       </c>
       <c r="D12">
-        <v>5.269193013485057</v>
+        <v>5.229945964584448</v>
       </c>
       <c r="E12">
-        <v>0.5453</v>
+        <v>0.6031300000000001</v>
       </c>
       <c r="F12">
-        <v>0.5783</v>
+        <v>0.6361300000000001</v>
       </c>
       <c r="G12">
         <v>0.204</v>
@@ -2265,37 +2265,37 @@
         <v>0.057</v>
       </c>
       <c r="M12">
-        <v>0.13636314</v>
+        <v>0.149999454</v>
       </c>
       <c r="N12">
-        <v>-0.07936314000000003</v>
+        <v>-0.09299945400000004</v>
       </c>
       <c r="O12">
-        <v>-0.01904715360000001</v>
+        <v>-0.02231986896000001</v>
       </c>
       <c r="P12">
-        <v>-0.06031598640000002</v>
+        <v>-0.07067958504000002</v>
       </c>
       <c r="Q12">
-        <v>-0.06131598640000002</v>
+        <v>-0.07167958504000002</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.3086377217153803</v>
+        <v>0.3115909545436429</v>
       </c>
       <c r="T12">
-        <v>1.291419551090261</v>
+        <v>1.305929883124982</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>0.1003203651661292</v>
+        <v>0.09120033196920835</v>
       </c>
       <c r="W12">
-        <v>0.2121444578938267</v>
+        <v>0.2142949617216607</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.4180015215255383</v>
+        <v>0.3800013832050347</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.3008883953332249</v>
+        <v>0.3027883953332249</v>
       </c>
       <c r="C13">
-        <v>4.797815964584448</v>
+        <v>4.701319248448001</v>
       </c>
       <c r="D13">
-        <v>5.229945964584448</v>
+        <v>5.191279248448001</v>
       </c>
       <c r="E13">
-        <v>0.6031300000000001</v>
+        <v>0.66096</v>
       </c>
       <c r="F13">
-        <v>0.6361300000000001</v>
+        <v>0.69396</v>
       </c>
       <c r="G13">
         <v>0.204</v>
@@ -2347,37 +2347,37 @@
         <v>0.057</v>
       </c>
       <c r="M13">
-        <v>0.149999454</v>
+        <v>0.163635768</v>
       </c>
       <c r="N13">
-        <v>-0.09299945400000004</v>
+        <v>-0.106635768</v>
       </c>
       <c r="O13">
-        <v>-0.02231986896000001</v>
+        <v>-0.02559258432</v>
       </c>
       <c r="P13">
-        <v>-0.07067958504000002</v>
+        <v>-0.08104318368000002</v>
       </c>
       <c r="Q13">
-        <v>-0.07167958504000002</v>
+        <v>-0.08204318368000002</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.3115909545436429</v>
+        <v>0.3146113062998207</v>
       </c>
       <c r="T13">
-        <v>1.305929883124982</v>
+        <v>1.320769995433221</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.09120033196920835</v>
+        <v>0.08360030430510766</v>
       </c>
       <c r="W13">
-        <v>0.2142949617216607</v>
+        <v>0.2160870482448556</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.3800013832050347</v>
+        <v>0.3483346012712819</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.3027883953332249</v>
+        <v>0.3046883953332249</v>
       </c>
       <c r="C14">
-        <v>4.701319248448001</v>
+        <v>4.605390087767757</v>
       </c>
       <c r="D14">
-        <v>5.191279248448001</v>
+        <v>5.153180087767757</v>
       </c>
       <c r="E14">
-        <v>0.66096</v>
+        <v>0.71879</v>
       </c>
       <c r="F14">
-        <v>0.69396</v>
+        <v>0.7517900000000001</v>
       </c>
       <c r="G14">
         <v>0.204</v>
@@ -2429,37 +2429,37 @@
         <v>0.057</v>
       </c>
       <c r="M14">
-        <v>0.163635768</v>
+        <v>0.177272082</v>
       </c>
       <c r="N14">
-        <v>-0.106635768</v>
+        <v>-0.120272082</v>
       </c>
       <c r="O14">
-        <v>-0.02559258432</v>
+        <v>-0.02886529968</v>
       </c>
       <c r="P14">
-        <v>-0.08104318368000002</v>
+        <v>-0.09140678232000002</v>
       </c>
       <c r="Q14">
-        <v>-0.08204318368000002</v>
+        <v>-0.09240678232000002</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.3146113062998207</v>
+        <v>0.3177010914297037</v>
       </c>
       <c r="T14">
-        <v>1.320769995433221</v>
+        <v>1.335951259748545</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.08360030430510766</v>
+        <v>0.07716951166625323</v>
       </c>
       <c r="W14">
-        <v>0.2160870482448556</v>
+        <v>0.2176034291490975</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.3483346012712819</v>
+        <v>0.3215396319427217</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.3046883953332249</v>
+        <v>0.3065883953332249</v>
       </c>
       <c r="C15">
-        <v>4.605390087767757</v>
+        <v>4.510016077597181</v>
       </c>
       <c r="D15">
-        <v>5.153180087767757</v>
+        <v>5.115636077597181</v>
       </c>
       <c r="E15">
-        <v>0.71879</v>
+        <v>0.7766200000000001</v>
       </c>
       <c r="F15">
-        <v>0.7517900000000001</v>
+        <v>0.8096200000000001</v>
       </c>
       <c r="G15">
         <v>0.204</v>
@@ -2511,37 +2511,37 @@
         <v>0.057</v>
       </c>
       <c r="M15">
-        <v>0.177272082</v>
+        <v>0.190908396</v>
       </c>
       <c r="N15">
-        <v>-0.120272082</v>
+        <v>-0.133908396</v>
       </c>
       <c r="O15">
-        <v>-0.02886529968</v>
+        <v>-0.03213801504000001</v>
       </c>
       <c r="P15">
-        <v>-0.09140678232000002</v>
+        <v>-0.10177038096</v>
       </c>
       <c r="Q15">
-        <v>-0.09240678232000002</v>
+        <v>-0.10277038096</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.3177010914297037</v>
+        <v>0.3208627320277235</v>
       </c>
       <c r="T15">
-        <v>1.335951259748545</v>
+        <v>1.351485576722366</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.07716951166625323</v>
+        <v>0.07165740369009227</v>
       </c>
       <c r="W15">
-        <v>0.2176034291490975</v>
+        <v>0.2189031842098762</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.3215396319427217</v>
+        <v>0.2985725153753844</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.3065883953332249</v>
+        <v>0.3084883953332249</v>
       </c>
       <c r="C16">
-        <v>4.510016077597181</v>
+        <v>4.415185171884902</v>
       </c>
       <c r="D16">
-        <v>5.115636077597181</v>
+        <v>5.078635171884902</v>
       </c>
       <c r="E16">
-        <v>0.7766200000000001</v>
+        <v>0.8344500000000001</v>
       </c>
       <c r="F16">
-        <v>0.8096200000000001</v>
+        <v>0.8674500000000002</v>
       </c>
       <c r="G16">
         <v>0.204</v>
@@ -2593,37 +2593,37 @@
         <v>0.057</v>
       </c>
       <c r="M16">
-        <v>0.190908396</v>
+        <v>0.20454471</v>
       </c>
       <c r="N16">
-        <v>-0.133908396</v>
+        <v>-0.1475447100000001</v>
       </c>
       <c r="O16">
-        <v>-0.03213801504000001</v>
+        <v>-0.03541073040000001</v>
       </c>
       <c r="P16">
-        <v>-0.10177038096</v>
+        <v>-0.1121339796</v>
       </c>
       <c r="Q16">
-        <v>-0.10277038096</v>
+        <v>-0.1131339796</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.3208627320277235</v>
+        <v>0.3240987641692261</v>
       </c>
       <c r="T16">
-        <v>1.351485576722366</v>
+        <v>1.367385407036746</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.07165740369009227</v>
+        <v>0.06688024344408612</v>
       </c>
       <c r="W16">
-        <v>0.2189031842098762</v>
+        <v>0.2200296385958845</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.2985725153753844</v>
+        <v>0.2786676810170254</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.3084883953332249</v>
+        <v>0.3103883953332249</v>
       </c>
       <c r="C17">
-        <v>4.415185171884902</v>
+        <v>4.320885670588638</v>
       </c>
       <c r="D17">
-        <v>5.078635171884902</v>
+        <v>5.042165670588639</v>
       </c>
       <c r="E17">
-        <v>0.83445</v>
+        <v>0.8922800000000001</v>
       </c>
       <c r="F17">
-        <v>0.8674500000000001</v>
+        <v>0.9252800000000001</v>
       </c>
       <c r="G17">
         <v>0.204</v>
@@ -2675,37 +2675,37 @@
         <v>0.057</v>
       </c>
       <c r="M17">
-        <v>0.20454471</v>
+        <v>0.218181024</v>
       </c>
       <c r="N17">
-        <v>-0.14754471</v>
+        <v>-0.161181024</v>
       </c>
       <c r="O17">
-        <v>-0.03541073040000001</v>
+        <v>-0.03868344576</v>
       </c>
       <c r="P17">
-        <v>-0.1121339796</v>
+        <v>-0.12249757824</v>
       </c>
       <c r="Q17">
-        <v>-0.1131339796</v>
+        <v>-0.12349757824</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.3240987641692261</v>
+        <v>0.3274118446950502</v>
       </c>
       <c r="T17">
-        <v>1.367385407036746</v>
+        <v>1.383663804739565</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.06688024344408613</v>
+        <v>0.06270022822883074</v>
       </c>
       <c r="W17">
-        <v>0.2200296385958845</v>
+        <v>0.2210152861836417</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.2786676810170255</v>
+        <v>0.2612509509534614</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.3103883953332249</v>
+        <v>0.3122883953332249</v>
       </c>
       <c r="C18">
-        <v>4.320885670588638</v>
+        <v>4.227106207340382</v>
       </c>
       <c r="D18">
-        <v>5.042165670588639</v>
+        <v>5.006216207340382</v>
       </c>
       <c r="E18">
-        <v>0.8922800000000001</v>
+        <v>0.9501100000000001</v>
       </c>
       <c r="F18">
-        <v>0.9252800000000001</v>
+        <v>0.9831100000000002</v>
       </c>
       <c r="G18">
         <v>0.204</v>
@@ -2757,37 +2757,37 @@
         <v>0.057</v>
       </c>
       <c r="M18">
-        <v>0.218181024</v>
+        <v>0.231817338</v>
       </c>
       <c r="N18">
-        <v>-0.161181024</v>
+        <v>-0.174817338</v>
       </c>
       <c r="O18">
-        <v>-0.03868344576</v>
+        <v>-0.04195616112000001</v>
       </c>
       <c r="P18">
-        <v>-0.12249757824</v>
+        <v>-0.13286117688</v>
       </c>
       <c r="Q18">
-        <v>-0.12349757824</v>
+        <v>-0.13386117688</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.3274118446950502</v>
+        <v>0.3308047584865569</v>
       </c>
       <c r="T18">
-        <v>1.383663804739565</v>
+        <v>1.400334452989439</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.06270022822883074</v>
+        <v>0.05901197950948776</v>
       </c>
       <c r="W18">
-        <v>0.2210152861836417</v>
+        <v>0.2218849752316628</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.2612509509534614</v>
+        <v>0.245883247956199</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.3122883953332249</v>
+        <v>0.3141883953332249</v>
       </c>
       <c r="C19">
-        <v>4.227106207340382</v>
+        <v>4.133835737635509</v>
       </c>
       <c r="D19">
-        <v>5.006216207340382</v>
+        <v>4.970775737635509</v>
       </c>
       <c r="E19">
-        <v>0.9501100000000001</v>
+        <v>1.00794</v>
       </c>
       <c r="F19">
-        <v>0.9831100000000002</v>
+        <v>1.04094</v>
       </c>
       <c r="G19">
         <v>0.204</v>
@@ -2839,37 +2839,37 @@
         <v>0.057</v>
       </c>
       <c r="M19">
-        <v>0.231817338</v>
+        <v>0.245453652</v>
       </c>
       <c r="N19">
-        <v>-0.174817338</v>
+        <v>-0.1884536520000001</v>
       </c>
       <c r="O19">
-        <v>-0.04195616112000001</v>
+        <v>-0.04522887648000001</v>
       </c>
       <c r="P19">
-        <v>-0.13286117688</v>
+        <v>-0.14322477552</v>
       </c>
       <c r="Q19">
-        <v>-0.13386117688</v>
+        <v>-0.14422477552</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.3308047584865569</v>
+        <v>0.3342804262729783</v>
       </c>
       <c r="T19">
-        <v>1.400334452989439</v>
+        <v>1.41741170241614</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.05901197950948776</v>
+        <v>0.05573353620340511</v>
       </c>
       <c r="W19">
-        <v>0.2218849752316628</v>
+        <v>0.2226580321632371</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.245883247956199</v>
+        <v>0.2322230675141879</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.314188395333225</v>
+        <v>0.3160883953332249</v>
       </c>
       <c r="C20">
-        <v>4.133835737635508</v>
+        <v>4.041063527520036</v>
       </c>
       <c r="D20">
-        <v>4.970775737635508</v>
+        <v>4.935833527520036</v>
       </c>
       <c r="E20">
-        <v>1.00794</v>
+        <v>1.06577</v>
       </c>
       <c r="F20">
-        <v>1.04094</v>
+        <v>1.09877</v>
       </c>
       <c r="G20">
         <v>0.204</v>
@@ -2921,37 +2921,37 @@
         <v>0.057</v>
       </c>
       <c r="M20">
-        <v>0.245453652</v>
+        <v>0.259089966</v>
       </c>
       <c r="N20">
-        <v>-0.188453652</v>
+        <v>-0.202089966</v>
       </c>
       <c r="O20">
-        <v>-0.04522887648</v>
+        <v>-0.04850159184</v>
       </c>
       <c r="P20">
-        <v>-0.14322477552</v>
+        <v>-0.15358837416</v>
       </c>
       <c r="Q20">
-        <v>-0.14422477552</v>
+        <v>-0.15458837416</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.3342804262729783</v>
+        <v>0.3378419130170892</v>
       </c>
       <c r="T20">
-        <v>1.41741170241614</v>
+        <v>1.434910612322512</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.05573353620340511</v>
+        <v>0.05280019219269958</v>
       </c>
       <c r="W20">
-        <v>0.2226580321632371</v>
+        <v>0.2233497146809614</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.232223067514188</v>
+        <v>0.220000800802915</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.3160883953332249</v>
+        <v>0.3179883953332249</v>
       </c>
       <c r="C21">
-        <v>4.041063527520036</v>
+        <v>3.948779142751697</v>
       </c>
       <c r="D21">
-        <v>4.935833527520036</v>
+        <v>4.901379142751697</v>
       </c>
       <c r="E21">
-        <v>1.06577</v>
+        <v>1.1236</v>
       </c>
       <c r="F21">
-        <v>1.09877</v>
+        <v>1.1566</v>
       </c>
       <c r="G21">
         <v>0.204</v>
@@ -3003,37 +3003,37 @@
         <v>0.057</v>
       </c>
       <c r="M21">
-        <v>0.259089966</v>
+        <v>0.27272628</v>
       </c>
       <c r="N21">
-        <v>-0.202089966</v>
+        <v>-0.21572628</v>
       </c>
       <c r="O21">
-        <v>-0.04850159184</v>
+        <v>-0.05177430720000001</v>
       </c>
       <c r="P21">
-        <v>-0.15358837416</v>
+        <v>-0.1639519728</v>
       </c>
       <c r="Q21">
-        <v>-0.15458837416</v>
+        <v>-0.1649519728</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.3378419130170892</v>
+        <v>0.3414924369298027</v>
       </c>
       <c r="T21">
-        <v>1.434910612322512</v>
+        <v>1.452846994976543</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.05280019219269958</v>
+        <v>0.05016018258306459</v>
       </c>
       <c r="W21">
-        <v>0.2233497146809614</v>
+        <v>0.2239722289469134</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.220000800802915</v>
+        <v>0.2090007607627691</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.3179883953332249</v>
+        <v>0.3198883953332249</v>
       </c>
       <c r="C22">
-        <v>3.948779142751697</v>
+        <v>3.85697243841182</v>
       </c>
       <c r="D22">
-        <v>4.901379142751697</v>
+        <v>4.86740243841182</v>
       </c>
       <c r="E22">
-        <v>1.1236</v>
+        <v>1.18143</v>
       </c>
       <c r="F22">
-        <v>1.1566</v>
+        <v>1.21443</v>
       </c>
       <c r="G22">
         <v>0.204</v>
@@ -3085,37 +3085,37 @@
         <v>0.057</v>
       </c>
       <c r="M22">
-        <v>0.27272628</v>
+        <v>0.286362594</v>
       </c>
       <c r="N22">
-        <v>-0.21572628</v>
+        <v>-0.229362594</v>
       </c>
       <c r="O22">
-        <v>-0.05177430720000001</v>
+        <v>-0.05504702256000001</v>
       </c>
       <c r="P22">
-        <v>-0.1639519728</v>
+        <v>-0.17431557144</v>
       </c>
       <c r="Q22">
-        <v>-0.1649519728</v>
+        <v>-0.17531557144</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.3414924369298027</v>
+        <v>0.3452353791694205</v>
       </c>
       <c r="T22">
-        <v>1.452846994976543</v>
+        <v>1.471237463267385</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.05016018258306459</v>
+        <v>0.04777160246006153</v>
       </c>
       <c r="W22">
-        <v>0.2239722289469134</v>
+        <v>0.2245354561399175</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.2090007607627691</v>
+        <v>0.1990483435835897</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.3198883953332249</v>
+        <v>0.321788395333225</v>
       </c>
       <c r="C23">
-        <v>3.85697243841182</v>
+        <v>3.765633548946315</v>
       </c>
       <c r="D23">
-        <v>4.86740243841182</v>
+        <v>4.833893548946316</v>
       </c>
       <c r="E23">
-        <v>1.18143</v>
+        <v>1.23926</v>
       </c>
       <c r="F23">
-        <v>1.21443</v>
+        <v>1.27226</v>
       </c>
       <c r="G23">
         <v>0.204</v>
@@ -3167,37 +3167,37 @@
         <v>0.057</v>
       </c>
       <c r="M23">
-        <v>0.286362594</v>
+        <v>0.2999989080000001</v>
       </c>
       <c r="N23">
-        <v>-0.229362594</v>
+        <v>-0.2429989080000001</v>
       </c>
       <c r="O23">
-        <v>-0.05504702256000001</v>
+        <v>-0.05831973792000002</v>
       </c>
       <c r="P23">
-        <v>-0.17431557144</v>
+        <v>-0.1846791700800001</v>
       </c>
       <c r="Q23">
-        <v>-0.17531557144</v>
+        <v>-0.1856791700800001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.3452353791694205</v>
+        <v>0.3490742942869772</v>
       </c>
       <c r="T23">
-        <v>1.471237463267385</v>
+        <v>1.490099482027224</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.04777160246006153</v>
+        <v>0.04560016598460417</v>
       </c>
       <c r="W23">
-        <v>0.2245354561399175</v>
+        <v>0.2250474808608303</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.1990483435835897</v>
+        <v>0.1900006916025174</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.321788395333225</v>
+        <v>0.3236883953332249</v>
       </c>
       <c r="C24">
-        <v>3.765633548946315</v>
+        <v>3.674752878615212</v>
       </c>
       <c r="D24">
-        <v>4.833893548946316</v>
+        <v>4.800842878615213</v>
       </c>
       <c r="E24">
-        <v>1.23926</v>
+        <v>1.29709</v>
       </c>
       <c r="F24">
-        <v>1.27226</v>
+        <v>1.33009</v>
       </c>
       <c r="G24">
         <v>0.204</v>
@@ -3249,37 +3249,37 @@
         <v>0.057</v>
       </c>
       <c r="M24">
-        <v>0.2999989080000001</v>
+        <v>0.313635222</v>
       </c>
       <c r="N24">
-        <v>-0.2429989080000001</v>
+        <v>-0.2566352220000001</v>
       </c>
       <c r="O24">
-        <v>-0.05831973792000002</v>
+        <v>-0.06159245328000001</v>
       </c>
       <c r="P24">
-        <v>-0.1846791700800001</v>
+        <v>-0.19504276872</v>
       </c>
       <c r="Q24">
-        <v>-0.1856791700800001</v>
+        <v>-0.19604276872</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.3490742942869772</v>
+        <v>0.3530129214855094</v>
       </c>
       <c r="T24">
-        <v>1.490099482027224</v>
+        <v>1.509451423352253</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.04560016598460417</v>
+        <v>0.04361755007223008</v>
       </c>
       <c r="W24">
-        <v>0.2250474808608303</v>
+        <v>0.2255149816929682</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.1900006916025174</v>
+        <v>0.1817397919676254</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.3236883953332249</v>
+        <v>0.3255883953332249</v>
       </c>
       <c r="C25">
-        <v>3.674752878615212</v>
+        <v>3.584321092331312</v>
       </c>
       <c r="D25">
-        <v>4.800842878615213</v>
+        <v>4.768241092331313</v>
       </c>
       <c r="E25">
-        <v>1.29709</v>
+        <v>1.35492</v>
       </c>
       <c r="F25">
-        <v>1.33009</v>
+        <v>1.38792</v>
       </c>
       <c r="G25">
         <v>0.204</v>
@@ -3331,37 +3331,37 @@
         <v>0.057</v>
       </c>
       <c r="M25">
-        <v>0.313635222</v>
+        <v>0.3272715360000001</v>
       </c>
       <c r="N25">
-        <v>-0.2566352220000001</v>
+        <v>-0.2702715360000001</v>
       </c>
       <c r="O25">
-        <v>-0.06159245328000001</v>
+        <v>-0.06486516864000003</v>
       </c>
       <c r="P25">
-        <v>-0.19504276872</v>
+        <v>-0.2054063673600001</v>
       </c>
       <c r="Q25">
-        <v>-0.19604276872</v>
+        <v>-0.2064063673600001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.3530129214855094</v>
+        <v>0.3570551967682135</v>
       </c>
       <c r="T25">
-        <v>1.509451423352253</v>
+        <v>1.529312626291098</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.04361755007223008</v>
+        <v>0.04180015215255382</v>
       </c>
       <c r="W25">
-        <v>0.2255149816929682</v>
+        <v>0.2259435241224278</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.1817397919676254</v>
+        <v>0.1741673006356409</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.3255883953332249</v>
+        <v>0.3274883953332249</v>
       </c>
       <c r="C26">
-        <v>3.584321092331312</v>
+        <v>3.494329106869639</v>
       </c>
       <c r="D26">
-        <v>4.768241092331313</v>
+        <v>4.73607910686964</v>
       </c>
       <c r="E26">
-        <v>1.35492</v>
+        <v>1.41275</v>
       </c>
       <c r="F26">
-        <v>1.38792</v>
+        <v>1.44575</v>
       </c>
       <c r="G26">
         <v>0.204</v>
@@ -3413,37 +3413,37 @@
         <v>0.057</v>
       </c>
       <c r="M26">
-        <v>0.327271536</v>
+        <v>0.34090785</v>
       </c>
       <c r="N26">
-        <v>-0.270271536</v>
+        <v>-0.28390785</v>
       </c>
       <c r="O26">
-        <v>-0.06486516864000001</v>
+        <v>-0.068137884</v>
       </c>
       <c r="P26">
-        <v>-0.20540636736</v>
+        <v>-0.215769966</v>
       </c>
       <c r="Q26">
-        <v>-0.20640636736</v>
+        <v>-0.216769966</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.3570551967682135</v>
+        <v>0.3612052660584563</v>
       </c>
       <c r="T26">
-        <v>1.529312626291098</v>
+        <v>1.549703461308312</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.04180015215255383</v>
+        <v>0.04012814606645168</v>
       </c>
       <c r="W26">
-        <v>0.2259435241224278</v>
+        <v>0.2263377831575307</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.1741673006356409</v>
+        <v>0.1672006086102154</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.3274883953332249</v>
+        <v>0.3293883953332249</v>
       </c>
       <c r="C27">
-        <v>3.494329106869639</v>
+        <v>3.404768082430226</v>
       </c>
       <c r="D27">
-        <v>4.73607910686964</v>
+        <v>4.704348082430227</v>
       </c>
       <c r="E27">
-        <v>1.41275</v>
+        <v>1.47058</v>
       </c>
       <c r="F27">
-        <v>1.44575</v>
+        <v>1.50358</v>
       </c>
       <c r="G27">
         <v>0.204</v>
@@ -3495,37 +3495,37 @@
         <v>0.057</v>
       </c>
       <c r="M27">
-        <v>0.34090785</v>
+        <v>0.3545441640000001</v>
       </c>
       <c r="N27">
-        <v>-0.28390785</v>
+        <v>-0.2975441640000001</v>
       </c>
       <c r="O27">
-        <v>-0.068137884</v>
+        <v>-0.07141059936000001</v>
       </c>
       <c r="P27">
-        <v>-0.215769966</v>
+        <v>-0.2261335646400001</v>
       </c>
       <c r="Q27">
-        <v>-0.216769966</v>
+        <v>-0.2271335646400001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.3612052660584563</v>
+        <v>0.3654674993835705</v>
       </c>
       <c r="T27">
-        <v>1.549703461308312</v>
+        <v>1.570645399974641</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.04012814606645168</v>
+        <v>0.03858475583312661</v>
       </c>
       <c r="W27">
-        <v>0.2263377831575307</v>
+        <v>0.2267017145745488</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.1672006086102154</v>
+        <v>0.1607698159713609</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.3293883953332249</v>
+        <v>0.331288395333225</v>
       </c>
       <c r="C28">
-        <v>3.404768082430226</v>
+        <v>3.315629414537842</v>
       </c>
       <c r="D28">
-        <v>4.704348082430227</v>
+        <v>4.673039414537842</v>
       </c>
       <c r="E28">
-        <v>1.47058</v>
+        <v>1.52841</v>
       </c>
       <c r="F28">
-        <v>1.50358</v>
+        <v>1.56141</v>
       </c>
       <c r="G28">
         <v>0.204</v>
@@ -3577,37 +3577,37 @@
         <v>0.057</v>
       </c>
       <c r="M28">
-        <v>0.3545441640000001</v>
+        <v>0.368180478</v>
       </c>
       <c r="N28">
-        <v>-0.2975441640000001</v>
+        <v>-0.311180478</v>
       </c>
       <c r="O28">
-        <v>-0.07141059936000001</v>
+        <v>-0.07468331472</v>
       </c>
       <c r="P28">
-        <v>-0.2261335646400001</v>
+        <v>-0.23649716328</v>
       </c>
       <c r="Q28">
-        <v>-0.2271335646400001</v>
+        <v>-0.23749716328</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.3654674993835705</v>
+        <v>0.3698465062244414</v>
       </c>
       <c r="T28">
-        <v>1.570645399974641</v>
+        <v>1.592161090385253</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.03858475583312661</v>
+        <v>0.03715569080227007</v>
       </c>
       <c r="W28">
-        <v>0.2267017145745488</v>
+        <v>0.2270386881088247</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.1607698159713609</v>
+        <v>0.1548153783427919</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.331288395333225</v>
+        <v>0.3331883953332249</v>
       </c>
       <c r="C29">
-        <v>3.315629414537842</v>
+        <v>3.226904726263019</v>
       </c>
       <c r="D29">
-        <v>4.673039414537842</v>
+        <v>4.64214472626302</v>
       </c>
       <c r="E29">
-        <v>1.52841</v>
+        <v>1.58624</v>
       </c>
       <c r="F29">
-        <v>1.56141</v>
+        <v>1.61924</v>
       </c>
       <c r="G29">
         <v>0.204</v>
@@ -3659,37 +3659,37 @@
         <v>0.057</v>
       </c>
       <c r="M29">
-        <v>0.368180478</v>
+        <v>0.3818167920000001</v>
       </c>
       <c r="N29">
-        <v>-0.311180478</v>
+        <v>-0.3248167920000001</v>
       </c>
       <c r="O29">
-        <v>-0.07468331472</v>
+        <v>-0.07795603008000002</v>
       </c>
       <c r="P29">
-        <v>-0.23649716328</v>
+        <v>-0.2468607619200001</v>
       </c>
       <c r="Q29">
-        <v>-0.23749716328</v>
+        <v>-0.2478607619200001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.3698465062244414</v>
+        <v>0.3743471521442254</v>
       </c>
       <c r="T29">
-        <v>1.592161090385253</v>
+        <v>1.614274438862826</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.03715569080227007</v>
+        <v>0.03582870184504613</v>
       </c>
       <c r="W29">
-        <v>0.2270386881088247</v>
+        <v>0.2273515921049381</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.1548153783427919</v>
+        <v>0.1492862576876922</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.3331883953332249</v>
+        <v>0.335088395333225</v>
       </c>
       <c r="C30">
-        <v>3.226904726263019</v>
+        <v>3.138585860749624</v>
       </c>
       <c r="D30">
-        <v>4.64214472626302</v>
+        <v>4.611655860749625</v>
       </c>
       <c r="E30">
-        <v>1.58624</v>
+        <v>1.64407</v>
       </c>
       <c r="F30">
-        <v>1.61924</v>
+        <v>1.67707</v>
       </c>
       <c r="G30">
         <v>0.204</v>
@@ -3741,37 +3741,37 @@
         <v>0.057</v>
       </c>
       <c r="M30">
-        <v>0.3818167920000001</v>
+        <v>0.3954531060000001</v>
       </c>
       <c r="N30">
-        <v>-0.3248167920000001</v>
+        <v>-0.3384531060000001</v>
       </c>
       <c r="O30">
-        <v>-0.07795603008000002</v>
+        <v>-0.08122874544000003</v>
       </c>
       <c r="P30">
-        <v>-0.2468607619200001</v>
+        <v>-0.2572243605600001</v>
       </c>
       <c r="Q30">
-        <v>-0.2478607619200001</v>
+        <v>-0.2582243605600001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.3743471521442254</v>
+        <v>0.3789745768223131</v>
       </c>
       <c r="T30">
-        <v>1.614274438862826</v>
+        <v>1.637010698565119</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.03582870184504613</v>
+        <v>0.03459322936763075</v>
       </c>
       <c r="W30">
-        <v>0.2273515921049381</v>
+        <v>0.2276429165151127</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.1492862576876922</v>
+        <v>0.1441384556984614</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.3350883953332249</v>
+        <v>0.3369883953332249</v>
       </c>
       <c r="C31">
-        <v>3.138585860749627</v>
+        <v>3.050664874035004</v>
       </c>
       <c r="D31">
-        <v>4.611655860749627</v>
+        <v>4.581564874035005</v>
       </c>
       <c r="E31">
-        <v>1.64407</v>
+        <v>1.7019</v>
       </c>
       <c r="F31">
-        <v>1.67707</v>
+        <v>1.7349</v>
       </c>
       <c r="G31">
         <v>0.204</v>
@@ -3823,37 +3823,37 @@
         <v>0.057</v>
       </c>
       <c r="M31">
-        <v>0.3954531060000001</v>
+        <v>0.40908942</v>
       </c>
       <c r="N31">
-        <v>-0.3384531060000001</v>
+        <v>-0.35208942</v>
       </c>
       <c r="O31">
-        <v>-0.08122874544000001</v>
+        <v>-0.08450146080000001</v>
       </c>
       <c r="P31">
-        <v>-0.25722436056</v>
+        <v>-0.2675879592</v>
       </c>
       <c r="Q31">
-        <v>-0.25822436056</v>
+        <v>-0.2685879592</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.3789745768223129</v>
+        <v>0.3837342136340604</v>
       </c>
       <c r="T31">
-        <v>1.637010698565119</v>
+        <v>1.660396565687478</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.03459322936763076</v>
+        <v>0.03344012172204307</v>
       </c>
       <c r="W31">
-        <v>0.2276429165151127</v>
+        <v>0.2279148192979423</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.1441384556984615</v>
+        <v>0.1393338405085127</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.3369883953332249</v>
+        <v>0.3388883953332249</v>
       </c>
       <c r="C32">
-        <v>3.050664874035004</v>
+        <v>2.963134028149347</v>
       </c>
       <c r="D32">
-        <v>4.581564874035005</v>
+        <v>4.551864028149348</v>
       </c>
       <c r="E32">
-        <v>1.7019</v>
+        <v>1.75973</v>
       </c>
       <c r="F32">
-        <v>1.7349</v>
+        <v>1.79273</v>
       </c>
       <c r="G32">
         <v>0.204</v>
@@ -3905,37 +3905,37 @@
         <v>0.057</v>
       </c>
       <c r="M32">
-        <v>0.40908942</v>
+        <v>0.4227257340000001</v>
       </c>
       <c r="N32">
-        <v>-0.35208942</v>
+        <v>-0.3657257340000001</v>
       </c>
       <c r="O32">
-        <v>-0.08450146080000001</v>
+        <v>-0.08777417616000002</v>
       </c>
       <c r="P32">
-        <v>-0.2675879592</v>
+        <v>-0.27795155784</v>
       </c>
       <c r="Q32">
-        <v>-0.2685879592</v>
+        <v>-0.27895155784</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.3837342136340604</v>
+        <v>0.3886318109331047</v>
       </c>
       <c r="T32">
-        <v>1.660396565687478</v>
+        <v>1.684460284030775</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.03344012172204307</v>
+        <v>0.03236140811810619</v>
       </c>
       <c r="W32">
-        <v>0.2279148192979423</v>
+        <v>0.2281691799657506</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.1393338405085127</v>
+        <v>0.1348392004921091</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.3388883953332249</v>
+        <v>0.3407883953332249</v>
       </c>
       <c r="C33">
-        <v>2.963134028149347</v>
+        <v>2.875985784481782</v>
       </c>
       <c r="D33">
-        <v>4.551864028149348</v>
+        <v>4.522545784481783</v>
       </c>
       <c r="E33">
-        <v>1.75973</v>
+        <v>1.81756</v>
       </c>
       <c r="F33">
-        <v>1.79273</v>
+        <v>1.85056</v>
       </c>
       <c r="G33">
         <v>0.204</v>
@@ -3987,37 +3987,37 @@
         <v>0.057</v>
       </c>
       <c r="M33">
-        <v>0.4227257340000001</v>
+        <v>0.4363620480000001</v>
       </c>
       <c r="N33">
-        <v>-0.3657257340000001</v>
+        <v>-0.3793620480000001</v>
       </c>
       <c r="O33">
-        <v>-0.08777417616000002</v>
+        <v>-0.09104689152000001</v>
       </c>
       <c r="P33">
-        <v>-0.27795155784</v>
+        <v>-0.2883151564800001</v>
       </c>
       <c r="Q33">
-        <v>-0.27895155784</v>
+        <v>-0.2893151564800001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.3886318109331047</v>
+        <v>0.3936734552115327</v>
       </c>
       <c r="T33">
-        <v>1.684460284030775</v>
+        <v>1.709231758795933</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.03236140811810619</v>
+        <v>0.03135011411441537</v>
       </c>
       <c r="W33">
-        <v>0.2281691799657506</v>
+        <v>0.2284076430918209</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.1348392004921091</v>
+        <v>0.1306254754767308</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.3407883953332249</v>
+        <v>0.3426883953332249</v>
       </c>
       <c r="C34">
-        <v>2.875985784481782</v>
+        <v>2.789212797401162</v>
       </c>
       <c r="D34">
-        <v>4.522545784481783</v>
+        <v>4.493602797401162</v>
       </c>
       <c r="E34">
-        <v>1.81756</v>
+        <v>1.87539</v>
       </c>
       <c r="F34">
-        <v>1.85056</v>
+        <v>1.90839</v>
       </c>
       <c r="G34">
         <v>0.204</v>
@@ -4069,37 +4069,37 @@
         <v>0.057</v>
       </c>
       <c r="M34">
-        <v>0.4363620480000001</v>
+        <v>0.4499983620000001</v>
       </c>
       <c r="N34">
-        <v>-0.3793620480000001</v>
+        <v>-0.3929983620000001</v>
       </c>
       <c r="O34">
-        <v>-0.09104689152000001</v>
+        <v>-0.09431960688000002</v>
       </c>
       <c r="P34">
-        <v>-0.2883151564800001</v>
+        <v>-0.2986787551200001</v>
       </c>
       <c r="Q34">
-        <v>-0.2893151564800001</v>
+        <v>-0.2996787551200001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.3936734552115327</v>
+        <v>0.3988655963340929</v>
       </c>
       <c r="T34">
-        <v>1.709231758795933</v>
+        <v>1.734742680569007</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.03135011411441537</v>
+        <v>0.03040011065640278</v>
       </c>
       <c r="W34">
-        <v>0.2284076430918209</v>
+        <v>0.2286316539072202</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.1306254754767308</v>
+        <v>0.1266671277350115</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.3426883953332249</v>
+        <v>0.3445883953332249</v>
       </c>
       <c r="C35">
-        <v>2.789212797401162</v>
+        <v>2.70280790812027</v>
       </c>
       <c r="D35">
-        <v>4.493602797401162</v>
+        <v>4.465027908120271</v>
       </c>
       <c r="E35">
-        <v>1.87539</v>
+        <v>1.93322</v>
       </c>
       <c r="F35">
-        <v>1.90839</v>
+        <v>1.96622</v>
       </c>
       <c r="G35">
         <v>0.204</v>
@@ -4151,37 +4151,37 @@
         <v>0.057</v>
       </c>
       <c r="M35">
-        <v>0.4499983620000001</v>
+        <v>0.4636346760000001</v>
       </c>
       <c r="N35">
-        <v>-0.3929983620000001</v>
+        <v>-0.4066346760000001</v>
       </c>
       <c r="O35">
-        <v>-0.09431960688000002</v>
+        <v>-0.09759232224000002</v>
       </c>
       <c r="P35">
-        <v>-0.2986787551200001</v>
+        <v>-0.3090423537600001</v>
       </c>
       <c r="Q35">
-        <v>-0.2996787551200001</v>
+        <v>-0.3100423537600001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.3988655963340929</v>
+        <v>0.4042150750664277</v>
       </c>
       <c r="T35">
-        <v>1.734742680569007</v>
+        <v>1.761026660577628</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.03040011065640278</v>
+        <v>0.02950598975474388</v>
       </c>
       <c r="W35">
-        <v>0.2286316539072202</v>
+        <v>0.2288424876158314</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.1266671277350115</v>
+        <v>0.1229416239780995</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.3445883953332249</v>
+        <v>0.3464883953332249</v>
       </c>
       <c r="C36">
-        <v>2.70280790812027</v>
+        <v>2.616764138792635</v>
       </c>
       <c r="D36">
-        <v>4.465027908120271</v>
+        <v>4.436814138792635</v>
       </c>
       <c r="E36">
-        <v>1.93322</v>
+        <v>1.99105</v>
       </c>
       <c r="F36">
-        <v>1.96622</v>
+        <v>2.02405</v>
       </c>
       <c r="G36">
         <v>0.204</v>
@@ -4233,37 +4233,37 @@
         <v>0.057</v>
       </c>
       <c r="M36">
-        <v>0.4636346760000001</v>
+        <v>0.4772709900000001</v>
       </c>
       <c r="N36">
-        <v>-0.4066346760000001</v>
+        <v>-0.4202709900000001</v>
       </c>
       <c r="O36">
-        <v>-0.09759232224000002</v>
+        <v>-0.1008650376</v>
       </c>
       <c r="P36">
-        <v>-0.3090423537600001</v>
+        <v>-0.3194059524000001</v>
       </c>
       <c r="Q36">
-        <v>-0.3100423537600001</v>
+        <v>-0.3204059524000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.4042150750664277</v>
+        <v>0.4097291531443727</v>
       </c>
       <c r="T36">
-        <v>1.761026660577628</v>
+        <v>1.788119378432669</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.02950598975474388</v>
+        <v>0.02866296147603691</v>
       </c>
       <c r="W36">
-        <v>0.2288424876158314</v>
+        <v>0.2290412736839505</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1229416239780995</v>
+        <v>0.1194290061501537</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.3464883953332249</v>
+        <v>0.3483883953332249</v>
       </c>
       <c r="C37">
-        <v>2.616764138792635</v>
+        <v>2.531074686831754</v>
       </c>
       <c r="D37">
-        <v>4.436814138792635</v>
+        <v>4.408954686831755</v>
       </c>
       <c r="E37">
-        <v>1.99105</v>
+        <v>2.04888</v>
       </c>
       <c r="F37">
-        <v>2.02405</v>
+        <v>2.08188</v>
       </c>
       <c r="G37">
         <v>0.204</v>
@@ -4315,37 +4315,37 @@
         <v>0.057</v>
       </c>
       <c r="M37">
-        <v>0.4772709900000001</v>
+        <v>0.4909073040000001</v>
       </c>
       <c r="N37">
-        <v>-0.4202709900000001</v>
+        <v>-0.4339073040000001</v>
       </c>
       <c r="O37">
-        <v>-0.1008650376</v>
+        <v>-0.10413775296</v>
       </c>
       <c r="P37">
-        <v>-0.3194059524000001</v>
+        <v>-0.3297695510400001</v>
       </c>
       <c r="Q37">
-        <v>-0.3204059524000001</v>
+        <v>-0.3307695510400001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.4097291531443727</v>
+        <v>0.4154155461622535</v>
       </c>
       <c r="T37">
-        <v>1.788119378432669</v>
+        <v>1.816058743720679</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.02866296147603691</v>
+        <v>0.02786676810170255</v>
       </c>
       <c r="W37">
-        <v>0.2290412736839505</v>
+        <v>0.2292290160816186</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1194290061501537</v>
+        <v>0.1161115337570939</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.3483883953332249</v>
+        <v>0.3502883953332249</v>
       </c>
       <c r="C38">
-        <v>2.531074686831754</v>
+        <v>2.445732919443008</v>
       </c>
       <c r="D38">
-        <v>4.408954686831754</v>
+        <v>4.381442919443009</v>
       </c>
       <c r="E38">
-        <v>2.04888</v>
+        <v>2.10671</v>
       </c>
       <c r="F38">
-        <v>2.08188</v>
+        <v>2.13971</v>
       </c>
       <c r="G38">
         <v>0.204</v>
@@ -4397,37 +4397,37 @@
         <v>0.057</v>
       </c>
       <c r="M38">
-        <v>0.490907304</v>
+        <v>0.504543618</v>
       </c>
       <c r="N38">
-        <v>-0.433907304</v>
+        <v>-0.447543618</v>
       </c>
       <c r="O38">
-        <v>-0.10413775296</v>
+        <v>-0.10741046832</v>
       </c>
       <c r="P38">
-        <v>-0.32976955104</v>
+        <v>-0.34013314968</v>
       </c>
       <c r="Q38">
-        <v>-0.33076955104</v>
+        <v>-0.34113314968</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.4154155461622535</v>
+        <v>0.4212824595934003</v>
       </c>
       <c r="T38">
-        <v>1.816058743720679</v>
+        <v>1.844885072986086</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.02786676810170256</v>
+        <v>0.02711361220706195</v>
       </c>
       <c r="W38">
-        <v>0.2292290160816186</v>
+        <v>0.2294066102415748</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1161115337570939</v>
+        <v>0.1129733841960915</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.3502883953332249</v>
+        <v>0.3521883953332249</v>
       </c>
       <c r="C39">
-        <v>2.445732919443008</v>
+        <v>2.360732368359022</v>
       </c>
       <c r="D39">
-        <v>4.381442919443009</v>
+        <v>4.354272368359022</v>
       </c>
       <c r="E39">
-        <v>2.10671</v>
+        <v>2.16454</v>
       </c>
       <c r="F39">
-        <v>2.13971</v>
+        <v>2.19754</v>
       </c>
       <c r="G39">
         <v>0.204</v>
@@ -4479,37 +4479,37 @@
         <v>0.057</v>
       </c>
       <c r="M39">
-        <v>0.504543618</v>
+        <v>0.518179932</v>
       </c>
       <c r="N39">
-        <v>-0.447543618</v>
+        <v>-0.461179932</v>
       </c>
       <c r="O39">
-        <v>-0.10741046832</v>
+        <v>-0.11068318368</v>
       </c>
       <c r="P39">
-        <v>-0.34013314968</v>
+        <v>-0.35049674832</v>
       </c>
       <c r="Q39">
-        <v>-0.34113314968</v>
+        <v>-0.35149674832</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.4212824595934003</v>
+        <v>0.4273386282965197</v>
       </c>
       <c r="T39">
-        <v>1.844885072986086</v>
+        <v>1.874641283840701</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.02711361220706195</v>
+        <v>0.02640009609634979</v>
       </c>
       <c r="W39">
-        <v>0.2294066102415748</v>
+        <v>0.2295748573404807</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1129733841960915</v>
+        <v>0.1100004004014574</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.3521883953332249</v>
+        <v>0.3540883953332249</v>
       </c>
       <c r="C40">
-        <v>2.360732368359022</v>
+        <v>2.276066724769714</v>
       </c>
       <c r="D40">
-        <v>4.354272368359022</v>
+        <v>4.327436724769714</v>
       </c>
       <c r="E40">
-        <v>2.16454</v>
+        <v>2.22237</v>
       </c>
       <c r="F40">
-        <v>2.19754</v>
+        <v>2.25537</v>
       </c>
       <c r="G40">
         <v>0.204</v>
@@ -4561,37 +4561,37 @@
         <v>0.057</v>
       </c>
       <c r="M40">
-        <v>0.518179932</v>
+        <v>0.531816246</v>
       </c>
       <c r="N40">
-        <v>-0.461179932</v>
+        <v>-0.474816246</v>
       </c>
       <c r="O40">
-        <v>-0.11068318368</v>
+        <v>-0.11395589904</v>
       </c>
       <c r="P40">
-        <v>-0.35049674832</v>
+        <v>-0.36086034696</v>
       </c>
       <c r="Q40">
-        <v>-0.35149674832</v>
+        <v>-0.36186034696</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.4273386282965197</v>
+        <v>0.4335933599079381</v>
       </c>
       <c r="T40">
-        <v>1.874641283840701</v>
+        <v>1.905373108165958</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.02640009609634979</v>
+        <v>0.02572317055541775</v>
       </c>
       <c r="W40">
-        <v>0.2295748573404807</v>
+        <v>0.2297344763830325</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1100004004014574</v>
+        <v>0.1071798773142406</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.3540883953332249</v>
+        <v>0.3559883953332249</v>
       </c>
       <c r="C41">
-        <v>2.276066724769714</v>
+        <v>2.191729834438663</v>
       </c>
       <c r="D41">
-        <v>4.327436724769714</v>
+        <v>4.300929834438663</v>
       </c>
       <c r="E41">
-        <v>2.22237</v>
+        <v>2.2802</v>
       </c>
       <c r="F41">
-        <v>2.25537</v>
+        <v>2.3132</v>
       </c>
       <c r="G41">
         <v>0.204</v>
@@ -4643,37 +4643,37 @@
         <v>0.057</v>
       </c>
       <c r="M41">
-        <v>0.531816246</v>
+        <v>0.5454525600000001</v>
       </c>
       <c r="N41">
-        <v>-0.474816246</v>
+        <v>-0.4884525600000001</v>
       </c>
       <c r="O41">
-        <v>-0.11395589904</v>
+        <v>-0.1172286144</v>
       </c>
       <c r="P41">
-        <v>-0.36086034696</v>
+        <v>-0.3712239456</v>
       </c>
       <c r="Q41">
-        <v>-0.36186034696</v>
+        <v>-0.3722239456000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.4335933599079381</v>
+        <v>0.4400565825730704</v>
       </c>
       <c r="T41">
-        <v>1.905373108165958</v>
+        <v>1.937129326635391</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.02572317055541775</v>
+        <v>0.0250800912915323</v>
       </c>
       <c r="W41">
-        <v>0.2297344763830325</v>
+        <v>0.2298861144734567</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1071798773142406</v>
+        <v>0.1045003803813845</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.3559883953332249</v>
+        <v>0.3578883953332249</v>
       </c>
       <c r="C42">
-        <v>2.191729834438663</v>
+        <v>2.107715692997876</v>
       </c>
       <c r="D42">
-        <v>4.300929834438663</v>
+        <v>4.274745692997876</v>
       </c>
       <c r="E42">
-        <v>2.2802</v>
+        <v>2.33803</v>
       </c>
       <c r="F42">
-        <v>2.3132</v>
+        <v>2.37103</v>
       </c>
       <c r="G42">
         <v>0.204</v>
@@ -4725,37 +4725,37 @@
         <v>0.057</v>
       </c>
       <c r="M42">
-        <v>0.5454525600000001</v>
+        <v>0.5590888740000001</v>
       </c>
       <c r="N42">
-        <v>-0.4884525600000001</v>
+        <v>-0.502088874</v>
       </c>
       <c r="O42">
-        <v>-0.1172286144</v>
+        <v>-0.12050132976</v>
       </c>
       <c r="P42">
-        <v>-0.3712239456</v>
+        <v>-0.38158754424</v>
       </c>
       <c r="Q42">
-        <v>-0.3722239456000001</v>
+        <v>-0.38258754424</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.4400565825730704</v>
+        <v>0.446738897531936</v>
       </c>
       <c r="T42">
-        <v>1.937129326635391</v>
+        <v>1.969962027086838</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.0250800912915323</v>
+        <v>0.02446838174783639</v>
       </c>
       <c r="W42">
-        <v>0.2298861144734567</v>
+        <v>0.2300303555838602</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1045003803813845</v>
+        <v>0.101951590615985</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.3578883953332249</v>
+        <v>0.3597883953332249</v>
       </c>
       <c r="C43">
-        <v>2.107715692997876</v>
+        <v>2.024018441413383</v>
       </c>
       <c r="D43">
-        <v>4.274745692997876</v>
+        <v>4.248878441413384</v>
       </c>
       <c r="E43">
-        <v>2.33803</v>
+        <v>2.39586</v>
       </c>
       <c r="F43">
-        <v>2.37103</v>
+        <v>2.42886</v>
       </c>
       <c r="G43">
         <v>0.204</v>
@@ -4807,37 +4807,37 @@
         <v>0.057</v>
       </c>
       <c r="M43">
-        <v>0.5590888740000001</v>
+        <v>0.5727251880000001</v>
       </c>
       <c r="N43">
-        <v>-0.502088874</v>
+        <v>-0.515725188</v>
       </c>
       <c r="O43">
-        <v>-0.12050132976</v>
+        <v>-0.12377404512</v>
       </c>
       <c r="P43">
-        <v>-0.38158754424</v>
+        <v>-0.39195114288</v>
       </c>
       <c r="Q43">
-        <v>-0.38258754424</v>
+        <v>-0.39295114288</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.446738897531936</v>
+        <v>0.4536516371445555</v>
       </c>
       <c r="T43">
-        <v>1.969962027086838</v>
+        <v>2.003926889622818</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.02446838174783639</v>
+        <v>0.02388580123003076</v>
       </c>
       <c r="W43">
-        <v>0.2300303555838602</v>
+        <v>0.2301677280699587</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.101951590615985</v>
+        <v>0.09952417179179496</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.3597883953332249</v>
+        <v>0.361688395333225</v>
       </c>
       <c r="C44">
-        <v>2.024018441413381</v>
+        <v>1.940632361614471</v>
       </c>
       <c r="D44">
-        <v>4.248878441413382</v>
+        <v>4.223322361614471</v>
       </c>
       <c r="E44">
-        <v>2.39586</v>
+        <v>2.45369</v>
       </c>
       <c r="F44">
-        <v>2.42886</v>
+        <v>2.48669</v>
       </c>
       <c r="G44">
         <v>0.204</v>
@@ -4889,37 +4889,37 @@
         <v>0.057</v>
       </c>
       <c r="M44">
-        <v>0.5727251880000001</v>
+        <v>0.5863615020000001</v>
       </c>
       <c r="N44">
-        <v>-0.515725188</v>
+        <v>-0.5293615020000001</v>
       </c>
       <c r="O44">
-        <v>-0.12377404512</v>
+        <v>-0.12704676048</v>
       </c>
       <c r="P44">
-        <v>-0.39195114288</v>
+        <v>-0.4023147415200001</v>
       </c>
       <c r="Q44">
-        <v>-0.39295114288</v>
+        <v>-0.4033147415200001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.4536516371445555</v>
+        <v>0.4608069290242847</v>
       </c>
       <c r="T44">
-        <v>2.003926889622818</v>
+        <v>2.039083501721464</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.02388580123003076</v>
+        <v>0.02333031748049516</v>
       </c>
       <c r="W44">
-        <v>0.2301677280699587</v>
+        <v>0.2302987111380992</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.09952417179179496</v>
+        <v>0.0972096561687299</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.361688395333225</v>
+        <v>0.363588395333225</v>
       </c>
       <c r="C45">
-        <v>1.940632361614471</v>
+        <v>1.857551872279727</v>
       </c>
       <c r="D45">
-        <v>4.223322361614471</v>
+        <v>4.198071872279727</v>
       </c>
       <c r="E45">
-        <v>2.45369</v>
+        <v>2.51152</v>
       </c>
       <c r="F45">
-        <v>2.48669</v>
+        <v>2.54452</v>
       </c>
       <c r="G45">
         <v>0.204</v>
@@ -4971,37 +4971,37 @@
         <v>0.057</v>
       </c>
       <c r="M45">
-        <v>0.5863615020000001</v>
+        <v>0.5999978160000001</v>
       </c>
       <c r="N45">
-        <v>-0.5293615020000001</v>
+        <v>-0.5429978160000001</v>
       </c>
       <c r="O45">
-        <v>-0.12704676048</v>
+        <v>-0.13031947584</v>
       </c>
       <c r="P45">
-        <v>-0.4023147415200001</v>
+        <v>-0.41267834016</v>
       </c>
       <c r="Q45">
-        <v>-0.4033147415200001</v>
+        <v>-0.41367834016</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.4608069290242847</v>
+        <v>0.4682177670425755</v>
       </c>
       <c r="T45">
-        <v>2.039083501721464</v>
+        <v>2.075495707109348</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.02333031748049516</v>
+        <v>0.02280008299230209</v>
       </c>
       <c r="W45">
-        <v>0.2302987111380992</v>
+        <v>0.2304237404304152</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.0972096561687299</v>
+        <v>0.09500034580125882</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.363588395333225</v>
+        <v>0.3654883953332249</v>
       </c>
       <c r="C46">
-        <v>1.857551872279727</v>
+        <v>1.774771524773314</v>
       </c>
       <c r="D46">
-        <v>4.198071872279727</v>
+        <v>4.173121524773315</v>
       </c>
       <c r="E46">
-        <v>2.51152</v>
+        <v>2.56935</v>
       </c>
       <c r="F46">
-        <v>2.54452</v>
+        <v>2.60235</v>
       </c>
       <c r="G46">
         <v>0.204</v>
@@ -5053,37 +5053,37 @@
         <v>0.057</v>
       </c>
       <c r="M46">
-        <v>0.5999978160000001</v>
+        <v>0.6136341300000001</v>
       </c>
       <c r="N46">
-        <v>-0.5429978160000001</v>
+        <v>-0.5566341300000001</v>
       </c>
       <c r="O46">
-        <v>-0.13031947584</v>
+        <v>-0.1335921912</v>
       </c>
       <c r="P46">
-        <v>-0.41267834016</v>
+        <v>-0.4230419388000001</v>
       </c>
       <c r="Q46">
-        <v>-0.41367834016</v>
+        <v>-0.4240419388000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.4682177670425755</v>
+        <v>0.4758980900797131</v>
       </c>
       <c r="T46">
-        <v>2.075495707109348</v>
+        <v>2.113231992693153</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.02280008299230209</v>
+        <v>0.02229341448136204</v>
       </c>
       <c r="W46">
-        <v>0.2304237404304152</v>
+        <v>0.2305432128652948</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.09500034580125882</v>
+        <v>0.09288922700567526</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.3654883953332249</v>
+        <v>0.3673883953332249</v>
       </c>
       <c r="C47">
-        <v>1.774771524773314</v>
+        <v>1.692285999225343</v>
       </c>
       <c r="D47">
-        <v>4.173121524773315</v>
+        <v>4.148465999225344</v>
       </c>
       <c r="E47">
-        <v>2.56935</v>
+        <v>2.627180000000001</v>
       </c>
       <c r="F47">
-        <v>2.60235</v>
+        <v>2.66018</v>
       </c>
       <c r="G47">
         <v>0.204</v>
@@ -5135,37 +5135,37 @@
         <v>0.057</v>
       </c>
       <c r="M47">
-        <v>0.6136341300000001</v>
+        <v>0.6272704440000001</v>
       </c>
       <c r="N47">
-        <v>-0.5566341300000001</v>
+        <v>-0.570270444</v>
       </c>
       <c r="O47">
-        <v>-0.1335921912</v>
+        <v>-0.13686490656</v>
       </c>
       <c r="P47">
-        <v>-0.4230419388000001</v>
+        <v>-0.43340553744</v>
       </c>
       <c r="Q47">
-        <v>-0.4240419388000001</v>
+        <v>-0.43440553744</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.4758980900797131</v>
+        <v>0.4838628695256337</v>
       </c>
       <c r="T47">
-        <v>2.113231992693153</v>
+        <v>2.152365918483767</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.02229341448136204</v>
+        <v>0.02180877503611504</v>
       </c>
       <c r="W47">
-        <v>0.2305432128652948</v>
+        <v>0.2306574908464841</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.09288922700567526</v>
+        <v>0.09086989598381279</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.3673883953332249</v>
+        <v>0.3692883953332249</v>
       </c>
       <c r="C48">
-        <v>1.692285999225343</v>
+        <v>1.610090100750348</v>
       </c>
       <c r="D48">
-        <v>4.148465999225344</v>
+        <v>4.124100100750349</v>
       </c>
       <c r="E48">
-        <v>2.627180000000001</v>
+        <v>2.685010000000001</v>
       </c>
       <c r="F48">
-        <v>2.66018</v>
+        <v>2.71801</v>
       </c>
       <c r="G48">
         <v>0.204</v>
@@ -5217,37 +5217,37 @@
         <v>0.057</v>
       </c>
       <c r="M48">
-        <v>0.6272704440000001</v>
+        <v>0.6409067580000002</v>
       </c>
       <c r="N48">
-        <v>-0.570270444</v>
+        <v>-0.5839067580000001</v>
       </c>
       <c r="O48">
-        <v>-0.13686490656</v>
+        <v>-0.14013762192</v>
       </c>
       <c r="P48">
-        <v>-0.43340553744</v>
+        <v>-0.4437691360800001</v>
       </c>
       <c r="Q48">
-        <v>-0.43440553744</v>
+        <v>-0.4447691360800001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.4838628695256337</v>
+        <v>0.4921282066864948</v>
       </c>
       <c r="T48">
-        <v>2.152365918483767</v>
+        <v>2.192976596191008</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.02180877503611504</v>
+        <v>0.02134475854598493</v>
       </c>
       <c r="W48">
-        <v>0.2306574908464841</v>
+        <v>0.2307669059348568</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.09086989598381279</v>
+        <v>0.08893649394160397</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.3692883953332249</v>
+        <v>0.3711883953332249</v>
       </c>
       <c r="C49">
-        <v>1.610090100750348</v>
+        <v>1.528178755798261</v>
       </c>
       <c r="D49">
-        <v>4.124100100750349</v>
+        <v>4.100018755798262</v>
       </c>
       <c r="E49">
-        <v>2.685010000000001</v>
+        <v>2.742840000000001</v>
       </c>
       <c r="F49">
-        <v>2.71801</v>
+        <v>2.775840000000001</v>
       </c>
       <c r="G49">
         <v>0.204</v>
@@ -5299,37 +5299,37 @@
         <v>0.057</v>
       </c>
       <c r="M49">
-        <v>0.6409067580000002</v>
+        <v>0.6545430720000002</v>
       </c>
       <c r="N49">
-        <v>-0.5839067580000001</v>
+        <v>-0.5975430720000001</v>
       </c>
       <c r="O49">
-        <v>-0.14013762192</v>
+        <v>-0.14341033728</v>
       </c>
       <c r="P49">
-        <v>-0.4437691360800001</v>
+        <v>-0.4541327347200001</v>
       </c>
       <c r="Q49">
-        <v>-0.4447691360800001</v>
+        <v>-0.4551327347200001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.4921282066864948</v>
+        <v>0.5007114414304658</v>
       </c>
       <c r="T49">
-        <v>2.192976596191008</v>
+        <v>2.235149223040835</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.02134475854598493</v>
+        <v>0.02090007607627691</v>
       </c>
       <c r="W49">
-        <v>0.2307669059348568</v>
+        <v>0.2308717620612139</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.08893649394160397</v>
+        <v>0.0870836503178205</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.3711883953332249</v>
+        <v>0.3730883953332249</v>
       </c>
       <c r="C50">
-        <v>1.528178755798261</v>
+        <v>1.446547008632476</v>
       </c>
       <c r="D50">
-        <v>4.100018755798262</v>
+        <v>4.076217008632477</v>
       </c>
       <c r="E50">
-        <v>2.74284</v>
+        <v>2.80067</v>
       </c>
       <c r="F50">
-        <v>2.77584</v>
+        <v>2.83367</v>
       </c>
       <c r="G50">
         <v>0.204</v>
@@ -5381,37 +5381,37 @@
         <v>0.057</v>
       </c>
       <c r="M50">
-        <v>0.6545430720000001</v>
+        <v>0.668179386</v>
       </c>
       <c r="N50">
-        <v>-0.597543072</v>
+        <v>-0.611179386</v>
       </c>
       <c r="O50">
-        <v>-0.14341033728</v>
+        <v>-0.14668305264</v>
       </c>
       <c r="P50">
-        <v>-0.45413273472</v>
+        <v>-0.46449633336</v>
       </c>
       <c r="Q50">
-        <v>-0.45513273472</v>
+        <v>-0.46549633336</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.5007114414304658</v>
+        <v>0.5096312736153769</v>
       </c>
       <c r="T50">
-        <v>2.235149223040835</v>
+        <v>2.278975678394577</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.02090007607627692</v>
+        <v>0.02047354391145494</v>
       </c>
       <c r="W50">
-        <v>0.2308717620612139</v>
+        <v>0.2309723383456789</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.0870836503178205</v>
+        <v>0.08530643296439566</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.3730883953332249</v>
+        <v>0.3749883953332249</v>
       </c>
       <c r="C51">
-        <v>1.446547008632476</v>
+        <v>1.365190017929898</v>
       </c>
       <c r="D51">
-        <v>4.076217008632477</v>
+        <v>4.052690017929899</v>
       </c>
       <c r="E51">
-        <v>2.80067</v>
+        <v>2.8585</v>
       </c>
       <c r="F51">
-        <v>2.83367</v>
+        <v>2.8915</v>
       </c>
       <c r="G51">
         <v>0.204</v>
@@ -5463,37 +5463,37 @@
         <v>0.057</v>
       </c>
       <c r="M51">
-        <v>0.668179386</v>
+        <v>0.6818157</v>
       </c>
       <c r="N51">
-        <v>-0.611179386</v>
+        <v>-0.6248157</v>
       </c>
       <c r="O51">
-        <v>-0.14668305264</v>
+        <v>-0.149955768</v>
       </c>
       <c r="P51">
-        <v>-0.46449633336</v>
+        <v>-0.474859932</v>
       </c>
       <c r="Q51">
-        <v>-0.46549633336</v>
+        <v>-0.475859932</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.5096312736153769</v>
+        <v>0.5189078990876844</v>
       </c>
       <c r="T51">
-        <v>2.278975678394577</v>
+        <v>2.324555191962469</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.02047354391145494</v>
+        <v>0.02006407303322584</v>
       </c>
       <c r="W51">
-        <v>0.2309723383456789</v>
+        <v>0.2310688915787653</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.08530643296439566</v>
+        <v>0.08360030430510779</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.3749883953332249</v>
+        <v>0.3768883953332249</v>
       </c>
       <c r="C52">
-        <v>1.365190017929898</v>
+        <v>1.284103053498036</v>
       </c>
       <c r="D52">
-        <v>4.052690017929899</v>
+        <v>4.029433053498036</v>
       </c>
       <c r="E52">
-        <v>2.8585</v>
+        <v>2.91633</v>
       </c>
       <c r="F52">
-        <v>2.8915</v>
+        <v>2.94933</v>
       </c>
       <c r="G52">
         <v>0.204</v>
@@ -5545,37 +5545,37 @@
         <v>0.057</v>
       </c>
       <c r="M52">
-        <v>0.6818157</v>
+        <v>0.6954520140000001</v>
       </c>
       <c r="N52">
-        <v>-0.6248157</v>
+        <v>-0.6384520140000001</v>
       </c>
       <c r="O52">
-        <v>-0.149955768</v>
+        <v>-0.15322848336</v>
       </c>
       <c r="P52">
-        <v>-0.474859932</v>
+        <v>-0.4852235306400001</v>
       </c>
       <c r="Q52">
-        <v>-0.475859932</v>
+        <v>-0.4862235306400001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.5189078990876844</v>
+        <v>0.5285631623343719</v>
       </c>
       <c r="T52">
-        <v>2.324555191962469</v>
+        <v>2.371995093839254</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.02006407303322584</v>
+        <v>0.01967065983649592</v>
       </c>
       <c r="W52">
-        <v>0.2310688915787653</v>
+        <v>0.2311616584105542</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.08360030430510779</v>
+        <v>0.08196108265206636</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.3768883953332249</v>
+        <v>0.3787883953332249</v>
       </c>
       <c r="C53">
-        <v>1.284103053498036</v>
+        <v>1.203281493104513</v>
       </c>
       <c r="D53">
-        <v>4.029433053498036</v>
+        <v>4.006441493104513</v>
       </c>
       <c r="E53">
-        <v>2.91633</v>
+        <v>2.97416</v>
       </c>
       <c r="F53">
-        <v>2.94933</v>
+        <v>3.00716</v>
       </c>
       <c r="G53">
         <v>0.204</v>
@@ -5627,37 +5627,37 @@
         <v>0.057</v>
       </c>
       <c r="M53">
-        <v>0.6954520140000001</v>
+        <v>0.7090883280000001</v>
       </c>
       <c r="N53">
-        <v>-0.6384520140000001</v>
+        <v>-0.6520883280000001</v>
       </c>
       <c r="O53">
-        <v>-0.15322848336</v>
+        <v>-0.15650119872</v>
       </c>
       <c r="P53">
-        <v>-0.4852235306400001</v>
+        <v>-0.49558712928</v>
       </c>
       <c r="Q53">
-        <v>-0.4862235306400001</v>
+        <v>-0.49658712928</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.5285631623343719</v>
+        <v>0.538620728216338</v>
       </c>
       <c r="T53">
-        <v>2.371995093839254</v>
+        <v>2.421411658294239</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.01967065983649592</v>
+        <v>0.01929237791656331</v>
       </c>
       <c r="W53">
-        <v>0.2311616584105542</v>
+        <v>0.2312508572872744</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.08196108265206636</v>
+        <v>0.08038490798568054</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.3787883953332249</v>
+        <v>0.3806883953332249</v>
       </c>
       <c r="C54">
-        <v>1.203281493104513</v>
+        <v>1.122720819414479</v>
       </c>
       <c r="D54">
-        <v>4.006441493104513</v>
+        <v>3.98371081941448</v>
       </c>
       <c r="E54">
-        <v>2.97416</v>
+        <v>3.03199</v>
       </c>
       <c r="F54">
-        <v>3.00716</v>
+        <v>3.06499</v>
       </c>
       <c r="G54">
         <v>0.204</v>
@@ -5709,37 +5709,37 @@
         <v>0.057</v>
       </c>
       <c r="M54">
-        <v>0.7090883280000001</v>
+        <v>0.7227246420000001</v>
       </c>
       <c r="N54">
-        <v>-0.6520883280000001</v>
+        <v>-0.665724642</v>
       </c>
       <c r="O54">
-        <v>-0.15650119872</v>
+        <v>-0.15977391408</v>
       </c>
       <c r="P54">
-        <v>-0.49558712928</v>
+        <v>-0.5059507279200001</v>
       </c>
       <c r="Q54">
-        <v>-0.49658712928</v>
+        <v>-0.5069507279200001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.538620728216338</v>
+        <v>0.5491062756251962</v>
       </c>
       <c r="T54">
-        <v>2.421411658294239</v>
+        <v>2.472931055279223</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.01929237791656331</v>
+        <v>0.01892837078606211</v>
       </c>
       <c r="W54">
-        <v>0.2312508572872744</v>
+        <v>0.2313366901686466</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.08038490798568054</v>
+        <v>0.07886821160859225</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.3806883953332249</v>
+        <v>0.3825883953332249</v>
       </c>
       <c r="C55">
-        <v>1.122720819414479</v>
+        <v>1.042416617031709</v>
       </c>
       <c r="D55">
-        <v>3.98371081941448</v>
+        <v>3.96123661703171</v>
       </c>
       <c r="E55">
-        <v>3.03199</v>
+        <v>3.08982</v>
       </c>
       <c r="F55">
-        <v>3.06499</v>
+        <v>3.12282</v>
       </c>
       <c r="G55">
         <v>0.204</v>
@@ -5791,37 +5791,37 @@
         <v>0.057</v>
       </c>
       <c r="M55">
-        <v>0.7227246420000001</v>
+        <v>0.7363609560000001</v>
       </c>
       <c r="N55">
-        <v>-0.665724642</v>
+        <v>-0.679360956</v>
       </c>
       <c r="O55">
-        <v>-0.15977391408</v>
+        <v>-0.16304662944</v>
       </c>
       <c r="P55">
-        <v>-0.5059507279200001</v>
+        <v>-0.51631432656</v>
       </c>
       <c r="Q55">
-        <v>-0.5069507279200001</v>
+        <v>-0.51731432656</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.5491062756251962</v>
+        <v>0.5600477163996569</v>
       </c>
       <c r="T55">
-        <v>2.472931055279223</v>
+        <v>2.526690426046162</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.01892837078606211</v>
+        <v>0.01857784540113503</v>
       </c>
       <c r="W55">
-        <v>0.2313366901686466</v>
+        <v>0.2314193440544124</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.07886821160859225</v>
+        <v>0.07740768917139607</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.3825883953332249</v>
+        <v>0.3844883953332249</v>
       </c>
       <c r="C56">
-        <v>1.042416617031709</v>
+        <v>0.9623645696392802</v>
       </c>
       <c r="D56">
-        <v>3.96123661703171</v>
+        <v>3.93901456963928</v>
       </c>
       <c r="E56">
-        <v>3.08982</v>
+        <v>3.147650000000001</v>
       </c>
       <c r="F56">
-        <v>3.12282</v>
+        <v>3.18065</v>
       </c>
       <c r="G56">
         <v>0.204</v>
@@ -5873,37 +5873,37 @@
         <v>0.057</v>
       </c>
       <c r="M56">
-        <v>0.7363609560000001</v>
+        <v>0.7499972700000002</v>
       </c>
       <c r="N56">
-        <v>-0.679360956</v>
+        <v>-0.6929972700000001</v>
       </c>
       <c r="O56">
-        <v>-0.16304662944</v>
+        <v>-0.1663193448</v>
       </c>
       <c r="P56">
-        <v>-0.51631432656</v>
+        <v>-0.5266779252000001</v>
       </c>
       <c r="Q56">
-        <v>-0.51731432656</v>
+        <v>-0.5276779252000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.5600477163996569</v>
+        <v>0.5714754434307606</v>
       </c>
       <c r="T56">
-        <v>2.526690426046162</v>
+        <v>2.582839102180522</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.01857784540113503</v>
+        <v>0.01824006639384167</v>
       </c>
       <c r="W56">
-        <v>0.2314193440544124</v>
+        <v>0.2314989923443321</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.07740768917139607</v>
+        <v>0.07600027664100706</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.3844883953332249</v>
+        <v>0.3863883953332249</v>
       </c>
       <c r="C57">
-        <v>0.9623645696392802</v>
+        <v>0.8825604572359729</v>
       </c>
       <c r="D57">
-        <v>3.93901456963928</v>
+        <v>3.917040457235973</v>
       </c>
       <c r="E57">
-        <v>3.147650000000001</v>
+        <v>3.205480000000001</v>
       </c>
       <c r="F57">
-        <v>3.18065</v>
+        <v>3.23848</v>
       </c>
       <c r="G57">
         <v>0.204</v>
@@ -5955,37 +5955,37 @@
         <v>0.057</v>
       </c>
       <c r="M57">
-        <v>0.7499972700000002</v>
+        <v>0.7636335840000001</v>
       </c>
       <c r="N57">
-        <v>-0.6929972700000001</v>
+        <v>-0.7066335840000001</v>
       </c>
       <c r="O57">
-        <v>-0.1663193448</v>
+        <v>-0.16959206016</v>
       </c>
       <c r="P57">
-        <v>-0.5266779252000001</v>
+        <v>-0.5370415238400001</v>
       </c>
       <c r="Q57">
-        <v>-0.5276779252000001</v>
+        <v>-0.5380415238400001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.5714754434307606</v>
+        <v>0.5834226125996413</v>
       </c>
       <c r="T57">
-        <v>2.582839102180522</v>
+        <v>2.641539990866442</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.01824006639384167</v>
+        <v>0.01791435092252307</v>
       </c>
       <c r="W57">
-        <v>0.2314989923443321</v>
+        <v>0.2315757960524691</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.07600027664100706</v>
+        <v>0.07464312884384616</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.3863883953332249</v>
+        <v>0.3882883953332249</v>
       </c>
       <c r="C58">
-        <v>0.8825604572359729</v>
+        <v>0.8030001534646369</v>
       </c>
       <c r="D58">
-        <v>3.917040457235973</v>
+        <v>3.895310153464637</v>
       </c>
       <c r="E58">
-        <v>3.205480000000001</v>
+        <v>3.263310000000001</v>
       </c>
       <c r="F58">
-        <v>3.23848</v>
+        <v>3.296310000000001</v>
       </c>
       <c r="G58">
         <v>0.204</v>
@@ -6037,37 +6037,37 @@
         <v>0.057</v>
       </c>
       <c r="M58">
-        <v>0.7636335840000001</v>
+        <v>0.7772698980000001</v>
       </c>
       <c r="N58">
-        <v>-0.7066335840000001</v>
+        <v>-0.7202698980000001</v>
       </c>
       <c r="O58">
-        <v>-0.16959206016</v>
+        <v>-0.17286477552</v>
       </c>
       <c r="P58">
-        <v>-0.5370415238400001</v>
+        <v>-0.5474051224800001</v>
       </c>
       <c r="Q58">
-        <v>-0.5380415238400001</v>
+        <v>-0.5484051224800001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.5834226125996413</v>
+        <v>0.5959254640554471</v>
       </c>
       <c r="T58">
-        <v>2.641539990866442</v>
+        <v>2.702971153444732</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.01791435092252307</v>
+        <v>0.01760006406423319</v>
       </c>
       <c r="W58">
-        <v>0.2315757960524691</v>
+        <v>0.2316499048936538</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.07464312884384616</v>
+        <v>0.07333360026763835</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.3882883953332249</v>
+        <v>0.3901883953332249</v>
       </c>
       <c r="C59">
-        <v>0.8030001534646369</v>
+        <v>0.723679623029017</v>
       </c>
       <c r="D59">
-        <v>3.895310153464637</v>
+        <v>3.873819623029017</v>
       </c>
       <c r="E59">
-        <v>3.263310000000001</v>
+        <v>3.321140000000001</v>
       </c>
       <c r="F59">
-        <v>3.296310000000001</v>
+        <v>3.354140000000001</v>
       </c>
       <c r="G59">
         <v>0.204</v>
@@ -6119,37 +6119,37 @@
         <v>0.057</v>
       </c>
       <c r="M59">
-        <v>0.7772698980000001</v>
+        <v>0.7909062120000002</v>
       </c>
       <c r="N59">
-        <v>-0.7202698980000001</v>
+        <v>-0.7339062120000002</v>
       </c>
       <c r="O59">
-        <v>-0.17286477552</v>
+        <v>-0.17613749088</v>
       </c>
       <c r="P59">
-        <v>-0.5474051224800001</v>
+        <v>-0.5577687211200002</v>
       </c>
       <c r="Q59">
-        <v>-0.5484051224800001</v>
+        <v>-0.5587687211200002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.5959254640554471</v>
+        <v>0.6090236893901005</v>
       </c>
       <c r="T59">
-        <v>2.702971153444732</v>
+        <v>2.76732760947913</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.01760006406423319</v>
+        <v>0.01729661468381537</v>
       </c>
       <c r="W59">
-        <v>0.2316499048936538</v>
+        <v>0.2317214582575564</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.07333360026763835</v>
+        <v>0.07206922784923075</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.3901883953332249</v>
+        <v>0.3920883953332249</v>
       </c>
       <c r="C60">
-        <v>0.7236796230290174</v>
+        <v>0.6445949191956055</v>
       </c>
       <c r="D60">
-        <v>3.873819623029017</v>
+        <v>3.852564919195606</v>
       </c>
       <c r="E60">
-        <v>3.32114</v>
+        <v>3.37897</v>
       </c>
       <c r="F60">
-        <v>3.35414</v>
+        <v>3.41197</v>
       </c>
       <c r="G60">
         <v>0.204</v>
@@ -6201,37 +6201,37 @@
         <v>0.057</v>
       </c>
       <c r="M60">
-        <v>0.7909062120000001</v>
+        <v>0.8045425260000001</v>
       </c>
       <c r="N60">
-        <v>-0.7339062120000001</v>
+        <v>-0.747542526</v>
       </c>
       <c r="O60">
-        <v>-0.17613749088</v>
+        <v>-0.17941020624</v>
       </c>
       <c r="P60">
-        <v>-0.5577687211200001</v>
+        <v>-0.56813231976</v>
       </c>
       <c r="Q60">
-        <v>-0.5587687211200001</v>
+        <v>-0.56913231976</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.6090236893901004</v>
+        <v>0.6227608525459566</v>
       </c>
       <c r="T60">
-        <v>2.767327609479129</v>
+        <v>2.834823404832279</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.01729661468381538</v>
+        <v>0.01700345172307275</v>
       </c>
       <c r="W60">
-        <v>0.2317214582575564</v>
+        <v>0.2317905860836995</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.07206922784923075</v>
+        <v>0.07084771551280311</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.3920883953332249</v>
+        <v>0.3939883953332248</v>
       </c>
       <c r="C61">
-        <v>0.6445949191956055</v>
+        <v>0.5657421813772876</v>
       </c>
       <c r="D61">
-        <v>3.852564919195606</v>
+        <v>3.831542181377288</v>
       </c>
       <c r="E61">
-        <v>3.37897</v>
+        <v>3.4368</v>
       </c>
       <c r="F61">
-        <v>3.41197</v>
+        <v>3.4698</v>
       </c>
       <c r="G61">
         <v>0.204</v>
@@ -6283,37 +6283,37 @@
         <v>0.057</v>
       </c>
       <c r="M61">
-        <v>0.8045425260000001</v>
+        <v>0.8181788400000001</v>
       </c>
       <c r="N61">
-        <v>-0.747542526</v>
+        <v>-0.76117884</v>
       </c>
       <c r="O61">
-        <v>-0.17941020624</v>
+        <v>-0.1826829216</v>
       </c>
       <c r="P61">
-        <v>-0.56813231976</v>
+        <v>-0.5784959184</v>
       </c>
       <c r="Q61">
-        <v>-0.56913231976</v>
+        <v>-0.5794959184</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.6227608525459566</v>
+        <v>0.6371848738596054</v>
       </c>
       <c r="T61">
-        <v>2.834823404832279</v>
+        <v>2.905693989953086</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.01700345172307275</v>
+        <v>0.01672006086102153</v>
       </c>
       <c r="W61">
-        <v>0.2317905860836995</v>
+        <v>0.2318574096489711</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.07084771551280311</v>
+        <v>0.06966692025425647</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.3939883953332248</v>
+        <v>0.395888395333225</v>
       </c>
       <c r="C62">
-        <v>0.5657421813772876</v>
+        <v>0.4871176327956697</v>
       </c>
       <c r="D62">
-        <v>3.831542181377288</v>
+        <v>3.81074763279567</v>
       </c>
       <c r="E62">
-        <v>3.4368</v>
+        <v>3.49463</v>
       </c>
       <c r="F62">
-        <v>3.4698</v>
+        <v>3.52763</v>
       </c>
       <c r="G62">
         <v>0.204</v>
@@ -6365,37 +6365,37 @@
         <v>0.057</v>
       </c>
       <c r="M62">
-        <v>0.8181788400000001</v>
+        <v>0.8318151540000001</v>
       </c>
       <c r="N62">
-        <v>-0.76117884</v>
+        <v>-0.774815154</v>
       </c>
       <c r="O62">
-        <v>-0.1826829216</v>
+        <v>-0.18595563696</v>
       </c>
       <c r="P62">
-        <v>-0.5784959184</v>
+        <v>-0.5888595170399999</v>
       </c>
       <c r="Q62">
-        <v>-0.5794959184</v>
+        <v>-0.5898595170399999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.6371848738596054</v>
+        <v>0.6523485885739544</v>
       </c>
       <c r="T62">
-        <v>2.905693989953086</v>
+        <v>2.980198964054448</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.01672006086102153</v>
+        <v>0.01644596150264413</v>
       </c>
       <c r="W62">
-        <v>0.2318574096489711</v>
+        <v>0.2319220422776765</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.06966692025425647</v>
+        <v>0.06852483959435063</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.395888395333225</v>
+        <v>0.3977883953332249</v>
       </c>
       <c r="C63">
-        <v>0.4871176327956697</v>
+        <v>0.4087175782191341</v>
       </c>
       <c r="D63">
-        <v>3.81074763279567</v>
+        <v>3.790177578219134</v>
       </c>
       <c r="E63">
-        <v>3.49463</v>
+        <v>3.55246</v>
       </c>
       <c r="F63">
-        <v>3.52763</v>
+        <v>3.58546</v>
       </c>
       <c r="G63">
         <v>0.204</v>
@@ -6447,37 +6447,37 @@
         <v>0.057</v>
       </c>
       <c r="M63">
-        <v>0.8318151540000001</v>
+        <v>0.8454514680000002</v>
       </c>
       <c r="N63">
-        <v>-0.774815154</v>
+        <v>-0.7884514680000001</v>
       </c>
       <c r="O63">
-        <v>-0.18595563696</v>
+        <v>-0.18922835232</v>
       </c>
       <c r="P63">
-        <v>-0.5888595170399999</v>
+        <v>-0.5992231156800001</v>
       </c>
       <c r="Q63">
-        <v>-0.5898595170399999</v>
+        <v>-0.6002231156800001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.6523485885739544</v>
+        <v>0.6683103935364268</v>
       </c>
       <c r="T63">
-        <v>2.980198964054448</v>
+        <v>3.058625252582196</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.01644596150264413</v>
+        <v>0.01618070405905309</v>
       </c>
       <c r="W63">
-        <v>0.2319220422776765</v>
+        <v>0.2319845899828753</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.06852483959435063</v>
+        <v>0.06741960024605465</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.3977883953332249</v>
+        <v>0.3996883953332249</v>
       </c>
       <c r="C64">
-        <v>0.4087175782191341</v>
+        <v>0.3305384017737318</v>
       </c>
       <c r="D64">
-        <v>3.790177578219134</v>
+        <v>3.769828401773732</v>
       </c>
       <c r="E64">
-        <v>3.55246</v>
+        <v>3.61029</v>
       </c>
       <c r="F64">
-        <v>3.58546</v>
+        <v>3.64329</v>
       </c>
       <c r="G64">
         <v>0.204</v>
@@ -6529,37 +6529,37 @@
         <v>0.057</v>
       </c>
       <c r="M64">
-        <v>0.8454514680000002</v>
+        <v>0.8590877820000001</v>
       </c>
       <c r="N64">
-        <v>-0.7884514680000001</v>
+        <v>-0.8020877820000001</v>
       </c>
       <c r="O64">
-        <v>-0.18922835232</v>
+        <v>-0.19250106768</v>
       </c>
       <c r="P64">
-        <v>-0.5992231156800001</v>
+        <v>-0.60958671432</v>
       </c>
       <c r="Q64">
-        <v>-0.6002231156800001</v>
+        <v>-0.61058671432</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.6683103935364268</v>
+        <v>0.685134998767141</v>
       </c>
       <c r="T64">
-        <v>3.058625252582196</v>
+        <v>3.141290799949282</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.01618070405905309</v>
+        <v>0.01592386748668717</v>
       </c>
       <c r="W64">
-        <v>0.2319845899828753</v>
+        <v>0.2320451520466392</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.06741960024605465</v>
+        <v>0.06634944786119656</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.3996883953332249</v>
+        <v>0.4015883953332249</v>
       </c>
       <c r="C65">
-        <v>0.3305384017737318</v>
+        <v>0.2525765648242393</v>
       </c>
       <c r="D65">
-        <v>3.769828401773732</v>
+        <v>3.74969656482424</v>
       </c>
       <c r="E65">
-        <v>3.61029</v>
+        <v>3.66812</v>
       </c>
       <c r="F65">
-        <v>3.64329</v>
+        <v>3.70112</v>
       </c>
       <c r="G65">
         <v>0.204</v>
@@ -6611,37 +6611,37 @@
         <v>0.057</v>
       </c>
       <c r="M65">
-        <v>0.8590877820000001</v>
+        <v>0.8727240960000001</v>
       </c>
       <c r="N65">
-        <v>-0.8020877820000001</v>
+        <v>-0.8157240960000001</v>
       </c>
       <c r="O65">
-        <v>-0.19250106768</v>
+        <v>-0.19577378304</v>
       </c>
       <c r="P65">
-        <v>-0.60958671432</v>
+        <v>-0.61995031296</v>
       </c>
       <c r="Q65">
-        <v>-0.61058671432</v>
+        <v>-0.62095031296</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.685134998767141</v>
+        <v>0.7028943042884506</v>
       </c>
       <c r="T65">
-        <v>3.141290799949282</v>
+        <v>3.228548877725651</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.01592386748668717</v>
+        <v>0.01567505705720769</v>
       </c>
       <c r="W65">
-        <v>0.2320451520466392</v>
+        <v>0.2321038215459104</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.06634944786119656</v>
+        <v>0.06531273773836543</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.4015883953332249</v>
+        <v>0.4034883953332249</v>
       </c>
       <c r="C66">
-        <v>0.2525765648242393</v>
+        <v>0.1748286039227427</v>
       </c>
       <c r="D66">
-        <v>3.74969656482424</v>
+        <v>3.729778603922743</v>
       </c>
       <c r="E66">
-        <v>3.66812</v>
+        <v>3.725950000000001</v>
       </c>
       <c r="F66">
-        <v>3.70112</v>
+        <v>3.75895</v>
       </c>
       <c r="G66">
         <v>0.204</v>
@@ -6693,37 +6693,37 @@
         <v>0.057</v>
       </c>
       <c r="M66">
-        <v>0.8727240960000001</v>
+        <v>0.8863604100000001</v>
       </c>
       <c r="N66">
-        <v>-0.8157240960000001</v>
+        <v>-0.82936041</v>
       </c>
       <c r="O66">
-        <v>-0.19577378304</v>
+        <v>-0.1990464984</v>
       </c>
       <c r="P66">
-        <v>-0.61995031296</v>
+        <v>-0.6303139116000001</v>
       </c>
       <c r="Q66">
-        <v>-0.62095031296</v>
+        <v>-0.6313139116000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.7028943042884506</v>
+        <v>0.7216684272681206</v>
       </c>
       <c r="T66">
-        <v>3.228548877725651</v>
+        <v>3.320793131374956</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.01567505705720769</v>
+        <v>0.01543390233325064</v>
       </c>
       <c r="W66">
-        <v>0.2321038215459104</v>
+        <v>0.2321606858298195</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.06531273773836543</v>
+        <v>0.06430792638854443</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.4034883953332249</v>
+        <v>0.4053883953332249</v>
       </c>
       <c r="C67">
-        <v>0.1748286039227427</v>
+        <v>0.09729112882225666</v>
       </c>
       <c r="D67">
-        <v>3.729778603922743</v>
+        <v>3.710071128822257</v>
       </c>
       <c r="E67">
-        <v>3.725950000000001</v>
+        <v>3.783780000000001</v>
       </c>
       <c r="F67">
-        <v>3.75895</v>
+        <v>3.816780000000001</v>
       </c>
       <c r="G67">
         <v>0.204</v>
@@ -6775,37 +6775,37 @@
         <v>0.057</v>
       </c>
       <c r="M67">
-        <v>0.8863604100000001</v>
+        <v>0.8999967240000002</v>
       </c>
       <c r="N67">
-        <v>-0.82936041</v>
+        <v>-0.8429967240000001</v>
       </c>
       <c r="O67">
-        <v>-0.1990464984</v>
+        <v>-0.20231921376</v>
       </c>
       <c r="P67">
-        <v>-0.6303139116000001</v>
+        <v>-0.6406775102400001</v>
       </c>
       <c r="Q67">
-        <v>-0.6313139116000001</v>
+        <v>-0.6416775102400001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.7216684272681206</v>
+        <v>0.7415469104230653</v>
       </c>
       <c r="T67">
-        <v>3.320793131374956</v>
+        <v>3.418463517591866</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.01543390233325064</v>
+        <v>0.01520005532820139</v>
       </c>
       <c r="W67">
-        <v>0.2321606858298195</v>
+        <v>0.2322158269536101</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.06430792638854443</v>
+        <v>0.06333356386750588</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.4053883953332249</v>
+        <v>0.4072883953332249</v>
       </c>
       <c r="C68">
-        <v>0.09729112882225666</v>
+        <v>0.01996082055298443</v>
       </c>
       <c r="D68">
-        <v>3.710071128822257</v>
+        <v>3.690570820552985</v>
       </c>
       <c r="E68">
-        <v>3.783780000000001</v>
+        <v>3.841610000000001</v>
       </c>
       <c r="F68">
-        <v>3.816780000000001</v>
+        <v>3.874610000000001</v>
       </c>
       <c r="G68">
         <v>0.204</v>
@@ -6857,37 +6857,37 @@
         <v>0.057</v>
       </c>
       <c r="M68">
-        <v>0.8999967240000002</v>
+        <v>0.9136330380000002</v>
       </c>
       <c r="N68">
-        <v>-0.8429967240000001</v>
+        <v>-0.8566330380000001</v>
       </c>
       <c r="O68">
-        <v>-0.20231921376</v>
+        <v>-0.20559192912</v>
       </c>
       <c r="P68">
-        <v>-0.6406775102400001</v>
+        <v>-0.6510411088800001</v>
       </c>
       <c r="Q68">
-        <v>-0.6416775102400001</v>
+        <v>-0.6520411088800001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.7415469104230653</v>
+        <v>0.7626301501328553</v>
       </c>
       <c r="T68">
-        <v>3.418463517591866</v>
+        <v>3.522053321155256</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.01520005532820139</v>
+        <v>0.01497318883076555</v>
       </c>
       <c r="W68">
-        <v>0.2322158269536101</v>
+        <v>0.2322693220737055</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.06333356386750588</v>
+        <v>0.06238828679485653</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.4072883953332249</v>
+        <v>0.4091883953332249</v>
       </c>
       <c r="C69">
-        <v>0.01996082055298443</v>
+        <v>-0.05716557044106629</v>
       </c>
       <c r="D69">
-        <v>3.690570820552985</v>
+        <v>3.671274429558934</v>
       </c>
       <c r="E69">
-        <v>3.841610000000001</v>
+        <v>3.899440000000001</v>
       </c>
       <c r="F69">
-        <v>3.874610000000001</v>
+        <v>3.932440000000001</v>
       </c>
       <c r="G69">
         <v>0.204</v>
@@ -6939,37 +6939,37 @@
         <v>0.057</v>
       </c>
       <c r="M69">
-        <v>0.9136330380000002</v>
+        <v>0.9272693520000002</v>
       </c>
       <c r="N69">
-        <v>-0.8566330380000001</v>
+        <v>-0.8702693520000001</v>
       </c>
       <c r="O69">
-        <v>-0.20559192912</v>
+        <v>-0.20886464448</v>
       </c>
       <c r="P69">
-        <v>-0.6510411088800001</v>
+        <v>-0.66140470752</v>
       </c>
       <c r="Q69">
-        <v>-0.6520411088800001</v>
+        <v>-0.66240470752</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.7626301501328553</v>
+        <v>0.785031092324507</v>
       </c>
       <c r="T69">
-        <v>3.522053321155256</v>
+        <v>3.632117487441358</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.01497318883076555</v>
+        <v>0.01475299487737194</v>
       </c>
       <c r="W69">
-        <v>0.2322693220737055</v>
+        <v>0.2323212438079157</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.06238828679485653</v>
+        <v>0.0614708119890498</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.4091883953332249</v>
+        <v>0.4110883953332249</v>
       </c>
       <c r="C70">
-        <v>-0.05716557044106629</v>
+        <v>-0.1340912261073219</v>
       </c>
       <c r="D70">
-        <v>3.671274429558934</v>
+        <v>3.652178773892679</v>
       </c>
       <c r="E70">
-        <v>3.899440000000001</v>
+        <v>3.957270000000001</v>
       </c>
       <c r="F70">
-        <v>3.932440000000001</v>
+        <v>3.990270000000001</v>
       </c>
       <c r="G70">
         <v>0.204</v>
@@ -7021,37 +7021,37 @@
         <v>0.057</v>
       </c>
       <c r="M70">
-        <v>0.9272693520000002</v>
+        <v>0.9409056660000001</v>
       </c>
       <c r="N70">
-        <v>-0.8702693520000001</v>
+        <v>-0.8839056660000001</v>
       </c>
       <c r="O70">
-        <v>-0.20886464448</v>
+        <v>-0.21213735984</v>
       </c>
       <c r="P70">
-        <v>-0.66140470752</v>
+        <v>-0.6717683061600001</v>
       </c>
       <c r="Q70">
-        <v>-0.66240470752</v>
+        <v>-0.6727683061600001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.785031092324507</v>
+        <v>0.8088772565930396</v>
       </c>
       <c r="T70">
-        <v>3.632117487441358</v>
+        <v>3.749282567681402</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.01475299487737194</v>
+        <v>0.01453918335741003</v>
       </c>
       <c r="W70">
-        <v>0.2323212438079157</v>
+        <v>0.2323716605643227</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.0614708119890498</v>
+        <v>0.06057993065587519</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.4110883953332249</v>
+        <v>0.4129883953332249</v>
       </c>
       <c r="C71">
-        <v>-0.1340912261073219</v>
+        <v>-0.210819262533823</v>
       </c>
       <c r="D71">
-        <v>3.652178773892679</v>
+        <v>3.633280737466178</v>
       </c>
       <c r="E71">
-        <v>3.957270000000001</v>
+        <v>4.0151</v>
       </c>
       <c r="F71">
-        <v>3.990270000000001</v>
+        <v>4.048100000000001</v>
       </c>
       <c r="G71">
         <v>0.204</v>
@@ -7103,37 +7103,37 @@
         <v>0.057</v>
       </c>
       <c r="M71">
-        <v>0.9409056660000001</v>
+        <v>0.9545419800000002</v>
       </c>
       <c r="N71">
-        <v>-0.8839056660000001</v>
+        <v>-0.8975419800000002</v>
       </c>
       <c r="O71">
-        <v>-0.21213735984</v>
+        <v>-0.2154100752</v>
       </c>
       <c r="P71">
-        <v>-0.6717683061600001</v>
+        <v>-0.6821319048000002</v>
       </c>
       <c r="Q71">
-        <v>-0.6727683061600001</v>
+        <v>-0.6831319048000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.8088772565930396</v>
+        <v>0.8343131651461408</v>
       </c>
       <c r="T71">
-        <v>3.749282567681402</v>
+        <v>3.874258653270782</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.01453918335741003</v>
+        <v>0.01433148073801845</v>
       </c>
       <c r="W71">
-        <v>0.2323716605643227</v>
+        <v>0.2324206368419753</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.06057993065587519</v>
+        <v>0.05971450307507697</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.4129883953332249</v>
+        <v>0.4148883953332249</v>
       </c>
       <c r="C72">
-        <v>-0.210819262533823</v>
+        <v>-0.287352731644396</v>
       </c>
       <c r="D72">
-        <v>3.633280737466178</v>
+        <v>3.614577268355605</v>
       </c>
       <c r="E72">
-        <v>4.0151</v>
+        <v>4.07293</v>
       </c>
       <c r="F72">
-        <v>4.048100000000001</v>
+        <v>4.105930000000001</v>
       </c>
       <c r="G72">
         <v>0.204</v>
@@ -7185,37 +7185,37 @@
         <v>0.057</v>
       </c>
       <c r="M72">
-        <v>0.9545419800000002</v>
+        <v>0.9681782940000002</v>
       </c>
       <c r="N72">
-        <v>-0.8975419800000002</v>
+        <v>-0.9111782940000002</v>
       </c>
       <c r="O72">
-        <v>-0.2154100752</v>
+        <v>-0.21868279056</v>
       </c>
       <c r="P72">
-        <v>-0.6821319048000002</v>
+        <v>-0.6924955034400001</v>
       </c>
       <c r="Q72">
-        <v>-0.6831319048000002</v>
+        <v>-0.6934955034400001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.8343131651461408</v>
+        <v>0.8615032742891113</v>
       </c>
       <c r="T72">
-        <v>3.874258653270782</v>
+        <v>4.007853779245638</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01433148073801845</v>
+        <v>0.01412962889663791</v>
       </c>
       <c r="W72">
-        <v>0.2324206368419753</v>
+        <v>0.2324682335061728</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.05971450307507697</v>
+        <v>0.0588734537359914</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.4148883953332249</v>
+        <v>0.4167883953332249</v>
       </c>
       <c r="C73">
-        <v>-0.2873527316443947</v>
+        <v>-0.3636946228417113</v>
       </c>
       <c r="D73">
-        <v>3.614577268355605</v>
+        <v>3.596065377158288</v>
       </c>
       <c r="E73">
-        <v>4.072929999999999</v>
+        <v>4.13076</v>
       </c>
       <c r="F73">
-        <v>4.10593</v>
+        <v>4.16376</v>
       </c>
       <c r="G73">
         <v>0.204</v>
@@ -7267,37 +7267,37 @@
         <v>0.057</v>
       </c>
       <c r="M73">
-        <v>0.968178294</v>
+        <v>0.981814608</v>
       </c>
       <c r="N73">
-        <v>-0.9111782939999999</v>
+        <v>-0.9248146079999999</v>
       </c>
       <c r="O73">
-        <v>-0.21868279056</v>
+        <v>-0.22195550592</v>
       </c>
       <c r="P73">
-        <v>-0.69249550344</v>
+        <v>-0.7028591020799999</v>
       </c>
       <c r="Q73">
-        <v>-0.69349550344</v>
+        <v>-0.7038591020799999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.861503274289111</v>
+        <v>0.8906355340851507</v>
       </c>
       <c r="T73">
-        <v>4.007853779245636</v>
+        <v>4.150991414218694</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01412962889663792</v>
+        <v>0.01393338405085128</v>
       </c>
       <c r="W73">
-        <v>0.2324682335061728</v>
+        <v>0.2325145080408093</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.0588734537359914</v>
+        <v>0.05805576687854708</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.4167883953332249</v>
+        <v>0.4186883953332249</v>
       </c>
       <c r="C74">
-        <v>-0.3636946228417113</v>
+        <v>-0.4398478646001336</v>
       </c>
       <c r="D74">
-        <v>3.596065377158288</v>
+        <v>3.577742135399866</v>
       </c>
       <c r="E74">
-        <v>4.13076</v>
+        <v>4.18859</v>
       </c>
       <c r="F74">
-        <v>4.16376</v>
+        <v>4.22159</v>
       </c>
       <c r="G74">
         <v>0.204</v>
@@ -7349,37 +7349,37 @@
         <v>0.057</v>
       </c>
       <c r="M74">
-        <v>0.981814608</v>
+        <v>0.9954509220000001</v>
       </c>
       <c r="N74">
-        <v>-0.9248146079999999</v>
+        <v>-0.938450922</v>
       </c>
       <c r="O74">
-        <v>-0.22195550592</v>
+        <v>-0.22522822128</v>
       </c>
       <c r="P74">
-        <v>-0.7028591020799999</v>
+        <v>-0.71322270072</v>
       </c>
       <c r="Q74">
-        <v>-0.7038591020799999</v>
+        <v>-0.71422270072</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.8906355340851507</v>
+        <v>0.9219257390512672</v>
       </c>
       <c r="T74">
-        <v>4.150991414218694</v>
+        <v>4.304731836967534</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01393338405085128</v>
+        <v>0.01374251577618208</v>
       </c>
       <c r="W74">
-        <v>0.2325145080408093</v>
+        <v>0.2325595147799763</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.05805576687854708</v>
+        <v>0.05726048240075876</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.4186883953332249</v>
+        <v>0.4205883953332249</v>
       </c>
       <c r="C75">
-        <v>-0.4398478646001336</v>
+        <v>-0.5158153260101002</v>
       </c>
       <c r="D75">
-        <v>3.577742135399866</v>
+        <v>3.5596046739899</v>
       </c>
       <c r="E75">
-        <v>4.18859</v>
+        <v>4.24642</v>
       </c>
       <c r="F75">
-        <v>4.22159</v>
+        <v>4.27942</v>
       </c>
       <c r="G75">
         <v>0.204</v>
@@ -7431,37 +7431,37 @@
         <v>0.057</v>
       </c>
       <c r="M75">
-        <v>0.9954509220000001</v>
+        <v>1.009087236</v>
       </c>
       <c r="N75">
-        <v>-0.938450922</v>
+        <v>-0.952087236</v>
       </c>
       <c r="O75">
-        <v>-0.22522822128</v>
+        <v>-0.22850093664</v>
       </c>
       <c r="P75">
-        <v>-0.71322270072</v>
+        <v>-0.72358629936</v>
       </c>
       <c r="Q75">
-        <v>-0.71422270072</v>
+        <v>-0.72458629936</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.9219257390512672</v>
+        <v>0.9556228828609316</v>
       </c>
       <c r="T75">
-        <v>4.304731836967534</v>
+        <v>4.470298446081671</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01374251577618208</v>
+        <v>0.01355680610353097</v>
       </c>
       <c r="W75">
-        <v>0.2325595147799763</v>
+        <v>0.2326033051207874</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.05726048240075876</v>
+        <v>0.0564866920980458</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.4205883953332249</v>
+        <v>0.4224883953332249</v>
       </c>
       <c r="C76">
-        <v>-0.5158153260101002</v>
+        <v>-0.5915998182757778</v>
       </c>
       <c r="D76">
-        <v>3.5596046739899</v>
+        <v>3.541650181724222</v>
       </c>
       <c r="E76">
-        <v>4.24642</v>
+        <v>4.30425</v>
       </c>
       <c r="F76">
-        <v>4.27942</v>
+        <v>4.33725</v>
       </c>
       <c r="G76">
         <v>0.204</v>
@@ -7513,37 +7513,37 @@
         <v>0.057</v>
       </c>
       <c r="M76">
-        <v>1.009087236</v>
+        <v>1.02272355</v>
       </c>
       <c r="N76">
-        <v>-0.952087236</v>
+        <v>-0.96572355</v>
       </c>
       <c r="O76">
-        <v>-0.22850093664</v>
+        <v>-0.231773652</v>
       </c>
       <c r="P76">
-        <v>-0.72358629936</v>
+        <v>-0.733949898</v>
       </c>
       <c r="Q76">
-        <v>-0.72458629936</v>
+        <v>-0.734949898</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.9556228828609316</v>
+        <v>0.9920157981753689</v>
       </c>
       <c r="T76">
-        <v>4.470298446081671</v>
+        <v>4.649110383924938</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01355680610353097</v>
+        <v>0.01337604868881723</v>
       </c>
       <c r="W76">
-        <v>0.2326033051207874</v>
+        <v>0.2326459277191769</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.0564866920980458</v>
+        <v>0.05573353620340515</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.4224883953332249</v>
+        <v>0.4243883953332249</v>
       </c>
       <c r="C77">
-        <v>-0.5915998182757778</v>
+        <v>-0.6672040961676116</v>
       </c>
       <c r="D77">
-        <v>3.541650181724222</v>
+        <v>3.523875903832388</v>
       </c>
       <c r="E77">
-        <v>4.30425</v>
+        <v>4.36208</v>
       </c>
       <c r="F77">
-        <v>4.33725</v>
+        <v>4.39508</v>
       </c>
       <c r="G77">
         <v>0.204</v>
@@ -7595,37 +7595,37 @@
         <v>0.057</v>
       </c>
       <c r="M77">
-        <v>1.02272355</v>
+        <v>1.036359864</v>
       </c>
       <c r="N77">
-        <v>-0.96572355</v>
+        <v>-0.979359864</v>
       </c>
       <c r="O77">
-        <v>-0.231773652</v>
+        <v>-0.23504636736</v>
       </c>
       <c r="P77">
-        <v>-0.733949898</v>
+        <v>-0.74431349664</v>
       </c>
       <c r="Q77">
-        <v>-0.734949898</v>
+        <v>-0.74531349664</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.9920157981753689</v>
+        <v>1.031441456432676</v>
       </c>
       <c r="T77">
-        <v>4.649110383924938</v>
+        <v>4.842823316588477</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01337604868881723</v>
+        <v>0.0132000480481749</v>
       </c>
       <c r="W77">
-        <v>0.2326459277191769</v>
+        <v>0.2326874286702404</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.05573353620340515</v>
+        <v>0.05500020020072882</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.4243883953332249</v>
+        <v>0.4262883953332249</v>
       </c>
       <c r="C78">
-        <v>-0.6672040961676116</v>
+        <v>-0.7426308594313573</v>
       </c>
       <c r="D78">
-        <v>3.523875903832388</v>
+        <v>3.506279140568643</v>
       </c>
       <c r="E78">
-        <v>4.36208</v>
+        <v>4.41991</v>
       </c>
       <c r="F78">
-        <v>4.39508</v>
+        <v>4.45291</v>
       </c>
       <c r="G78">
         <v>0.204</v>
@@ -7677,37 +7677,37 @@
         <v>0.057</v>
       </c>
       <c r="M78">
-        <v>1.036359864</v>
+        <v>1.049996178</v>
       </c>
       <c r="N78">
-        <v>-0.979359864</v>
+        <v>-0.992996178</v>
       </c>
       <c r="O78">
-        <v>-0.23504636736</v>
+        <v>-0.23831908272</v>
       </c>
       <c r="P78">
-        <v>-0.74431349664</v>
+        <v>-0.7546770952799999</v>
       </c>
       <c r="Q78">
-        <v>-0.74531349664</v>
+        <v>-0.7556770952799999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>1.031441456432676</v>
+        <v>1.074295432799314</v>
       </c>
       <c r="T78">
-        <v>4.842823316588477</v>
+        <v>5.053380852092324</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.0132000480481749</v>
+        <v>0.01302861885274405</v>
       </c>
       <c r="W78">
-        <v>0.2326874286702404</v>
+        <v>0.232727851674523</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.05500020020072882</v>
+        <v>0.05428591188643361</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.4262883953332249</v>
+        <v>0.4281883953332249</v>
       </c>
       <c r="C79">
-        <v>-0.7426308594313573</v>
+        <v>-0.8178827541551108</v>
       </c>
       <c r="D79">
-        <v>3.506279140568643</v>
+        <v>3.488857245844889</v>
       </c>
       <c r="E79">
-        <v>4.41991</v>
+        <v>4.47774</v>
       </c>
       <c r="F79">
-        <v>4.45291</v>
+        <v>4.51074</v>
       </c>
       <c r="G79">
         <v>0.204</v>
@@ -7759,37 +7759,37 @@
         <v>0.057</v>
       </c>
       <c r="M79">
-        <v>1.049996178</v>
+        <v>1.063632492</v>
       </c>
       <c r="N79">
-        <v>-0.992996178</v>
+        <v>-1.006632492</v>
       </c>
       <c r="O79">
-        <v>-0.23831908272</v>
+        <v>-0.24159179808</v>
       </c>
       <c r="P79">
-        <v>-0.7546770952799999</v>
+        <v>-0.7650406939200001</v>
       </c>
       <c r="Q79">
-        <v>-0.7556770952799999</v>
+        <v>-0.7660406939200001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>1.074295432799314</v>
+        <v>1.121045225199283</v>
       </c>
       <c r="T79">
-        <v>5.053380852092324</v>
+        <v>5.283079981732884</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01302861885274405</v>
+        <v>0.01286158527770887</v>
       </c>
       <c r="W79">
-        <v>0.232727851674523</v>
+        <v>0.2327672381915163</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.05428591188643361</v>
+        <v>0.05358993865712025</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.4281883953332249</v>
+        <v>0.4300883953332249</v>
       </c>
       <c r="C80">
-        <v>-0.8178827541551108</v>
+        <v>-0.8929623740957742</v>
       </c>
       <c r="D80">
-        <v>3.488857245844889</v>
+        <v>3.471607625904226</v>
       </c>
       <c r="E80">
-        <v>4.47774</v>
+        <v>4.53557</v>
       </c>
       <c r="F80">
-        <v>4.51074</v>
+        <v>4.56857</v>
       </c>
       <c r="G80">
         <v>0.204</v>
@@ -7841,37 +7841,37 @@
         <v>0.057</v>
       </c>
       <c r="M80">
-        <v>1.063632492</v>
+        <v>1.077268806</v>
       </c>
       <c r="N80">
-        <v>-1.006632492</v>
+        <v>-1.020268806</v>
       </c>
       <c r="O80">
-        <v>-0.24159179808</v>
+        <v>-0.24486451344</v>
       </c>
       <c r="P80">
-        <v>-0.7650406939200001</v>
+        <v>-0.7754042925600002</v>
       </c>
       <c r="Q80">
-        <v>-0.7660406939200001</v>
+        <v>-0.7764042925600002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>1.121045225199283</v>
+        <v>1.172247378780201</v>
       </c>
       <c r="T80">
-        <v>5.283079981732884</v>
+        <v>5.53465521895826</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01286158527770887</v>
+        <v>0.01269878040077585</v>
       </c>
       <c r="W80">
-        <v>0.2327672381915163</v>
+        <v>0.2328056275814971</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.05358993865712025</v>
+        <v>0.05291158500323268</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.4300883953332249</v>
+        <v>0.4319883953332249</v>
       </c>
       <c r="C81">
-        <v>-0.8929623740957742</v>
+        <v>-0.9678722619663733</v>
       </c>
       <c r="D81">
-        <v>3.471607625904226</v>
+        <v>3.454527738033627</v>
       </c>
       <c r="E81">
-        <v>4.53557</v>
+        <v>4.5934</v>
       </c>
       <c r="F81">
-        <v>4.56857</v>
+        <v>4.6264</v>
       </c>
       <c r="G81">
         <v>0.204</v>
@@ -7923,37 +7923,37 @@
         <v>0.057</v>
       </c>
       <c r="M81">
-        <v>1.077268806</v>
+        <v>1.09090512</v>
       </c>
       <c r="N81">
-        <v>-1.020268806</v>
+        <v>-1.03390512</v>
       </c>
       <c r="O81">
-        <v>-0.24486451344</v>
+        <v>-0.2481372288000001</v>
       </c>
       <c r="P81">
-        <v>-0.7754042925600002</v>
+        <v>-0.7857678912000001</v>
       </c>
       <c r="Q81">
-        <v>-0.7764042925600002</v>
+        <v>-0.7867678912000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>1.172247378780201</v>
+        <v>1.228569747719211</v>
       </c>
       <c r="T81">
-        <v>5.53465521895826</v>
+        <v>5.811387979906174</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01269878040077585</v>
+        <v>0.01254004564576615</v>
       </c>
       <c r="W81">
-        <v>0.2328056275814971</v>
+        <v>0.2328430572367284</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.05291158500323268</v>
+        <v>0.05225019019069221</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.4319883953332249</v>
+        <v>0.4338883953332249</v>
       </c>
       <c r="C82">
-        <v>-0.9678722619663733</v>
+        <v>-1.04261491068556</v>
       </c>
       <c r="D82">
-        <v>3.454527738033627</v>
+        <v>3.43761508931444</v>
       </c>
       <c r="E82">
-        <v>4.5934</v>
+        <v>4.65123</v>
       </c>
       <c r="F82">
-        <v>4.6264</v>
+        <v>4.68423</v>
       </c>
       <c r="G82">
         <v>0.204</v>
@@ -8005,37 +8005,37 @@
         <v>0.057</v>
       </c>
       <c r="M82">
-        <v>1.09090512</v>
+        <v>1.104541434</v>
       </c>
       <c r="N82">
-        <v>-1.03390512</v>
+        <v>-1.047541434</v>
       </c>
       <c r="O82">
-        <v>-0.2481372288000001</v>
+        <v>-0.2514099441600001</v>
       </c>
       <c r="P82">
-        <v>-0.7857678912000001</v>
+        <v>-0.7961314898400002</v>
       </c>
       <c r="Q82">
-        <v>-0.7867678912000001</v>
+        <v>-0.7971314898400002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>1.228569747719211</v>
+        <v>1.290820787072854</v>
       </c>
       <c r="T82">
-        <v>5.811387979906174</v>
+        <v>6.117250505164393</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01254004564576615</v>
+        <v>0.01238523026742336</v>
       </c>
       <c r="W82">
-        <v>0.2328430572367284</v>
+        <v>0.2328795627029416</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.05225019019069221</v>
+        <v>0.05160512611426393</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.4338883953332249</v>
+        <v>0.4357883953332249</v>
       </c>
       <c r="C83">
-        <v>-1.04261491068556</v>
+        <v>-1.117192764590589</v>
       </c>
       <c r="D83">
-        <v>3.43761508931444</v>
+        <v>3.420867235409411</v>
       </c>
       <c r="E83">
-        <v>4.65123</v>
+        <v>4.70906</v>
       </c>
       <c r="F83">
-        <v>4.68423</v>
+        <v>4.74206</v>
       </c>
       <c r="G83">
         <v>0.204</v>
@@ -8087,37 +8087,37 @@
         <v>0.057</v>
       </c>
       <c r="M83">
-        <v>1.104541434</v>
+        <v>1.118177748</v>
       </c>
       <c r="N83">
-        <v>-1.047541434</v>
+        <v>-1.061177748</v>
       </c>
       <c r="O83">
-        <v>-0.2514099441600001</v>
+        <v>-0.25468265952</v>
       </c>
       <c r="P83">
-        <v>-0.7961314898400002</v>
+        <v>-0.8064950884800002</v>
       </c>
       <c r="Q83">
-        <v>-0.7971314898400002</v>
+        <v>-0.8074950884800002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>1.290820787072854</v>
+        <v>1.359988608576902</v>
       </c>
       <c r="T83">
-        <v>6.117250505164393</v>
+        <v>6.457097755451304</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01238523026742336</v>
+        <v>0.01223419087391819</v>
       </c>
       <c r="W83">
-        <v>0.2328795627029416</v>
+        <v>0.2329151777919301</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.05160512611426393</v>
+        <v>0.05097579530799246</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.4357883953332249</v>
+        <v>0.4376883953332249</v>
       </c>
       <c r="C84">
-        <v>-1.117192764590589</v>
+        <v>-1.191608220615004</v>
       </c>
       <c r="D84">
-        <v>3.420867235409411</v>
+        <v>3.404281779384996</v>
       </c>
       <c r="E84">
-        <v>4.70906</v>
+        <v>4.76689</v>
       </c>
       <c r="F84">
-        <v>4.74206</v>
+        <v>4.79989</v>
       </c>
       <c r="G84">
         <v>0.204</v>
@@ -8169,37 +8169,37 @@
         <v>0.057</v>
       </c>
       <c r="M84">
-        <v>1.118177748</v>
+        <v>1.131814062</v>
       </c>
       <c r="N84">
-        <v>-1.061177748</v>
+        <v>-1.074814062</v>
       </c>
       <c r="O84">
-        <v>-0.25468265952</v>
+        <v>-0.25795537488</v>
       </c>
       <c r="P84">
-        <v>-0.8064950884800002</v>
+        <v>-0.8168586871200001</v>
       </c>
       <c r="Q84">
-        <v>-0.8074950884800002</v>
+        <v>-0.8178586871200001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>1.359988608576902</v>
+        <v>1.437293820846131</v>
       </c>
       <c r="T84">
-        <v>6.457097755451304</v>
+        <v>6.836927035183734</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01223419087391819</v>
+        <v>0.01208679098387099</v>
       </c>
       <c r="W84">
-        <v>0.2329151777919301</v>
+        <v>0.2329499346860032</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.05097579530799246</v>
+        <v>0.0503616290994624</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.4376883953332249</v>
+        <v>0.4395883953332249</v>
       </c>
       <c r="C85">
-        <v>-1.191608220615004</v>
+        <v>-1.26586362943224</v>
       </c>
       <c r="D85">
-        <v>3.404281779384996</v>
+        <v>3.38785637056776</v>
       </c>
       <c r="E85">
-        <v>4.76689</v>
+        <v>4.82472</v>
       </c>
       <c r="F85">
-        <v>4.79989</v>
+        <v>4.85772</v>
       </c>
       <c r="G85">
         <v>0.204</v>
@@ -8251,37 +8251,37 @@
         <v>0.057</v>
       </c>
       <c r="M85">
-        <v>1.131814062</v>
+        <v>1.145450376</v>
       </c>
       <c r="N85">
-        <v>-1.074814062</v>
+        <v>-1.088450376</v>
       </c>
       <c r="O85">
-        <v>-0.25795537488</v>
+        <v>-0.26122809024</v>
       </c>
       <c r="P85">
-        <v>-0.8168586871200001</v>
+        <v>-0.8272222857600001</v>
       </c>
       <c r="Q85">
-        <v>-0.8178586871200001</v>
+        <v>-0.8282222857600001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>1.437293820846131</v>
+        <v>1.524262184649015</v>
       </c>
       <c r="T85">
-        <v>6.836927035183734</v>
+        <v>7.26423497488272</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01208679098387099</v>
+        <v>0.01194290061501538</v>
       </c>
       <c r="W85">
-        <v>0.2329499346860032</v>
+        <v>0.2329838640349794</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.0503616290994624</v>
+        <v>0.04976208589589737</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.4395883953332249</v>
+        <v>0.4414883953332249</v>
       </c>
       <c r="C86">
-        <v>-1.26586362943224</v>
+        <v>-1.339961296566269</v>
       </c>
       <c r="D86">
-        <v>3.38785637056776</v>
+        <v>3.371588703433732</v>
       </c>
       <c r="E86">
-        <v>4.82472</v>
+        <v>4.88255</v>
       </c>
       <c r="F86">
-        <v>4.85772</v>
+        <v>4.915550000000001</v>
       </c>
       <c r="G86">
         <v>0.204</v>
@@ -8333,37 +8333,37 @@
         <v>0.057</v>
       </c>
       <c r="M86">
-        <v>1.145450376</v>
+        <v>1.15908669</v>
       </c>
       <c r="N86">
-        <v>-1.088450376</v>
+        <v>-1.10208669</v>
       </c>
       <c r="O86">
-        <v>-0.26122809024</v>
+        <v>-0.2645008056</v>
       </c>
       <c r="P86">
-        <v>-0.8272222857600001</v>
+        <v>-0.8375858844000001</v>
       </c>
       <c r="Q86">
-        <v>-0.8282222857600001</v>
+        <v>-0.8385858844000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>1.524262184649014</v>
+        <v>1.622826330292281</v>
       </c>
       <c r="T86">
-        <v>7.264234974882714</v>
+        <v>7.748517306541562</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01194290061501538</v>
+        <v>0.01180239590189755</v>
       </c>
       <c r="W86">
-        <v>0.2329838640349794</v>
+        <v>0.2330169950463326</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.04976208589589737</v>
+        <v>0.0491766495912398</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.4414883953332249</v>
+        <v>0.4433883953332249</v>
       </c>
       <c r="C87">
-        <v>-1.339961296566269</v>
+        <v>-1.413903483470404</v>
       </c>
       <c r="D87">
-        <v>3.371588703433732</v>
+        <v>3.355476516529596</v>
       </c>
       <c r="E87">
-        <v>4.88255</v>
+        <v>4.94038</v>
       </c>
       <c r="F87">
-        <v>4.915550000000001</v>
+        <v>4.973380000000001</v>
       </c>
       <c r="G87">
         <v>0.204</v>
@@ -8415,37 +8415,37 @@
         <v>0.057</v>
       </c>
       <c r="M87">
-        <v>1.15908669</v>
+        <v>1.172723004</v>
       </c>
       <c r="N87">
-        <v>-1.10208669</v>
+        <v>-1.115723004</v>
       </c>
       <c r="O87">
-        <v>-0.2645008056</v>
+        <v>-0.2677735209600001</v>
       </c>
       <c r="P87">
-        <v>-0.8375858844000001</v>
+        <v>-0.8479494830400003</v>
       </c>
       <c r="Q87">
-        <v>-0.8385858844000001</v>
+        <v>-0.8489494830400003</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>1.622826330292281</v>
+        <v>1.735471068170302</v>
       </c>
       <c r="T87">
-        <v>7.748517306541562</v>
+        <v>8.301982828437389</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01180239590189755</v>
+        <v>0.01166515874024758</v>
       </c>
       <c r="W87">
-        <v>0.2330169950463326</v>
+        <v>0.2330493555690496</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.0491766495912398</v>
+        <v>0.04860482808436484</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.4433883953332249</v>
+        <v>0.4452883953332249</v>
       </c>
       <c r="C88">
-        <v>-1.413903483470404</v>
+        <v>-1.48769240857532</v>
       </c>
       <c r="D88">
-        <v>3.355476516529596</v>
+        <v>3.33951759142468</v>
       </c>
       <c r="E88">
-        <v>4.94038</v>
+        <v>4.99821</v>
       </c>
       <c r="F88">
-        <v>4.973380000000001</v>
+        <v>5.031210000000001</v>
       </c>
       <c r="G88">
         <v>0.204</v>
@@ -8497,37 +8497,37 @@
         <v>0.057</v>
       </c>
       <c r="M88">
-        <v>1.172723004</v>
+        <v>1.186359318</v>
       </c>
       <c r="N88">
-        <v>-1.115723004</v>
+        <v>-1.129359318</v>
       </c>
       <c r="O88">
-        <v>-0.2677735209600001</v>
+        <v>-0.2710462363200001</v>
       </c>
       <c r="P88">
-        <v>-0.8479494830400003</v>
+        <v>-0.8583130816800002</v>
       </c>
       <c r="Q88">
-        <v>-0.8489494830400003</v>
+        <v>-0.8593130816800002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.735471068170302</v>
+        <v>1.865445765721863</v>
       </c>
       <c r="T88">
-        <v>8.301982828437389</v>
+        <v>8.940596892163342</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01166515874024758</v>
+        <v>0.01153107645587692</v>
       </c>
       <c r="W88">
-        <v>0.2330493555690496</v>
+        <v>0.2330809721717042</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.04860482808436484</v>
+        <v>0.04804615189948713</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.4452883953332249</v>
+        <v>0.447188395333225</v>
       </c>
       <c r="C89">
-        <v>-1.48769240857532</v>
+        <v>-1.561330248307308</v>
       </c>
       <c r="D89">
-        <v>3.33951759142468</v>
+        <v>3.323709751692693</v>
       </c>
       <c r="E89">
-        <v>4.99821</v>
+        <v>5.05604</v>
       </c>
       <c r="F89">
-        <v>5.031210000000001</v>
+        <v>5.089040000000001</v>
       </c>
       <c r="G89">
         <v>0.204</v>
@@ -8579,37 +8579,37 @@
         <v>0.057</v>
       </c>
       <c r="M89">
-        <v>1.186359318</v>
+        <v>1.199995632</v>
       </c>
       <c r="N89">
-        <v>-1.129359318</v>
+        <v>-1.142995632</v>
       </c>
       <c r="O89">
-        <v>-0.2710462363200001</v>
+        <v>-0.2743189516800001</v>
       </c>
       <c r="P89">
-        <v>-0.8583130816800002</v>
+        <v>-0.8686766803200002</v>
       </c>
       <c r="Q89">
-        <v>-0.8593130816800002</v>
+        <v>-0.8696766803200002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.865445765721863</v>
+        <v>2.017082912865352</v>
       </c>
       <c r="T89">
-        <v>8.940596892163342</v>
+        <v>9.685646633176955</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01153107645587692</v>
+        <v>0.01140004149615104</v>
       </c>
       <c r="W89">
-        <v>0.2330809721717042</v>
+        <v>0.2331118702152076</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.04804615189948713</v>
+        <v>0.04750017290062925</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.447188395333225</v>
+        <v>0.4490883953332249</v>
       </c>
       <c r="C90">
-        <v>-1.561330248307308</v>
+        <v>-1.634819138077736</v>
       </c>
       <c r="D90">
-        <v>3.323709751692693</v>
+        <v>3.308050861922264</v>
       </c>
       <c r="E90">
-        <v>5.05604</v>
+        <v>5.11387</v>
       </c>
       <c r="F90">
-        <v>5.089040000000001</v>
+        <v>5.146870000000001</v>
       </c>
       <c r="G90">
         <v>0.204</v>
@@ -8661,37 +8661,37 @@
         <v>0.057</v>
       </c>
       <c r="M90">
-        <v>1.199995632</v>
+        <v>1.213631946</v>
       </c>
       <c r="N90">
-        <v>-1.142995632</v>
+        <v>-1.156631946</v>
       </c>
       <c r="O90">
-        <v>-0.2743189516800001</v>
+        <v>-0.27759166704</v>
       </c>
       <c r="P90">
-        <v>-0.8686766803200002</v>
+        <v>-0.8790402789600003</v>
       </c>
       <c r="Q90">
-        <v>-0.8696766803200002</v>
+        <v>-0.8800402789600003</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>2.017082912865352</v>
+        <v>2.196290450398565</v>
       </c>
       <c r="T90">
-        <v>9.685646633176955</v>
+        <v>10.56615996346577</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01140004149615104</v>
+        <v>0.0112719511422617</v>
       </c>
       <c r="W90">
-        <v>0.2331118702152076</v>
+        <v>0.2331420739206547</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.04750017290062925</v>
+        <v>0.04696646309275709</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.4490883953332249</v>
+        <v>0.4509883953332249</v>
       </c>
       <c r="C91">
-        <v>-1.634819138077736</v>
+        <v>-1.708161173244694</v>
       </c>
       <c r="D91">
-        <v>3.308050861922264</v>
+        <v>3.292538826755307</v>
       </c>
       <c r="E91">
-        <v>5.11387</v>
+        <v>5.1717</v>
       </c>
       <c r="F91">
-        <v>5.146870000000001</v>
+        <v>5.204700000000001</v>
       </c>
       <c r="G91">
         <v>0.204</v>
@@ -8743,37 +8743,37 @@
         <v>0.057</v>
       </c>
       <c r="M91">
-        <v>1.213631946</v>
+        <v>1.22726826</v>
       </c>
       <c r="N91">
-        <v>-1.156631946</v>
+        <v>-1.17026826</v>
       </c>
       <c r="O91">
-        <v>-0.27759166704</v>
+        <v>-0.2808643824000001</v>
       </c>
       <c r="P91">
-        <v>-0.8790402789600003</v>
+        <v>-0.8894038776000002</v>
       </c>
       <c r="Q91">
-        <v>-0.8800402789600003</v>
+        <v>-0.8904038776000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>2.196290450398565</v>
+        <v>2.411339495438423</v>
       </c>
       <c r="T91">
-        <v>10.56615996346577</v>
+        <v>11.62277595981235</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.0112719511422617</v>
+        <v>0.01114670724068102</v>
       </c>
       <c r="W91">
-        <v>0.2331420739206547</v>
+        <v>0.2331716064326474</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.04696646309275709</v>
+        <v>0.04644461350283757</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.4509883953332249</v>
+        <v>0.4528883953332249</v>
       </c>
       <c r="C92">
-        <v>-1.708161173244694</v>
+        <v>-1.781358410047684</v>
       </c>
       <c r="D92">
-        <v>3.292538826755307</v>
+        <v>3.277171589952316</v>
       </c>
       <c r="E92">
-        <v>5.1717</v>
+        <v>5.22953</v>
       </c>
       <c r="F92">
-        <v>5.204700000000001</v>
+        <v>5.262530000000001</v>
       </c>
       <c r="G92">
         <v>0.204</v>
@@ -8825,37 +8825,37 @@
         <v>0.057</v>
       </c>
       <c r="M92">
-        <v>1.22726826</v>
+        <v>1.240904574</v>
       </c>
       <c r="N92">
-        <v>-1.17026826</v>
+        <v>-1.183904574</v>
       </c>
       <c r="O92">
-        <v>-0.2808643824000001</v>
+        <v>-0.2841370977600001</v>
       </c>
       <c r="P92">
-        <v>-0.8894038776000002</v>
+        <v>-0.8997674762400002</v>
       </c>
       <c r="Q92">
-        <v>-0.8904038776000002</v>
+        <v>-0.9007674762400002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>2.411339495438423</v>
+        <v>2.674177217153803</v>
       </c>
       <c r="T92">
-        <v>11.62277595981235</v>
+        <v>12.91419551090261</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01114670724068102</v>
+        <v>0.01102421595232189</v>
       </c>
       <c r="W92">
-        <v>0.2331716064326474</v>
+        <v>0.2332004898784425</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.04644461350283757</v>
+        <v>0.04593423313467448</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.4528883953332249</v>
+        <v>0.4547883953332249</v>
       </c>
       <c r="C93">
-        <v>-1.781358410047684</v>
+        <v>-1.854412866516276</v>
       </c>
       <c r="D93">
-        <v>3.277171589952316</v>
+        <v>3.261947133483725</v>
       </c>
       <c r="E93">
-        <v>5.22953</v>
+        <v>5.287360000000001</v>
       </c>
       <c r="F93">
-        <v>5.262530000000001</v>
+        <v>5.320360000000001</v>
       </c>
       <c r="G93">
         <v>0.204</v>
@@ -8907,37 +8907,37 @@
         <v>0.057</v>
       </c>
       <c r="M93">
-        <v>1.240904574</v>
+        <v>1.254540888</v>
       </c>
       <c r="N93">
-        <v>-1.183904574</v>
+        <v>-1.197540888</v>
       </c>
       <c r="O93">
-        <v>-0.2841370977600001</v>
+        <v>-0.28740981312</v>
       </c>
       <c r="P93">
-        <v>-0.8997674762400002</v>
+        <v>-0.9101310748800002</v>
       </c>
       <c r="Q93">
-        <v>-0.9007674762400002</v>
+        <v>-0.9111310748800002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>2.674177217153803</v>
+        <v>3.002724369298029</v>
       </c>
       <c r="T93">
-        <v>12.91419551090261</v>
+        <v>14.52846994976544</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01102421595232189</v>
+        <v>0.01090438751805752</v>
       </c>
       <c r="W93">
-        <v>0.2332004898784425</v>
+        <v>0.233228745423242</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.04593423313467448</v>
+        <v>0.04543494799190628</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.4547883953332249</v>
+        <v>0.4566883953332249</v>
       </c>
       <c r="C94">
-        <v>-1.854412866516276</v>
+        <v>-1.927326523353536</v>
       </c>
       <c r="D94">
-        <v>3.261947133483725</v>
+        <v>3.246863476646465</v>
       </c>
       <c r="E94">
-        <v>5.287360000000001</v>
+        <v>5.345190000000001</v>
       </c>
       <c r="F94">
-        <v>5.320360000000001</v>
+        <v>5.378190000000001</v>
       </c>
       <c r="G94">
         <v>0.204</v>
@@ -8989,37 +8989,37 @@
         <v>0.057</v>
       </c>
       <c r="M94">
-        <v>1.254540888</v>
+        <v>1.268177202</v>
       </c>
       <c r="N94">
-        <v>-1.197540888</v>
+        <v>-1.211177202</v>
       </c>
       <c r="O94">
-        <v>-0.28740981312</v>
+        <v>-0.29068252848</v>
       </c>
       <c r="P94">
-        <v>-0.9101310748800002</v>
+        <v>-0.9204946735200001</v>
       </c>
       <c r="Q94">
-        <v>-0.9111310748800002</v>
+        <v>-0.9214946735200001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>3.002724369298029</v>
+        <v>3.425142136340605</v>
       </c>
       <c r="T94">
-        <v>14.52846994976544</v>
+        <v>16.60396565687479</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01090438751805752</v>
+        <v>0.01078713603936873</v>
       </c>
       <c r="W94">
-        <v>0.233228745423242</v>
+        <v>0.2332563933219169</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.04543494799190628</v>
+        <v>0.04494640016403628</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.4566883953332249</v>
+        <v>0.4585883953332249</v>
       </c>
       <c r="C95">
-        <v>-1.927326523353536</v>
+        <v>-2.00010132479508</v>
       </c>
       <c r="D95">
-        <v>3.246863476646465</v>
+        <v>3.231918675204921</v>
       </c>
       <c r="E95">
-        <v>5.345190000000001</v>
+        <v>5.403020000000001</v>
       </c>
       <c r="F95">
-        <v>5.378190000000001</v>
+        <v>5.436020000000001</v>
       </c>
       <c r="G95">
         <v>0.204</v>
@@ -9071,37 +9071,37 @@
         <v>0.057</v>
       </c>
       <c r="M95">
-        <v>1.268177202</v>
+        <v>1.281813516</v>
       </c>
       <c r="N95">
-        <v>-1.211177202</v>
+        <v>-1.224813516</v>
       </c>
       <c r="O95">
-        <v>-0.29068252848</v>
+        <v>-0.2939552438400001</v>
       </c>
       <c r="P95">
-        <v>-0.9204946735200001</v>
+        <v>-0.9308582721600003</v>
       </c>
       <c r="Q95">
-        <v>-0.9214946735200001</v>
+        <v>-0.9318582721600003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>3.425142136340605</v>
+        <v>3.988365825730707</v>
       </c>
       <c r="T95">
-        <v>16.60396565687479</v>
+        <v>19.37129326635392</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01078713603936873</v>
+        <v>0.01067237927299247</v>
       </c>
       <c r="W95">
-        <v>0.2332563933219169</v>
+        <v>0.2332834529674284</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.04494640016403628</v>
+        <v>0.04446824697080187</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.4585883953332249</v>
+        <v>0.4604883953332249</v>
       </c>
       <c r="C96">
-        <v>-2.00010132479508</v>
+        <v>-2.072739179444485</v>
       </c>
       <c r="D96">
-        <v>3.231918675204921</v>
+        <v>3.217110820555516</v>
       </c>
       <c r="E96">
-        <v>5.403020000000001</v>
+        <v>5.460850000000001</v>
       </c>
       <c r="F96">
-        <v>5.436020000000001</v>
+        <v>5.493850000000001</v>
       </c>
       <c r="G96">
         <v>0.204</v>
@@ -9153,37 +9153,37 @@
         <v>0.057</v>
       </c>
       <c r="M96">
-        <v>1.281813516</v>
+        <v>1.29544983</v>
       </c>
       <c r="N96">
-        <v>-1.224813516</v>
+        <v>-1.23844983</v>
       </c>
       <c r="O96">
-        <v>-0.2939552438400001</v>
+        <v>-0.2972279592000001</v>
       </c>
       <c r="P96">
-        <v>-0.9308582721600003</v>
+        <v>-0.9412218708000003</v>
       </c>
       <c r="Q96">
-        <v>-0.9318582721600003</v>
+        <v>-0.9422218708000003</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>3.988365825730707</v>
+        <v>4.776878990876851</v>
       </c>
       <c r="T96">
-        <v>19.37129326635392</v>
+        <v>23.24555191962472</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01067237927299247</v>
+        <v>0.01056003843853991</v>
       </c>
       <c r="W96">
-        <v>0.2332834529674284</v>
+        <v>0.2333099429361923</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.04446824697080187</v>
+        <v>0.04400016016058295</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.4604883953332249</v>
+        <v>0.4623883953332248</v>
       </c>
       <c r="C97">
-        <v>-2.072739179444485</v>
+        <v>-2.145241961085859</v>
       </c>
       <c r="D97">
-        <v>3.217110820555516</v>
+        <v>3.202438038914142</v>
       </c>
       <c r="E97">
-        <v>5.460850000000001</v>
+        <v>5.518680000000001</v>
       </c>
       <c r="F97">
-        <v>5.493850000000001</v>
+        <v>5.551680000000001</v>
       </c>
       <c r="G97">
         <v>0.204</v>
@@ -9235,37 +9235,37 @@
         <v>0.057</v>
       </c>
       <c r="M97">
-        <v>1.29544983</v>
+        <v>1.309086144</v>
       </c>
       <c r="N97">
-        <v>-1.23844983</v>
+        <v>-1.252086144</v>
       </c>
       <c r="O97">
-        <v>-0.2972279592000001</v>
+        <v>-0.3005006745600001</v>
       </c>
       <c r="P97">
-        <v>-0.9412218708000003</v>
+        <v>-0.9515854694400003</v>
       </c>
       <c r="Q97">
-        <v>-0.9422218708000003</v>
+        <v>-0.9525854694400003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>4.776878990876851</v>
+        <v>5.959648738596066</v>
       </c>
       <c r="T97">
-        <v>23.24555191962472</v>
+        <v>29.05693989953091</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01056003843853991</v>
+        <v>0.01045003803813846</v>
       </c>
       <c r="W97">
-        <v>0.2333099429361923</v>
+        <v>0.233335881030607</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.04400016016058295</v>
+        <v>0.04354182515891014</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.4623883953332248</v>
+        <v>0.4642883953332249</v>
       </c>
       <c r="C98">
-        <v>-2.145241961085858</v>
+        <v>-2.217611509474272</v>
       </c>
       <c r="D98">
-        <v>3.202438038914142</v>
+        <v>3.187898490525728</v>
       </c>
       <c r="E98">
-        <v>5.51868</v>
+        <v>5.57651</v>
       </c>
       <c r="F98">
-        <v>5.55168</v>
+        <v>5.60951</v>
       </c>
       <c r="G98">
         <v>0.204</v>
@@ -9317,37 +9317,37 @@
         <v>0.057</v>
       </c>
       <c r="M98">
-        <v>1.309086144</v>
+        <v>1.322722458</v>
       </c>
       <c r="N98">
-        <v>-1.252086144</v>
+        <v>-1.265722458</v>
       </c>
       <c r="O98">
-        <v>-0.30050067456</v>
+        <v>-0.30377338992</v>
       </c>
       <c r="P98">
-        <v>-0.9515854694400001</v>
+        <v>-0.9619490680800001</v>
       </c>
       <c r="Q98">
-        <v>-0.9525854694400001</v>
+        <v>-0.9629490680800001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>5.95964873859605</v>
+        <v>7.930931651461401</v>
       </c>
       <c r="T98">
-        <v>29.05693989953084</v>
+        <v>38.74258653270778</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01045003803813846</v>
+        <v>0.01034230568722981</v>
       </c>
       <c r="W98">
-        <v>0.233335881030607</v>
+        <v>0.2333612843189512</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.04354182515891014</v>
+        <v>0.04309294036345757</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.4642883953332249</v>
+        <v>0.4661883953332249</v>
       </c>
       <c r="C99">
-        <v>-2.217611509474272</v>
+        <v>-2.289849631104742</v>
       </c>
       <c r="D99">
-        <v>3.187898490525728</v>
+        <v>3.173490368895258</v>
       </c>
       <c r="E99">
-        <v>5.57651</v>
+        <v>5.63434</v>
       </c>
       <c r="F99">
-        <v>5.60951</v>
+        <v>5.66734</v>
       </c>
       <c r="G99">
         <v>0.204</v>
@@ -9399,37 +9399,37 @@
         <v>0.057</v>
       </c>
       <c r="M99">
-        <v>1.322722458</v>
+        <v>1.336358772</v>
       </c>
       <c r="N99">
-        <v>-1.265722458</v>
+        <v>-1.279358772</v>
       </c>
       <c r="O99">
-        <v>-0.30377338992</v>
+        <v>-0.30704610528</v>
       </c>
       <c r="P99">
-        <v>-0.9619490680800001</v>
+        <v>-0.9723126667200002</v>
       </c>
       <c r="Q99">
-        <v>-0.9629490680800001</v>
+        <v>-0.9733126667200002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>7.930931651461401</v>
+        <v>11.8734974771921</v>
       </c>
       <c r="T99">
-        <v>38.74258653270778</v>
+        <v>58.11387979906167</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01034230568722981</v>
+        <v>0.01023677195572747</v>
       </c>
       <c r="W99">
-        <v>0.2333612843189512</v>
+        <v>0.2333861691728395</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.04309294036345757</v>
+        <v>0.04265321648219778</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.4661883953332249</v>
+        <v>0.4680883953332249</v>
       </c>
       <c r="C100">
-        <v>-2.289849631104742</v>
+        <v>-2.36195809996047</v>
       </c>
       <c r="D100">
-        <v>3.173490368895258</v>
+        <v>3.15921190003953</v>
       </c>
       <c r="E100">
-        <v>5.63434</v>
+        <v>5.69217</v>
       </c>
       <c r="F100">
-        <v>5.66734</v>
+        <v>5.72517</v>
       </c>
       <c r="G100">
         <v>0.204</v>
@@ -9481,37 +9481,37 @@
         <v>0.057</v>
       </c>
       <c r="M100">
-        <v>1.336358772</v>
+        <v>1.349995086</v>
       </c>
       <c r="N100">
-        <v>-1.279358772</v>
+        <v>-1.292995086</v>
       </c>
       <c r="O100">
-        <v>-0.30704610528</v>
+        <v>-0.31031882064</v>
       </c>
       <c r="P100">
-        <v>-0.9723126667200002</v>
+        <v>-0.9826762653600001</v>
       </c>
       <c r="Q100">
-        <v>-0.9733126667200002</v>
+        <v>-0.9836762653600001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>11.8734974771921</v>
+        <v>23.7011949543842</v>
       </c>
       <c r="T100">
-        <v>58.11387979906167</v>
+        <v>116.2277595981233</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01023677195572747</v>
+        <v>0.01013337021880093</v>
       </c>
       <c r="W100">
-        <v>0.2333861691728395</v>
+        <v>0.2334105513024068</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.04265321648219778</v>
+        <v>0.04222237591167044</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.4680883953332249</v>
-      </c>
-      <c r="C101">
-        <v>-2.36195809996047</v>
-      </c>
-      <c r="D101">
-        <v>3.15921190003953</v>
-      </c>
-      <c r="E101">
-        <v>5.69217</v>
-      </c>
-      <c r="F101">
-        <v>5.72517</v>
-      </c>
-      <c r="G101">
-        <v>0.204</v>
-      </c>
-      <c r="H101">
-        <v>5.75</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.056</v>
-      </c>
-      <c r="K101">
-        <v>-0.001000000000000001</v>
-      </c>
-      <c r="L101">
-        <v>0.057</v>
-      </c>
-      <c r="M101">
-        <v>1.349995086</v>
-      </c>
-      <c r="N101">
-        <v>-1.292995086</v>
-      </c>
-      <c r="O101">
-        <v>-0.31031882064</v>
-      </c>
-      <c r="P101">
-        <v>-0.9826762653600001</v>
-      </c>
-      <c r="Q101">
-        <v>-0.9836762653600001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>23.7011949543842</v>
-      </c>
-      <c r="T101">
-        <v>116.2277595981233</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01013337021880093</v>
-      </c>
-      <c r="W101">
-        <v>0.2334105513024068</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.04222237591167044</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
